--- a/news_daily/2026-10-23.xlsx
+++ b/news_daily/2026-10-23.xlsx
@@ -14,11 +14,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="執行紀錄" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$AT$34</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$AT$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$AT$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$AT$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$W$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$AW$51</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$AW$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$AW$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$AW$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$W$3</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -463,7 +463,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT34"/>
+  <dimension ref="A1:AW51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -512,6 +512,9 @@
     <col width="22" customWidth="1" min="44" max="44"/>
     <col width="22" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -745,6 +748,21 @@
           <t>最近執行</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Title_ZH</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>FinBERT_Title</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>分析快取</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -933,6 +951,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1109,6 +1130,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1309,6 +1333,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -1505,6 +1532,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1681,6 +1711,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1881,6 +1914,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2057,6 +2093,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
@@ -2257,6 +2296,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU9" s="3" t="inlineStr"/>
+      <c r="AV9" s="3" t="inlineStr"/>
+      <c r="AW9" s="3" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -2457,6 +2499,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2633,6 +2678,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -2829,6 +2877,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3009,6 +3060,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -3213,6 +3267,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -3417,6 +3474,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU15" s="4" t="inlineStr"/>
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -3617,6 +3677,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU16" s="4" t="inlineStr"/>
+      <c r="AV16" s="4" t="inlineStr"/>
+      <c r="AW16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -3821,6 +3884,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU17" s="4" t="inlineStr"/>
+      <c r="AV17" s="4" t="inlineStr"/>
+      <c r="AW17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3997,6 +4063,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4177,6 +4246,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU19" s="2" t="inlineStr"/>
+      <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4357,6 +4429,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU20" s="2" t="inlineStr"/>
+      <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4561,6 +4636,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4777,6 +4855,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU22" s="3" t="inlineStr"/>
+      <c r="AV22" s="3" t="inlineStr"/>
+      <c r="AW22" s="3" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -4978,7 +5059,14 @@
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU23" s="3" t="inlineStr"/>
+      <c r="AV23" s="3" t="inlineStr"/>
+      <c r="AW23" s="3" t="inlineStr">
+        <is>
+          <t>沿用</t>
         </is>
       </c>
     </row>
@@ -5178,7 +5266,14 @@
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU24" s="3" t="inlineStr"/>
+      <c r="AV24" s="3" t="inlineStr"/>
+      <c r="AW24" s="3" t="inlineStr">
+        <is>
+          <t>沿用</t>
         </is>
       </c>
     </row>
@@ -5377,6 +5472,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU25" s="3" t="inlineStr"/>
+      <c r="AV25" s="3" t="inlineStr"/>
+      <c r="AW25" s="3" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -5577,6 +5675,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU26" s="3" t="inlineStr"/>
+      <c r="AV26" s="3" t="inlineStr"/>
+      <c r="AW26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="3" t="inlineStr">
@@ -5789,6 +5890,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU27" s="3" t="inlineStr"/>
+      <c r="AV27" s="3" t="inlineStr"/>
+      <c r="AW27" s="3" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5949,6 +6053,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU28" s="2" t="inlineStr"/>
+      <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="inlineStr">
@@ -6141,6 +6248,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU29" s="3" t="inlineStr"/>
+      <c r="AV29" s="3" t="inlineStr"/>
+      <c r="AW29" s="3" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6313,6 +6423,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU30" s="2" t="inlineStr"/>
+      <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6489,6 +6602,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU31" s="2" t="inlineStr"/>
+      <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6661,6 +6777,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU32" s="2" t="inlineStr"/>
+      <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6821,6 +6940,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU33" s="2" t="inlineStr"/>
+      <c r="AV33" s="2" t="inlineStr"/>
+      <c r="AW33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6993,9 +7115,2657 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU34" s="2" t="inlineStr"/>
+      <c r="AV34" s="2" t="inlineStr"/>
+      <c r="AW34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:02:46+08:00</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms' Q3: The Market Is Being Dramatic About Negative Free Cash Flow (META)</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 發生任何信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>-0.954</v>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPdE5iVjdqcEFjRXpTekoydE1SeVFDeFlhem5tOTU5YmNxUllsSUJqX3UzLU1NWk5NVk50XzZpazBfV0l6LTBMd3hQWHlzZXlpVGQxbUpRT1FrSnk3a1ZxZWc0WnViT19DSlJ0djFtbDdUcUNvME1jN0dNWF9RMi1kSTFnWEY3THdVZndyb21mdm9yWWtIQmlRWDFWTk1pYlVYdkY5RDFKUXJPbGo1MDJ1LXNVdXAwcEU2?oc=5</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>149e59ea41d352c6658f6cf5</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="AL35" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AM35" s="2" t="inlineStr"/>
+      <c r="AN35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>c20c109fac208b53f739b04e</t>
+        </is>
+      </c>
+      <c r="AP35" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR35" s="2" t="inlineStr"/>
+      <c r="AS35" s="2" t="inlineStr">
+        <is>
+          <t>5561c485d0bf6a8f7f3c02db776ad98b37ba9deae1b4991a83a6428d34222d39</t>
+        </is>
+      </c>
+      <c r="AT35" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU35" s="2" t="inlineStr"/>
+      <c r="AV35" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms' Q3: The Market Is Being Dramatic About Negative Free Cash Flow (META)</t>
+        </is>
+      </c>
+      <c r="AW35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQeWhsa1VSYXhEM3JSbUNSMEZWTEFqd3A5NGd5SFJWdEZoZmpTRlNzUmM1RVFYT3cwb2JrNzRPMUFfUHlETHI5S1AyajJJdmF0YW5XbnU3MzBGREZOREo4YUszYUl3b3Y1TEdsMXpTWmxqX18zNUlSS2RwcjA0ZkJ6SXo1ek1IcWlhVl9IU1lJTVJqQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>ec4ba7c19aafcde2fbd710f7</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr"/>
+      <c r="AE36" s="2" t="inlineStr"/>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="inlineStr"/>
+      <c r="AL36" s="2" t="inlineStr"/>
+      <c r="AM36" s="2" t="inlineStr"/>
+      <c r="AN36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>0c52c54c8a0e83fbafe6b0e1</t>
+        </is>
+      </c>
+      <c r="AP36" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR36" s="2" t="inlineStr"/>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>703f213218315ca169df93ed957d57b06b6c1dd9d90f95dcae08448b5366a4d2</t>
+        </is>
+      </c>
+      <c r="AT36" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="inlineStr"/>
+      <c r="AV36" s="2" t="inlineStr">
+        <is>
+          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
+        </is>
+      </c>
+      <c r="AW36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:30:04+08:00</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>-0.873</v>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2724913</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>d1348ad94c5e9aa7d9188003</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr"/>
+      <c r="AE37" s="2" t="inlineStr"/>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="inlineStr"/>
+      <c r="AL37" s="2" t="inlineStr"/>
+      <c r="AM37" s="2" t="inlineStr"/>
+      <c r="AN37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>2ff90a8d58ba249a9252028a</t>
+        </is>
+      </c>
+      <c r="AP37" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="AQ37" s="2" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="AR37" s="2" t="inlineStr"/>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>3b9ae9feaec50aeeb331e95a5ee2a1e3c8322512f70ac97854f13f8a8a230dbf</t>
+        </is>
+      </c>
+      <c r="AT37" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU37" s="2" t="inlineStr">
+        <is>
+          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
+        </is>
+      </c>
+      <c r="AV37" s="2" t="inlineStr">
+        <is>
+          <t>Publishers and advertisers call on EU and UK antitrust regulators to suspend Meta's new business terms</t>
+        </is>
+      </c>
+      <c r="AW37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:24:10+08:00</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>-0.824</v>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2726833</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>f25a40e5e491828684fad933</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr"/>
+      <c r="AE38" s="2" t="inlineStr"/>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="inlineStr"/>
+      <c r="AL38" s="2" t="inlineStr"/>
+      <c r="AM38" s="2" t="inlineStr"/>
+      <c r="AN38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>0e55b465fd7b98d6d05db82c</t>
+        </is>
+      </c>
+      <c r="AP38" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR38" s="2" t="inlineStr"/>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>1f1b7d07ae6f5f91e714914b3b662be882027be3a6ebc1733cfc29a4f725c9d0</t>
+        </is>
+      </c>
+      <c r="AT38" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU38" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選</t>
+        </is>
+      </c>
+      <c r="AV38" s="2" t="inlineStr">
+        <is>
+          <t>Brazilian president accuses Meta of rigging election</t>
+        </is>
+      </c>
+      <c r="AW38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T14:15:46+08:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>-0.745</v>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-META/news/</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>a37f44666d6b93b23fa84c03</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr"/>
+      <c r="AE39" s="2" t="inlineStr"/>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="inlineStr"/>
+      <c r="AL39" s="2" t="inlineStr"/>
+      <c r="AM39" s="2" t="inlineStr"/>
+      <c r="AN39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>c9eb84ac77729681440eb57a</t>
+        </is>
+      </c>
+      <c r="AP39" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR39" s="2" t="inlineStr"/>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>1f591b90e9b440b67c36a5eb4472a728985b298e24dc706d0798748c6426b66a</t>
+        </is>
+      </c>
+      <c r="AT39" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU39" s="2" t="inlineStr">
+        <is>
+          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
+        </is>
+      </c>
+      <c r="AV39" s="2" t="inlineStr">
+        <is>
+          <t>Greece passes social media ban for children under 15</t>
+        </is>
+      </c>
+      <c r="AW39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:13:48+08:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="n">
+        <v>-0.378</v>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxON0pWLThkWllqVTRvcVRMY1NVeUN0UVNxa08tNkRhbzQxTUFlaTZON1BOYkh4bDEtaHB4X2d6dHk3VS1sVDhYMEhhZ0IyMVpjTXJjWVJ3WE9ZTDdWWG9paC1zdHZpbFpFNVZNTk9aYXhQRnRtWVlXRE0tZ2hOaDFmc2RIQUV5aTRBbEJaaDNsWUNxUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>464a7cf6ed8a0d8eb8b7128c</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr"/>
+      <c r="AE40" s="2" t="inlineStr"/>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI40" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK40" s="2" t="inlineStr"/>
+      <c r="AL40" s="2" t="inlineStr"/>
+      <c r="AM40" s="2" t="inlineStr"/>
+      <c r="AN40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>2030e51b7ee960a291545c4e</t>
+        </is>
+      </c>
+      <c r="AP40" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ40" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR40" s="2" t="inlineStr"/>
+      <c r="AS40" s="2" t="inlineStr">
+        <is>
+          <t>70d3c8f7cedf509a0d49a31d514c14f40cdbe72f4eeffa852820c7c46d87a158</t>
+        </is>
+      </c>
+      <c r="AT40" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU40" s="2" t="inlineStr"/>
+      <c r="AV40" s="2" t="inlineStr">
+        <is>
+          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
+        </is>
+      </c>
+      <c r="AW40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:02:10+08:00</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQTm1ESVJlZTFrQ2dzbzNrYXVrSWxNSmpkMkNVa2FKMG1WZ0Q5WDJpemo5dnR4Vzl3TXNORk9pa2hWQWZfUDJxS0ljT28xeW9yN2JyODJFRUZDX21QSVM3Yi1SSkZhNE5yOG4zUEJ1V2VGazJ1M3dQVEZVU2tBY0E5N1BmYlgweGJRUHlXRlRUXzh3b3F1dHdnUUJ6UWU?oc=5</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>36137dc64507e498c5a8b4a3</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr"/>
+      <c r="AE41" s="2" t="inlineStr"/>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI41" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK41" s="2" t="inlineStr"/>
+      <c r="AL41" s="2" t="inlineStr"/>
+      <c r="AM41" s="2" t="inlineStr"/>
+      <c r="AN41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>db841bab92ab7c46294c18f6</t>
+        </is>
+      </c>
+      <c r="AP41" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ41" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR41" s="2" t="inlineStr"/>
+      <c r="AS41" s="2" t="inlineStr">
+        <is>
+          <t>e75e8c8129bbdb2191154bec165f56eaf1d00c270b682a696164f93458fff26e</t>
+        </is>
+      </c>
+      <c r="AT41" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU41" s="2" t="inlineStr"/>
+      <c r="AV41" s="2" t="inlineStr">
+        <is>
+          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
+        </is>
+      </c>
+      <c r="AW41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:23:56+08:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVW91c2d5NHc5a2FWRXBqWktkSEVlTnQ4dzRiT1dYZzNoNUpjQ3dJMUduVzVScDVBbk9Ock5ERGVIRlJtUEQ4WS1GTnF5dFRjTTRKU3Q0RjVhVW13cGhWbmZVcEhuU0lzQ1VKTmJsbF9saWZQa1ZiSVJJRkVBV3BBejdHeUFPVlhhUDROb0N4YVhzdGdzUFNwV05ZLXk?oc=5</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>785b78480c14b20eb1f594f0</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr"/>
+      <c r="AE42" s="2" t="inlineStr"/>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI42" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ42" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK42" s="2" t="inlineStr"/>
+      <c r="AL42" s="2" t="inlineStr"/>
+      <c r="AM42" s="2" t="inlineStr"/>
+      <c r="AN42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>5c22badffe5cdc021e3009ee</t>
+        </is>
+      </c>
+      <c r="AP42" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR42" s="2" t="inlineStr"/>
+      <c r="AS42" s="2" t="inlineStr">
+        <is>
+          <t>6d610b7eb950150470f57c0b234a95303c318c7975b534d2cd2e804370ec4b99</t>
+        </is>
+      </c>
+      <c r="AT42" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU42" s="2" t="inlineStr"/>
+      <c r="AV42" s="2" t="inlineStr">
+        <is>
+          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="AW42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:40:12+08:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNb3BSbEJKZ3ZoRHcwbURvdW96Sm1iS3I5WXNSOWRTdHZJaC1GVWJYaVpuWHVUVVdwbGE3QlVrdlg3VGFrS0tpX05PM3FDVzFpX1FBcnJGT1dmZmxJQ2V6NTV6Uklsci02dFlvNFl1cUVjeDNmNTFjMFJqdEpBcFlPX3otemVOcVlQckNDT2pfZ2lCODZlQnQyWENyZThHQ3RMcmV3Wnh2ZTREeEJhS3R6a045b20xUXByZlpFTg?oc=5</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Barchart.com</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>802f478a954c806c1d45e5e7</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr"/>
+      <c r="AE43" s="2" t="inlineStr"/>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI43" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ43" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK43" s="2" t="inlineStr"/>
+      <c r="AL43" s="2" t="inlineStr"/>
+      <c r="AM43" s="2" t="inlineStr"/>
+      <c r="AN43" s="2" t="inlineStr"/>
+      <c r="AO43" s="2" t="inlineStr">
+        <is>
+          <t>7a52a62180c5bc31721f420f</t>
+        </is>
+      </c>
+      <c r="AP43" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ43" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR43" s="2" t="inlineStr"/>
+      <c r="AS43" s="2" t="inlineStr">
+        <is>
+          <t>61557616d68c76cf4c34a0623191d34058d3274ed70d8fc1e86334c98f7433ca</t>
+        </is>
+      </c>
+      <c r="AT43" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU43" s="2" t="inlineStr"/>
+      <c r="AV43" s="2" t="inlineStr">
+        <is>
+          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
+        </is>
+      </c>
+      <c r="AW43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:33:47+08:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQQXhDOGpZb054SmlrVEdRLUdPNmMxWEhWc3Z1Um9vLWVXZnBrdVJYRWpWSTRaSG1YNC1xcjBnemZlZGEzOGo5NGhvRllmcHRPZm5RMFpQSWdRX1NWRUEzNFpsUzNBclZDem1aT3lYMHpYMHU3NUlSZ3g0dVNBVDJHeDYzMVRHT2FZVEE?oc=5</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>097dc8c2b12cafa6727c9bbb</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr"/>
+      <c r="AE44" s="2" t="inlineStr"/>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI44" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK44" s="2" t="inlineStr"/>
+      <c r="AL44" s="2" t="inlineStr"/>
+      <c r="AM44" s="2" t="inlineStr"/>
+      <c r="AN44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>2c57a52603540bb61b3bf4fa</t>
+        </is>
+      </c>
+      <c r="AP44" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ44" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR44" s="2" t="inlineStr"/>
+      <c r="AS44" s="2" t="inlineStr">
+        <is>
+          <t>b36d9804e90e3ff91df4cf736f0b68d3b88ee6026366e5b8f3336a9db6b54010</t>
+        </is>
+      </c>
+      <c r="AT44" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU44" s="2" t="inlineStr"/>
+      <c r="AV44" s="2" t="inlineStr">
+        <is>
+          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="AW44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:15:24+08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQYm8yUUVkOEpqVThyY3FUNkxnSEVKT2tzSEpVVnZrci1yYjlKMlZtZHpxeHFYQmlYbzdkRmZzOUl6aGxJeXZNU0x4Ny1QUUtZbnpNc0RfazVMMDA5R0dCdy1nak5DekZMWEVtUTFacWtuWXp2Z2dLTFhsamRjUGRhem94ckVfcHZyalV2ZVVrNnNORnBIdmFPdEYwaVNRcklDbV91RUNyZlo2dGpk?oc=5</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>9abb1549a2b10e0057938029</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr"/>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr"/>
+      <c r="AE45" s="2" t="inlineStr"/>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK45" s="2" t="inlineStr"/>
+      <c r="AL45" s="2" t="inlineStr"/>
+      <c r="AM45" s="2" t="inlineStr"/>
+      <c r="AN45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>b7806ae6c60efbb0fc8012c9</t>
+        </is>
+      </c>
+      <c r="AP45" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ45" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR45" s="2" t="inlineStr"/>
+      <c r="AS45" s="2" t="inlineStr">
+        <is>
+          <t>7460bf9f6be0b4f2f93f68a081035b7483fdc8361ea4c7c337c2c96d815d773e</t>
+        </is>
+      </c>
+      <c r="AT45" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU45" s="2" t="inlineStr"/>
+      <c r="AV45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
+        </is>
+      </c>
+      <c r="AW45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNd2FTR2VVcnNyQXoyWndTa205TWVDOTZhTTdudU0yWUlPMERDXy0zVnRlSHgtNkJRWGJyTEtqUXl0WHZjeUNKYzNWdk5ZeEtnYmZUWjJKbmVfaVVtOTJ0QlhYOWcxSVVabFBKQUtZVF9wM0M4WUU5RXBQT2JRZXZwd0NOWUd1aUoyUC1rVGxyS1g0V3Jvbm5sU1BxX3Fmdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>726f56e7556fab9bdf9deab7</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr"/>
+      <c r="AE46" s="2" t="inlineStr"/>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI46" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK46" s="2" t="inlineStr"/>
+      <c r="AL46" s="2" t="inlineStr"/>
+      <c r="AM46" s="2" t="inlineStr"/>
+      <c r="AN46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>693874aa285dd04e50bb1359</t>
+        </is>
+      </c>
+      <c r="AP46" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ46" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR46" s="2" t="inlineStr"/>
+      <c r="AS46" s="2" t="inlineStr">
+        <is>
+          <t>0517b27ea681c43f5c5a7dc8767c5d0bfb6b5ca885d47a82bbe3196b354fc837</t>
+        </is>
+      </c>
+      <c r="AT46" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU46" s="2" t="inlineStr"/>
+      <c r="AV46" s="2" t="inlineStr">
+        <is>
+          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
+        </is>
+      </c>
+      <c r="AW46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:22:37+08:00</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>$Meta Platforms (META.US)$ ...</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxOMzFhUEtyNm9YNHpPOGRETW0xU0EzXy1PckFJTk9jdFpSbXJIbkVvaVZRNDJMUi16UjRvLVVjMzFoVWZ4aDBFTjZPVmhqem9ndkJWT0hvQzd3alBSVXhTbFB3NVhIVDZTc1pGZzhKNVhGamd5enB1WGJza1dndkF4UUdWa0JfaUhmWjYzVGpBR2RqV2c5Nzk4QVh4bXUwQUJ5VlVNbmhnWTNpVmhiTU85NXlyQUVCYzZ6dF80WWU5RjBRNzBZUjJYcW1NTkUtaEtYSWVOOF91OXdOWmJkOTNGM3pxb1FhVDR0ODhKcWZuc3NqWFQzTXRqbXZWRkZRSmFQaFpJaTJJNEU0NTlHYzFtOG51djlKMzE0NEVyVThtN2Z1OU5tbjMtb3RKMW9rTHdpdmZlazgySXNZdFZra2JLS0lOMmdWbDZOWHVMSVNfcWNfdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Moomoo</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>8463c439cab6cd0ceeed0259</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr"/>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr"/>
+      <c r="AE47" s="2" t="inlineStr"/>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI47" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ47" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK47" s="2" t="inlineStr"/>
+      <c r="AL47" s="2" t="inlineStr"/>
+      <c r="AM47" s="2" t="inlineStr"/>
+      <c r="AN47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>50895bc72b56d2d92b44606e</t>
+        </is>
+      </c>
+      <c r="AP47" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ47" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR47" s="2" t="inlineStr"/>
+      <c r="AS47" s="2" t="inlineStr">
+        <is>
+          <t>39a874f75cef45cadda21059624f246da76bcea88d3705c5c291469f18417643</t>
+        </is>
+      </c>
+      <c r="AT47" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU47" s="2" t="inlineStr"/>
+      <c r="AV47" s="2" t="inlineStr">
+        <is>
+          <t>$Meta Platforms (META.US)$ ...</t>
+        </is>
+      </c>
+      <c r="AW47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T16:01:04+08:00</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>小摩上調Meta目標價至940美元</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/news/5330363</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>c0a62dd94e77e5e7c175baf7</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr"/>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr"/>
+      <c r="AE48" s="2" t="inlineStr"/>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI48" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ48" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK48" s="2" t="inlineStr"/>
+      <c r="AL48" s="2" t="inlineStr"/>
+      <c r="AM48" s="2" t="inlineStr"/>
+      <c r="AN48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>f241bb1e8daac06e5ebfd5dd</t>
+        </is>
+      </c>
+      <c r="AP48" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ48" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR48" s="2" t="inlineStr"/>
+      <c r="AS48" s="2" t="inlineStr">
+        <is>
+          <t>3fb9a23409e8708ea25ee8cb1bc2c57d982f0b2f9aece44cf25ef07e40b312e8</t>
+        </is>
+      </c>
+      <c r="AT48" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU48" s="2" t="inlineStr">
+        <is>
+          <t>小摩上調Meta目標價至940美元</t>
+        </is>
+      </c>
+      <c r="AV48" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan raised its Meta target price to $940</t>
+        </is>
+      </c>
+      <c r="AW48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:48:55+08:00</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr"/>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2725612</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>8276af8c1e2d6a8b1be57709</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr"/>
+      <c r="Y49" s="2" t="inlineStr"/>
+      <c r="Z49" s="2" t="inlineStr"/>
+      <c r="AA49" s="2" t="inlineStr"/>
+      <c r="AB49" s="2" t="inlineStr"/>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr"/>
+      <c r="AE49" s="2" t="inlineStr"/>
+      <c r="AF49" s="2" t="inlineStr"/>
+      <c r="AG49" s="2" t="inlineStr"/>
+      <c r="AH49" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI49" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ49" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK49" s="2" t="inlineStr"/>
+      <c r="AL49" s="2" t="inlineStr"/>
+      <c r="AM49" s="2" t="inlineStr"/>
+      <c r="AN49" s="2" t="inlineStr"/>
+      <c r="AO49" s="2" t="inlineStr">
+        <is>
+          <t>062e54352538d735417bc00a</t>
+        </is>
+      </c>
+      <c r="AP49" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ49" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR49" s="2" t="inlineStr"/>
+      <c r="AS49" s="2" t="inlineStr">
+        <is>
+          <t>4b5ef37f6c305b434f4c1c87831cc70b581ac080fa1eb75cf03d769479d206b7</t>
+        </is>
+      </c>
+      <c r="AT49" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU49" s="2" t="inlineStr">
+        <is>
+          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
+        </is>
+      </c>
+      <c r="AV49" s="2" t="inlineStr">
+        <is>
+          <t>"The Wolf of Wall Street" Ackman: If the war and inflation cool down, 2027 will be an amazing year</t>
+        </is>
+      </c>
+      <c r="AW49" s="2" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:13:19+08:00</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr"/>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS0s3YXJsQVNHNFBJSGVFUVMtOWwwVlE5UzN2c2V2OFVKOU1UZHJfT0c0Y1dXUHFWdFI0R2JBcGg3ZzJBUmZBSmF6ZHBvS3NyMWp0NklKQWxiTFFYZzRGSmNicFZzTFk0X0lrcFpWZ0VIcFd1Zi1UUVpMX2NlYzJmVEUxTVJrODRzblZvX25IRV9tajluWlBJ?oc=5</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>5774c207e5b4837ece36440d</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr"/>
+      <c r="Y50" s="2" t="inlineStr"/>
+      <c r="Z50" s="2" t="inlineStr"/>
+      <c r="AA50" s="2" t="inlineStr"/>
+      <c r="AB50" s="2" t="inlineStr"/>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr"/>
+      <c r="AE50" s="2" t="inlineStr"/>
+      <c r="AF50" s="2" t="inlineStr"/>
+      <c r="AG50" s="2" t="inlineStr"/>
+      <c r="AH50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI50" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ50" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK50" s="2" t="inlineStr"/>
+      <c r="AL50" s="2" t="inlineStr"/>
+      <c r="AM50" s="2" t="inlineStr"/>
+      <c r="AN50" s="2" t="inlineStr"/>
+      <c r="AO50" s="2" t="inlineStr">
+        <is>
+          <t>2ed2364af3d9acea1114881a</t>
+        </is>
+      </c>
+      <c r="AP50" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ50" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR50" s="2" t="inlineStr"/>
+      <c r="AS50" s="2" t="inlineStr">
+        <is>
+          <t>29d466f90bfdbdf0f7a04f87c9e7bf26725f4409800afedde98bde36f1864b93</t>
+        </is>
+      </c>
+      <c r="AT50" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU50" s="2" t="inlineStr"/>
+      <c r="AV50" s="2" t="inlineStr">
+        <is>
+          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
+        </is>
+      </c>
+      <c r="AW50" s="2" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:07:13+08:00</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr"/>
+      <c r="I51" s="2" t="inlineStr"/>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOU5uNjZ6MTZvd2dkQlFWUFJ2VW9RdGNmLS12R0x2UDlmMC1jRzBpWmFWNGwzcXFySjFBUzd1V1JSeU5FNGVYdDQzZ1hod1g5SmVOZUw2eTZKTEt0QnpFT0JONTc5eEhHUlNUTHlhMnd6TmF2eW9JX1FzZElGZzRsak1MdVFER2RYVDVJOHVVSnZLSXVzWUNBOFVoU0JfUF9z?oc=5</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>1662077625e20e4158c6d6d9</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr"/>
+      <c r="Y51" s="2" t="inlineStr"/>
+      <c r="Z51" s="2" t="inlineStr"/>
+      <c r="AA51" s="2" t="inlineStr"/>
+      <c r="AB51" s="2" t="inlineStr"/>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr"/>
+      <c r="AE51" s="2" t="inlineStr"/>
+      <c r="AF51" s="2" t="inlineStr"/>
+      <c r="AG51" s="2" t="inlineStr"/>
+      <c r="AH51" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI51" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ51" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK51" s="2" t="inlineStr"/>
+      <c r="AL51" s="2" t="inlineStr"/>
+      <c r="AM51" s="2" t="inlineStr"/>
+      <c r="AN51" s="2" t="inlineStr"/>
+      <c r="AO51" s="2" t="inlineStr">
+        <is>
+          <t>27ae0e4f67d27857be0e98ca</t>
+        </is>
+      </c>
+      <c r="AP51" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ51" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR51" s="2" t="inlineStr"/>
+      <c r="AS51" s="2" t="inlineStr">
+        <is>
+          <t>8d2bf44846475f369f3134681a465fafc51dc63ac9d90ebf8bca03c554f5390f</t>
+        </is>
+      </c>
+      <c r="AT51" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU51" s="2" t="inlineStr"/>
+      <c r="AV51" s="2" t="inlineStr">
+        <is>
+          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
+        </is>
+      </c>
+      <c r="AW51" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT34"/>
+  <autoFilter ref="A1:AW51"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -7006,7 +9776,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT18"/>
+  <dimension ref="A1:AW18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -7055,6 +9825,9 @@
     <col width="22" customWidth="1" min="44" max="44"/>
     <col width="22" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7288,6 +10061,21 @@
           <t>最近執行</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Title_ZH</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>FinBERT_Title</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>分析快取</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
@@ -7484,6 +10272,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU2" s="3" t="inlineStr"/>
+      <c r="AV2" s="3" t="inlineStr"/>
+      <c r="AW2" s="3" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -7684,6 +10475,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU3" s="4" t="inlineStr"/>
+      <c r="AV3" s="4" t="inlineStr"/>
+      <c r="AW3" s="4" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
@@ -7884,6 +10678,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU4" s="3" t="inlineStr"/>
+      <c r="AV4" s="3" t="inlineStr"/>
+      <c r="AW4" s="3" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -8084,6 +10881,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
@@ -8280,6 +11080,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU6" s="3" t="inlineStr"/>
+      <c r="AV6" s="3" t="inlineStr"/>
+      <c r="AW6" s="3" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -8484,6 +11287,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -8688,6 +11494,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU8" s="4" t="inlineStr"/>
+      <c r="AV8" s="4" t="inlineStr"/>
+      <c r="AW8" s="4" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
@@ -8888,6 +11697,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU9" s="4" t="inlineStr"/>
+      <c r="AV9" s="4" t="inlineStr"/>
+      <c r="AW9" s="4" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
@@ -9092,6 +11904,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU10" s="4" t="inlineStr"/>
+      <c r="AV10" s="4" t="inlineStr"/>
+      <c r="AW10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
@@ -9296,6 +12111,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU11" s="3" t="inlineStr"/>
+      <c r="AV11" s="3" t="inlineStr"/>
+      <c r="AW11" s="3" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -9512,6 +12330,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU12" s="3" t="inlineStr"/>
+      <c r="AV12" s="3" t="inlineStr"/>
+      <c r="AW12" s="3" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
@@ -9713,7 +12534,14 @@
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU13" s="3" t="inlineStr"/>
+      <c r="AV13" s="3" t="inlineStr"/>
+      <c r="AW13" s="3" t="inlineStr">
+        <is>
+          <t>沿用</t>
         </is>
       </c>
     </row>
@@ -9913,7 +12741,14 @@
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU14" s="3" t="inlineStr"/>
+      <c r="AV14" s="3" t="inlineStr"/>
+      <c r="AW14" s="3" t="inlineStr">
+        <is>
+          <t>沿用</t>
         </is>
       </c>
     </row>
@@ -10112,6 +12947,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU15" s="3" t="inlineStr"/>
+      <c r="AV15" s="3" t="inlineStr"/>
+      <c r="AW15" s="3" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -10312,6 +13150,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU16" s="3" t="inlineStr"/>
+      <c r="AV16" s="3" t="inlineStr"/>
+      <c r="AW16" s="3" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -10524,6 +13365,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU17" s="3" t="inlineStr"/>
+      <c r="AV17" s="3" t="inlineStr"/>
+      <c r="AW17" s="3" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="3" t="inlineStr">
@@ -10716,9 +13560,12 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU18" s="3" t="inlineStr"/>
+      <c r="AV18" s="3" t="inlineStr"/>
+      <c r="AW18" s="3" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT18"/>
+  <autoFilter ref="A1:AW18"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -10729,7 +13576,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT31"/>
+  <dimension ref="A1:AW32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -10778,6 +13625,9 @@
     <col width="22" customWidth="1" min="44" max="44"/>
     <col width="22" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -11011,6 +13861,21 @@
           <t>最近執行</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Title_ZH</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>FinBERT_Title</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>分析快取</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -11199,6 +14064,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -11375,6 +14243,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU3" s="2" t="inlineStr"/>
+      <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -11575,6 +14446,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU4" s="2" t="inlineStr"/>
+      <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
@@ -11771,6 +14645,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU5" s="3" t="inlineStr"/>
+      <c r="AV5" s="3" t="inlineStr"/>
+      <c r="AW5" s="3" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -11947,6 +14824,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -12147,6 +15027,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU7" s="4" t="inlineStr"/>
+      <c r="AV7" s="4" t="inlineStr"/>
+      <c r="AW7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -12323,6 +15206,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -12499,6 +15385,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
@@ -12695,6 +15584,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU10" s="3" t="inlineStr"/>
+      <c r="AV10" s="3" t="inlineStr"/>
+      <c r="AW10" s="3" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -12875,6 +15767,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -13079,6 +15974,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU12" s="4" t="inlineStr"/>
+      <c r="AV12" s="4" t="inlineStr"/>
+      <c r="AW12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -13283,6 +16181,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU13" s="4" t="inlineStr"/>
+      <c r="AV13" s="4" t="inlineStr"/>
+      <c r="AW13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -13483,6 +16384,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU14" s="4" t="inlineStr"/>
+      <c r="AV14" s="4" t="inlineStr"/>
+      <c r="AW14" s="4" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="4" t="inlineStr">
@@ -13687,6 +16591,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU15" s="4" t="inlineStr"/>
+      <c r="AV15" s="4" t="inlineStr"/>
+      <c r="AW15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -13863,6 +16770,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -14043,6 +16953,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -14223,6 +17136,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU18" s="2" t="inlineStr"/>
+      <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -14427,6 +17343,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU19" s="3" t="inlineStr"/>
+      <c r="AV19" s="3" t="inlineStr"/>
+      <c r="AW19" s="3" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -14643,6 +17562,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU20" s="3" t="inlineStr"/>
+      <c r="AV20" s="3" t="inlineStr"/>
+      <c r="AW20" s="3" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -14844,7 +17766,14 @@
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU21" s="3" t="inlineStr"/>
+      <c r="AV21" s="3" t="inlineStr"/>
+      <c r="AW21" s="3" t="inlineStr">
+        <is>
+          <t>沿用</t>
         </is>
       </c>
     </row>
@@ -15044,7 +17973,14 @@
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU22" s="3" t="inlineStr"/>
+      <c r="AV22" s="3" t="inlineStr"/>
+      <c r="AW22" s="3" t="inlineStr">
+        <is>
+          <t>沿用</t>
         </is>
       </c>
     </row>
@@ -15247,6 +18183,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU23" s="3" t="inlineStr"/>
+      <c r="AV23" s="3" t="inlineStr"/>
+      <c r="AW23" s="3" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -15459,6 +18398,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU24" s="3" t="inlineStr"/>
+      <c r="AV24" s="3" t="inlineStr"/>
+      <c r="AW24" s="3" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -15619,6 +18561,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU25" s="2" t="inlineStr"/>
+      <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="3" t="inlineStr">
@@ -15811,6 +18756,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU26" s="3" t="inlineStr"/>
+      <c r="AV26" s="3" t="inlineStr"/>
+      <c r="AW26" s="3" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -15983,6 +18931,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU27" s="2" t="inlineStr"/>
+      <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -16159,6 +19110,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU28" s="2" t="inlineStr"/>
+      <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -16331,6 +19285,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU29" s="2" t="inlineStr"/>
+      <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -16491,6 +19448,9 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU30" s="2" t="inlineStr"/>
+      <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -16663,9 +19623,185 @@
           <t>a62af6ad2a0044b7a685a4178159b27a</t>
         </is>
       </c>
+      <c r="AU31" s="2" t="inlineStr"/>
+      <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" s="2" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:02:46+08:00</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms' Q3: The Market Is Being Dramatic About Negative Free Cash Flow (META)</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 發生任何信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="2" t="inlineStr"/>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>-0.954</v>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiuAFBVV95cUxPdE5iVjdqcEFjRXpTekoydE1SeVFDeFlhem5tOTU5YmNxUllsSUJqX3UzLU1NWk5NVk50XzZpazBfV0l6LTBMd3hQWHlzZXlpVGQxbUpRT1FrSnk3a1ZxZWc0WnViT19DSlJ0djFtbDdUcUNvME1jN0dNWF9RMi1kSTFnWEY3THdVZndyb21mdm9yWWtIQmlRWDFWTk1pYlVYdkY5RDFKUXJPbGo1MDJ1LXNVdXAwcEU2?oc=5</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>149e59ea41d352c6658f6cf5</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr"/>
+      <c r="Y32" s="2" t="inlineStr"/>
+      <c r="Z32" s="2" t="inlineStr"/>
+      <c r="AA32" s="2" t="inlineStr"/>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD32" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE32" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF32" s="2" t="inlineStr"/>
+      <c r="AG32" s="2" t="inlineStr"/>
+      <c r="AH32" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI32" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ32" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK32" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="AL32" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AM32" s="2" t="inlineStr"/>
+      <c r="AN32" s="2" t="inlineStr"/>
+      <c r="AO32" s="2" t="inlineStr">
+        <is>
+          <t>c20c109fac208b53f739b04e</t>
+        </is>
+      </c>
+      <c r="AP32" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ32" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR32" s="2" t="inlineStr"/>
+      <c r="AS32" s="2" t="inlineStr">
+        <is>
+          <t>5561c485d0bf6a8f7f3c02db776ad98b37ba9deae1b4991a83a6428d34222d39</t>
+        </is>
+      </c>
+      <c r="AT32" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU32" s="2" t="inlineStr"/>
+      <c r="AV32" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms' Q3: The Market Is Being Dramatic About Negative Free Cash Flow (META)</t>
+        </is>
+      </c>
+      <c r="AW32" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT31"/>
+  <autoFilter ref="A1:AW32"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16676,7 +19812,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AT1"/>
+  <dimension ref="A1:AW17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -16725,6 +19861,9 @@
     <col width="22" customWidth="1" min="44" max="44"/>
     <col width="22" customWidth="1" min="45" max="45"/>
     <col width="22" customWidth="1" min="46" max="46"/>
+    <col width="22" customWidth="1" min="47" max="47"/>
+    <col width="22" customWidth="1" min="48" max="48"/>
+    <col width="22" customWidth="1" min="49" max="49"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16958,9 +20097,2496 @@
           <t>最近執行</t>
         </is>
       </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>Title_ZH</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>FinBERT_Title</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>分析快取</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
+      <c r="I2" s="2" t="inlineStr"/>
+      <c r="J2" s="2" t="inlineStr"/>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>-0.9330000000000001</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr"/>
+      <c r="R2" s="2" t="inlineStr"/>
+      <c r="S2" s="2" t="inlineStr"/>
+      <c r="T2" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U2" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQeWhsa1VSYXhEM3JSbUNSMEZWTEFqd3A5NGd5SFJWdEZoZmpTRlNzUmM1RVFYT3cwb2JrNzRPMUFfUHlETHI5S1AyajJJdmF0YW5XbnU3MzBGREZOREo4YUszYUl3b3Y1TEdsMXpTWmxqX18zNUlSS2RwcjA0ZkJ6SXo1ek1IcWlhVl9IU1lJTVJqQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W2" s="2" t="inlineStr">
+        <is>
+          <t>ec4ba7c19aafcde2fbd710f7</t>
+        </is>
+      </c>
+      <c r="X2" s="2" t="inlineStr"/>
+      <c r="Y2" s="2" t="inlineStr"/>
+      <c r="Z2" s="2" t="inlineStr"/>
+      <c r="AA2" s="2" t="inlineStr"/>
+      <c r="AB2" s="2" t="inlineStr"/>
+      <c r="AC2" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD2" s="2" t="inlineStr"/>
+      <c r="AE2" s="2" t="inlineStr"/>
+      <c r="AF2" s="2" t="inlineStr"/>
+      <c r="AG2" s="2" t="inlineStr"/>
+      <c r="AH2" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI2" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ2" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK2" s="2" t="inlineStr"/>
+      <c r="AL2" s="2" t="inlineStr"/>
+      <c r="AM2" s="2" t="inlineStr"/>
+      <c r="AN2" s="2" t="inlineStr"/>
+      <c r="AO2" s="2" t="inlineStr">
+        <is>
+          <t>0c52c54c8a0e83fbafe6b0e1</t>
+        </is>
+      </c>
+      <c r="AP2" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ2" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR2" s="2" t="inlineStr"/>
+      <c r="AS2" s="2" t="inlineStr">
+        <is>
+          <t>703f213218315ca169df93ed957d57b06b6c1dd9d90f95dcae08448b5366a4d2</t>
+        </is>
+      </c>
+      <c r="AT2" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU2" s="2" t="inlineStr"/>
+      <c r="AV2" s="2" t="inlineStr">
+        <is>
+          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
+        </is>
+      </c>
+      <c r="AW2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:30:04+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
+      <c r="I3" s="2" t="inlineStr"/>
+      <c r="J3" s="2" t="inlineStr"/>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>-0.873</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+      <c r="S3" s="2" t="inlineStr"/>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2724913</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>d1348ad94c5e9aa7d9188003</t>
+        </is>
+      </c>
+      <c r="X3" s="2" t="inlineStr"/>
+      <c r="Y3" s="2" t="inlineStr"/>
+      <c r="Z3" s="2" t="inlineStr"/>
+      <c r="AA3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AC3" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD3" s="2" t="inlineStr"/>
+      <c r="AE3" s="2" t="inlineStr"/>
+      <c r="AF3" s="2" t="inlineStr"/>
+      <c r="AG3" s="2" t="inlineStr"/>
+      <c r="AH3" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI3" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ3" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK3" s="2" t="inlineStr"/>
+      <c r="AL3" s="2" t="inlineStr"/>
+      <c r="AM3" s="2" t="inlineStr"/>
+      <c r="AN3" s="2" t="inlineStr"/>
+      <c r="AO3" s="2" t="inlineStr">
+        <is>
+          <t>2ff90a8d58ba249a9252028a</t>
+        </is>
+      </c>
+      <c r="AP3" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="AQ3" s="2" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="AR3" s="2" t="inlineStr"/>
+      <c r="AS3" s="2" t="inlineStr">
+        <is>
+          <t>3b9ae9feaec50aeeb331e95a5ee2a1e3c8322512f70ac97854f13f8a8a230dbf</t>
+        </is>
+      </c>
+      <c r="AT3" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU3" s="2" t="inlineStr">
+        <is>
+          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
+        </is>
+      </c>
+      <c r="AV3" s="2" t="inlineStr">
+        <is>
+          <t>Publishers and advertisers call on EU and UK antitrust regulators to suspend Meta's new business terms</t>
+        </is>
+      </c>
+      <c r="AW3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:24:10+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
+      <c r="I4" s="2" t="inlineStr"/>
+      <c r="J4" s="2" t="inlineStr"/>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>-0.824</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+      <c r="S4" s="2" t="inlineStr"/>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2726833</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>f25a40e5e491828684fad933</t>
+        </is>
+      </c>
+      <c r="X4" s="2" t="inlineStr"/>
+      <c r="Y4" s="2" t="inlineStr"/>
+      <c r="Z4" s="2" t="inlineStr"/>
+      <c r="AA4" s="2" t="inlineStr"/>
+      <c r="AB4" s="2" t="inlineStr"/>
+      <c r="AC4" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD4" s="2" t="inlineStr"/>
+      <c r="AE4" s="2" t="inlineStr"/>
+      <c r="AF4" s="2" t="inlineStr"/>
+      <c r="AG4" s="2" t="inlineStr"/>
+      <c r="AH4" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI4" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ4" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK4" s="2" t="inlineStr"/>
+      <c r="AL4" s="2" t="inlineStr"/>
+      <c r="AM4" s="2" t="inlineStr"/>
+      <c r="AN4" s="2" t="inlineStr"/>
+      <c r="AO4" s="2" t="inlineStr">
+        <is>
+          <t>0e55b465fd7b98d6d05db82c</t>
+        </is>
+      </c>
+      <c r="AP4" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ4" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR4" s="2" t="inlineStr"/>
+      <c r="AS4" s="2" t="inlineStr">
+        <is>
+          <t>1f1b7d07ae6f5f91e714914b3b662be882027be3a6ebc1733cfc29a4f725c9d0</t>
+        </is>
+      </c>
+      <c r="AT4" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU4" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選</t>
+        </is>
+      </c>
+      <c r="AV4" s="2" t="inlineStr">
+        <is>
+          <t>Brazilian president accuses Meta of rigging election</t>
+        </is>
+      </c>
+      <c r="AW4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T14:15:46+08:00</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
+      <c r="I5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>-0.745</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+      <c r="S5" s="2" t="inlineStr"/>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-META/news/</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>a37f44666d6b93b23fa84c03</t>
+        </is>
+      </c>
+      <c r="X5" s="2" t="inlineStr"/>
+      <c r="Y5" s="2" t="inlineStr"/>
+      <c r="Z5" s="2" t="inlineStr"/>
+      <c r="AA5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AC5" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD5" s="2" t="inlineStr"/>
+      <c r="AE5" s="2" t="inlineStr"/>
+      <c r="AF5" s="2" t="inlineStr"/>
+      <c r="AG5" s="2" t="inlineStr"/>
+      <c r="AH5" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI5" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ5" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK5" s="2" t="inlineStr"/>
+      <c r="AL5" s="2" t="inlineStr"/>
+      <c r="AM5" s="2" t="inlineStr"/>
+      <c r="AN5" s="2" t="inlineStr"/>
+      <c r="AO5" s="2" t="inlineStr">
+        <is>
+          <t>c9eb84ac77729681440eb57a</t>
+        </is>
+      </c>
+      <c r="AP5" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ5" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR5" s="2" t="inlineStr"/>
+      <c r="AS5" s="2" t="inlineStr">
+        <is>
+          <t>1f591b90e9b440b67c36a5eb4472a728985b298e24dc706d0798748c6426b66a</t>
+        </is>
+      </c>
+      <c r="AT5" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU5" s="2" t="inlineStr">
+        <is>
+          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
+        </is>
+      </c>
+      <c r="AV5" s="2" t="inlineStr">
+        <is>
+          <t>Greece passes social media ban for children under 15</t>
+        </is>
+      </c>
+      <c r="AW5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:13:48+08:00</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>-0.378</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxON0pWLThkWllqVTRvcVRMY1NVeUN0UVNxa08tNkRhbzQxTUFlaTZON1BOYkh4bDEtaHB4X2d6dHk3VS1sVDhYMEhhZ0IyMVpjTXJjWVJ3WE9ZTDdWWG9paC1zdHZpbFpFNVZNTk9aYXhQRnRtWVlXRE0tZ2hOaDFmc2RIQUV5aTRBbEJaaDNsWUNxUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>464a7cf6ed8a0d8eb8b7128c</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr"/>
+      <c r="Y6" s="2" t="inlineStr"/>
+      <c r="Z6" s="2" t="inlineStr"/>
+      <c r="AA6" s="2" t="inlineStr"/>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD6" s="2" t="inlineStr"/>
+      <c r="AE6" s="2" t="inlineStr"/>
+      <c r="AF6" s="2" t="inlineStr"/>
+      <c r="AG6" s="2" t="inlineStr"/>
+      <c r="AH6" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI6" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ6" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK6" s="2" t="inlineStr"/>
+      <c r="AL6" s="2" t="inlineStr"/>
+      <c r="AM6" s="2" t="inlineStr"/>
+      <c r="AN6" s="2" t="inlineStr"/>
+      <c r="AO6" s="2" t="inlineStr">
+        <is>
+          <t>2030e51b7ee960a291545c4e</t>
+        </is>
+      </c>
+      <c r="AP6" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ6" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR6" s="2" t="inlineStr"/>
+      <c r="AS6" s="2" t="inlineStr">
+        <is>
+          <t>70d3c8f7cedf509a0d49a31d514c14f40cdbe72f4eeffa852820c7c46d87a158</t>
+        </is>
+      </c>
+      <c r="AT6" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU6" s="2" t="inlineStr"/>
+      <c r="AV6" s="2" t="inlineStr">
+        <is>
+          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
+        </is>
+      </c>
+      <c r="AW6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:02:10+08:00</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.008999999999999999</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQTm1ESVJlZTFrQ2dzbzNrYXVrSWxNSmpkMkNVa2FKMG1WZ0Q5WDJpemo5dnR4Vzl3TXNORk9pa2hWQWZfUDJxS0ljT28xeW9yN2JyODJFRUZDX21QSVM3Yi1SSkZhNE5yOG4zUEJ1V2VGazJ1M3dQVEZVU2tBY0E5N1BmYlgweGJRUHlXRlRUXzh3b3F1dHdnUUJ6UWU?oc=5</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>36137dc64507e498c5a8b4a3</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr"/>
+      <c r="Y7" s="2" t="inlineStr"/>
+      <c r="Z7" s="2" t="inlineStr"/>
+      <c r="AA7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD7" s="2" t="inlineStr"/>
+      <c r="AE7" s="2" t="inlineStr"/>
+      <c r="AF7" s="2" t="inlineStr"/>
+      <c r="AG7" s="2" t="inlineStr"/>
+      <c r="AH7" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI7" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ7" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK7" s="2" t="inlineStr"/>
+      <c r="AL7" s="2" t="inlineStr"/>
+      <c r="AM7" s="2" t="inlineStr"/>
+      <c r="AN7" s="2" t="inlineStr"/>
+      <c r="AO7" s="2" t="inlineStr">
+        <is>
+          <t>db841bab92ab7c46294c18f6</t>
+        </is>
+      </c>
+      <c r="AP7" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ7" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR7" s="2" t="inlineStr"/>
+      <c r="AS7" s="2" t="inlineStr">
+        <is>
+          <t>e75e8c8129bbdb2191154bec165f56eaf1d00c270b682a696164f93458fff26e</t>
+        </is>
+      </c>
+      <c r="AT7" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU7" s="2" t="inlineStr"/>
+      <c r="AV7" s="2" t="inlineStr">
+        <is>
+          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
+        </is>
+      </c>
+      <c r="AW7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:23:56+08:00</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="n">
+        <v>0.011</v>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVW91c2d5NHc5a2FWRXBqWktkSEVlTnQ4dzRiT1dYZzNoNUpjQ3dJMUduVzVScDVBbk9Ock5ERGVIRlJtUEQ4WS1GTnF5dFRjTTRKU3Q0RjVhVW13cGhWbmZVcEhuU0lzQ1VKTmJsbF9saWZQa1ZiSVJJRkVBV3BBejdHeUFPVlhhUDROb0N4YVhzdGdzUFNwV05ZLXk?oc=5</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>785b78480c14b20eb1f594f0</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr"/>
+      <c r="Y8" s="2" t="inlineStr"/>
+      <c r="Z8" s="2" t="inlineStr"/>
+      <c r="AA8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD8" s="2" t="inlineStr"/>
+      <c r="AE8" s="2" t="inlineStr"/>
+      <c r="AF8" s="2" t="inlineStr"/>
+      <c r="AG8" s="2" t="inlineStr"/>
+      <c r="AH8" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI8" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ8" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK8" s="2" t="inlineStr"/>
+      <c r="AL8" s="2" t="inlineStr"/>
+      <c r="AM8" s="2" t="inlineStr"/>
+      <c r="AN8" s="2" t="inlineStr"/>
+      <c r="AO8" s="2" t="inlineStr">
+        <is>
+          <t>5c22badffe5cdc021e3009ee</t>
+        </is>
+      </c>
+      <c r="AP8" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ8" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR8" s="2" t="inlineStr"/>
+      <c r="AS8" s="2" t="inlineStr">
+        <is>
+          <t>6d610b7eb950150470f57c0b234a95303c318c7975b534d2cd2e804370ec4b99</t>
+        </is>
+      </c>
+      <c r="AT8" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU8" s="2" t="inlineStr"/>
+      <c r="AV8" s="2" t="inlineStr">
+        <is>
+          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="AW8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:40:12+08:00</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr"/>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNb3BSbEJKZ3ZoRHcwbURvdW96Sm1iS3I5WXNSOWRTdHZJaC1GVWJYaVpuWHVUVVdwbGE3QlVrdlg3VGFrS0tpX05PM3FDVzFpX1FBcnJGT1dmZmxJQ2V6NTV6Uklsci02dFlvNFl1cUVjeDNmNTFjMFJqdEpBcFlPX3otemVOcVlQckNDT2pfZ2lCODZlQnQyWENyZThHQ3RMcmV3Wnh2ZTREeEJhS3R6a045b20xUXByZlpFTg?oc=5</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Barchart.com</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>802f478a954c806c1d45e5e7</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr"/>
+      <c r="Y9" s="2" t="inlineStr"/>
+      <c r="Z9" s="2" t="inlineStr"/>
+      <c r="AA9" s="2" t="inlineStr"/>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD9" s="2" t="inlineStr"/>
+      <c r="AE9" s="2" t="inlineStr"/>
+      <c r="AF9" s="2" t="inlineStr"/>
+      <c r="AG9" s="2" t="inlineStr"/>
+      <c r="AH9" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI9" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ9" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK9" s="2" t="inlineStr"/>
+      <c r="AL9" s="2" t="inlineStr"/>
+      <c r="AM9" s="2" t="inlineStr"/>
+      <c r="AN9" s="2" t="inlineStr"/>
+      <c r="AO9" s="2" t="inlineStr">
+        <is>
+          <t>7a52a62180c5bc31721f420f</t>
+        </is>
+      </c>
+      <c r="AP9" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ9" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR9" s="2" t="inlineStr"/>
+      <c r="AS9" s="2" t="inlineStr">
+        <is>
+          <t>61557616d68c76cf4c34a0623191d34058d3274ed70d8fc1e86334c98f7433ca</t>
+        </is>
+      </c>
+      <c r="AT9" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU9" s="2" t="inlineStr"/>
+      <c r="AV9" s="2" t="inlineStr">
+        <is>
+          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
+        </is>
+      </c>
+      <c r="AW9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:33:47+08:00</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="2" t="inlineStr"/>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQQXhDOGpZb054SmlrVEdRLUdPNmMxWEhWc3Z1Um9vLWVXZnBrdVJYRWpWSTRaSG1YNC1xcjBnemZlZGEzOGo5NGhvRllmcHRPZm5RMFpQSWdRX1NWRUEzNFpsUzNBclZDem1aT3lYMHpYMHU3NUlSZ3g0dVNBVDJHeDYzMVRHT2FZVEE?oc=5</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>097dc8c2b12cafa6727c9bbb</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr"/>
+      <c r="Y10" s="2" t="inlineStr"/>
+      <c r="Z10" s="2" t="inlineStr"/>
+      <c r="AA10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD10" s="2" t="inlineStr"/>
+      <c r="AE10" s="2" t="inlineStr"/>
+      <c r="AF10" s="2" t="inlineStr"/>
+      <c r="AG10" s="2" t="inlineStr"/>
+      <c r="AH10" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI10" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ10" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK10" s="2" t="inlineStr"/>
+      <c r="AL10" s="2" t="inlineStr"/>
+      <c r="AM10" s="2" t="inlineStr"/>
+      <c r="AN10" s="2" t="inlineStr"/>
+      <c r="AO10" s="2" t="inlineStr">
+        <is>
+          <t>2c57a52603540bb61b3bf4fa</t>
+        </is>
+      </c>
+      <c r="AP10" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ10" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR10" s="2" t="inlineStr"/>
+      <c r="AS10" s="2" t="inlineStr">
+        <is>
+          <t>b36d9804e90e3ff91df4cf736f0b68d3b88ee6026366e5b8f3336a9db6b54010</t>
+        </is>
+      </c>
+      <c r="AT10" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU10" s="2" t="inlineStr"/>
+      <c r="AV10" s="2" t="inlineStr">
+        <is>
+          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="AW10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:15:24+08:00</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr"/>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQYm8yUUVkOEpqVThyY3FUNkxnSEVKT2tzSEpVVnZrci1yYjlKMlZtZHpxeHFYQmlYbzdkRmZzOUl6aGxJeXZNU0x4Ny1QUUtZbnpNc0RfazVMMDA5R0dCdy1nak5DekZMWEVtUTFacWtuWXp2Z2dLTFhsamRjUGRhem94ckVfcHZyalV2ZVVrNnNORnBIdmFPdEYwaVNRcklDbV91RUNyZlo2dGpk?oc=5</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>9abb1549a2b10e0057938029</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr"/>
+      <c r="Y11" s="2" t="inlineStr"/>
+      <c r="Z11" s="2" t="inlineStr"/>
+      <c r="AA11" s="2" t="inlineStr"/>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD11" s="2" t="inlineStr"/>
+      <c r="AE11" s="2" t="inlineStr"/>
+      <c r="AF11" s="2" t="inlineStr"/>
+      <c r="AG11" s="2" t="inlineStr"/>
+      <c r="AH11" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI11" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ11" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK11" s="2" t="inlineStr"/>
+      <c r="AL11" s="2" t="inlineStr"/>
+      <c r="AM11" s="2" t="inlineStr"/>
+      <c r="AN11" s="2" t="inlineStr"/>
+      <c r="AO11" s="2" t="inlineStr">
+        <is>
+          <t>b7806ae6c60efbb0fc8012c9</t>
+        </is>
+      </c>
+      <c r="AP11" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ11" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR11" s="2" t="inlineStr"/>
+      <c r="AS11" s="2" t="inlineStr">
+        <is>
+          <t>7460bf9f6be0b4f2f93f68a081035b7483fdc8361ea4c7c337c2c96d815d773e</t>
+        </is>
+      </c>
+      <c r="AT11" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU11" s="2" t="inlineStr"/>
+      <c r="AV11" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
+        </is>
+      </c>
+      <c r="AW11" s="2" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr"/>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="n">
+        <v>0.079</v>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNd2FTR2VVcnNyQXoyWndTa205TWVDOTZhTTdudU0yWUlPMERDXy0zVnRlSHgtNkJRWGJyTEtqUXl0WHZjeUNKYzNWdk5ZeEtnYmZUWjJKbmVfaVVtOTJ0QlhYOWcxSVVabFBKQUtZVF9wM0M4WUU5RXBQT2JRZXZwd0NOWUd1aUoyUC1rVGxyS1g0V3Jvbm5sU1BxX3Fmdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>726f56e7556fab9bdf9deab7</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr"/>
+      <c r="Y12" s="2" t="inlineStr"/>
+      <c r="Z12" s="2" t="inlineStr"/>
+      <c r="AA12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD12" s="2" t="inlineStr"/>
+      <c r="AE12" s="2" t="inlineStr"/>
+      <c r="AF12" s="2" t="inlineStr"/>
+      <c r="AG12" s="2" t="inlineStr"/>
+      <c r="AH12" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI12" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ12" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK12" s="2" t="inlineStr"/>
+      <c r="AL12" s="2" t="inlineStr"/>
+      <c r="AM12" s="2" t="inlineStr"/>
+      <c r="AN12" s="2" t="inlineStr"/>
+      <c r="AO12" s="2" t="inlineStr">
+        <is>
+          <t>693874aa285dd04e50bb1359</t>
+        </is>
+      </c>
+      <c r="AP12" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ12" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR12" s="2" t="inlineStr"/>
+      <c r="AS12" s="2" t="inlineStr">
+        <is>
+          <t>0517b27ea681c43f5c5a7dc8767c5d0bfb6b5ca885d47a82bbe3196b354fc837</t>
+        </is>
+      </c>
+      <c r="AT12" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU12" s="2" t="inlineStr"/>
+      <c r="AV12" s="2" t="inlineStr">
+        <is>
+          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
+        </is>
+      </c>
+      <c r="AW12" s="2" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:22:37+08:00</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>$Meta Platforms (META.US)$ ...</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="2" t="inlineStr"/>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>0.148</v>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxOMzFhUEtyNm9YNHpPOGRETW0xU0EzXy1PckFJTk9jdFpSbXJIbkVvaVZRNDJMUi16UjRvLVVjMzFoVWZ4aDBFTjZPVmhqem9ndkJWT0hvQzd3alBSVXhTbFB3NVhIVDZTc1pGZzhKNVhGamd5enB1WGJza1dndkF4UUdWa0JfaUhmWjYzVGpBR2RqV2c5Nzk4QVh4bXUwQUJ5VlVNbmhnWTNpVmhiTU85NXlyQUVCYzZ6dF80WWU5RjBRNzBZUjJYcW1NTkUtaEtYSWVOOF91OXdOWmJkOTNGM3pxb1FhVDR0ODhKcWZuc3NqWFQzTXRqbXZWRkZRSmFQaFpJaTJJNEU0NTlHYzFtOG51djlKMzE0NEVyVThtN2Z1OU5tbjMtb3RKMW9rTHdpdmZlazgySXNZdFZra2JLS0lOMmdWbDZOWHVMSVNfcWNfdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Moomoo</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>8463c439cab6cd0ceeed0259</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr"/>
+      <c r="Y13" s="2" t="inlineStr"/>
+      <c r="Z13" s="2" t="inlineStr"/>
+      <c r="AA13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD13" s="2" t="inlineStr"/>
+      <c r="AE13" s="2" t="inlineStr"/>
+      <c r="AF13" s="2" t="inlineStr"/>
+      <c r="AG13" s="2" t="inlineStr"/>
+      <c r="AH13" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI13" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ13" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK13" s="2" t="inlineStr"/>
+      <c r="AL13" s="2" t="inlineStr"/>
+      <c r="AM13" s="2" t="inlineStr"/>
+      <c r="AN13" s="2" t="inlineStr"/>
+      <c r="AO13" s="2" t="inlineStr">
+        <is>
+          <t>50895bc72b56d2d92b44606e</t>
+        </is>
+      </c>
+      <c r="AP13" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ13" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR13" s="2" t="inlineStr"/>
+      <c r="AS13" s="2" t="inlineStr">
+        <is>
+          <t>39a874f75cef45cadda21059624f246da76bcea88d3705c5c291469f18417643</t>
+        </is>
+      </c>
+      <c r="AT13" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU13" s="2" t="inlineStr"/>
+      <c r="AV13" s="2" t="inlineStr">
+        <is>
+          <t>$Meta Platforms (META.US)$ ...</t>
+        </is>
+      </c>
+      <c r="AW13" s="2" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T16:01:04+08:00</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>小摩上調Meta目標價至940美元</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>0.619</v>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/news/5330363</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>c0a62dd94e77e5e7c175baf7</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr"/>
+      <c r="Y14" s="2" t="inlineStr"/>
+      <c r="Z14" s="2" t="inlineStr"/>
+      <c r="AA14" s="2" t="inlineStr"/>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD14" s="2" t="inlineStr"/>
+      <c r="AE14" s="2" t="inlineStr"/>
+      <c r="AF14" s="2" t="inlineStr"/>
+      <c r="AG14" s="2" t="inlineStr"/>
+      <c r="AH14" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI14" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ14" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK14" s="2" t="inlineStr"/>
+      <c r="AL14" s="2" t="inlineStr"/>
+      <c r="AM14" s="2" t="inlineStr"/>
+      <c r="AN14" s="2" t="inlineStr"/>
+      <c r="AO14" s="2" t="inlineStr">
+        <is>
+          <t>f241bb1e8daac06e5ebfd5dd</t>
+        </is>
+      </c>
+      <c r="AP14" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ14" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR14" s="2" t="inlineStr"/>
+      <c r="AS14" s="2" t="inlineStr">
+        <is>
+          <t>3fb9a23409e8708ea25ee8cb1bc2c57d982f0b2f9aece44cf25ef07e40b312e8</t>
+        </is>
+      </c>
+      <c r="AT14" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU14" s="2" t="inlineStr">
+        <is>
+          <t>小摩上調Meta目標價至940美元</t>
+        </is>
+      </c>
+      <c r="AV14" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan raised its Meta target price to $940</t>
+        </is>
+      </c>
+      <c r="AW14" s="2" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:48:55+08:00</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr"/>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>0.724</v>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2725612</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>8276af8c1e2d6a8b1be57709</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr"/>
+      <c r="Y15" s="2" t="inlineStr"/>
+      <c r="Z15" s="2" t="inlineStr"/>
+      <c r="AA15" s="2" t="inlineStr"/>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD15" s="2" t="inlineStr"/>
+      <c r="AE15" s="2" t="inlineStr"/>
+      <c r="AF15" s="2" t="inlineStr"/>
+      <c r="AG15" s="2" t="inlineStr"/>
+      <c r="AH15" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI15" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ15" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK15" s="2" t="inlineStr"/>
+      <c r="AL15" s="2" t="inlineStr"/>
+      <c r="AM15" s="2" t="inlineStr"/>
+      <c r="AN15" s="2" t="inlineStr"/>
+      <c r="AO15" s="2" t="inlineStr">
+        <is>
+          <t>062e54352538d735417bc00a</t>
+        </is>
+      </c>
+      <c r="AP15" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ15" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR15" s="2" t="inlineStr"/>
+      <c r="AS15" s="2" t="inlineStr">
+        <is>
+          <t>4b5ef37f6c305b434f4c1c87831cc70b581ac080fa1eb75cf03d769479d206b7</t>
+        </is>
+      </c>
+      <c r="AT15" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU15" s="2" t="inlineStr">
+        <is>
+          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
+        </is>
+      </c>
+      <c r="AV15" s="2" t="inlineStr">
+        <is>
+          <t>"The Wolf of Wall Street" Ackman: If the war and inflation cool down, 2027 will be an amazing year</t>
+        </is>
+      </c>
+      <c r="AW15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:13:19+08:00</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="2" t="inlineStr"/>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>0.899</v>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS0s3YXJsQVNHNFBJSGVFUVMtOWwwVlE5UzN2c2V2OFVKOU1UZHJfT0c0Y1dXUHFWdFI0R2JBcGg3ZzJBUmZBSmF6ZHBvS3NyMWp0NklKQWxiTFFYZzRGSmNicFZzTFk0X0lrcFpWZ0VIcFd1Zi1UUVpMX2NlYzJmVEUxTVJrODRzblZvX25IRV9tajluWlBJ?oc=5</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>5774c207e5b4837ece36440d</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr"/>
+      <c r="Y16" s="2" t="inlineStr"/>
+      <c r="Z16" s="2" t="inlineStr"/>
+      <c r="AA16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD16" s="2" t="inlineStr"/>
+      <c r="AE16" s="2" t="inlineStr"/>
+      <c r="AF16" s="2" t="inlineStr"/>
+      <c r="AG16" s="2" t="inlineStr"/>
+      <c r="AH16" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI16" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ16" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK16" s="2" t="inlineStr"/>
+      <c r="AL16" s="2" t="inlineStr"/>
+      <c r="AM16" s="2" t="inlineStr"/>
+      <c r="AN16" s="2" t="inlineStr"/>
+      <c r="AO16" s="2" t="inlineStr">
+        <is>
+          <t>2ed2364af3d9acea1114881a</t>
+        </is>
+      </c>
+      <c r="AP16" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ16" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR16" s="2" t="inlineStr"/>
+      <c r="AS16" s="2" t="inlineStr">
+        <is>
+          <t>29d466f90bfdbdf0f7a04f87c9e7bf26725f4409800afedde98bde36f1864b93</t>
+        </is>
+      </c>
+      <c r="AT16" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU16" s="2" t="inlineStr"/>
+      <c r="AV16" s="2" t="inlineStr">
+        <is>
+          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
+        </is>
+      </c>
+      <c r="AW16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:07:13+08:00</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
+      <c r="I17" s="2" t="inlineStr"/>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>待補分析</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>0.9330000000000001</v>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOU5uNjZ6MTZvd2dkQlFWUFJ2VW9RdGNmLS12R0x2UDlmMC1jRzBpWmFWNGwzcXFySjFBUzd1V1JSeU5FNGVYdDQzZ1hod1g5SmVOZUw2eTZKTEt0QnpFT0JONTc5eEhHUlNUTHlhMnd6TmF2eW9JX1FzZElGZzRsak1MdVFER2RYVDVJOHVVSnZLSXVzWUNBOFVoU0JfUF9z?oc=5</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>1662077625e20e4158c6d6d9</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr"/>
+      <c r="Y17" s="2" t="inlineStr"/>
+      <c r="Z17" s="2" t="inlineStr"/>
+      <c r="AA17" s="2" t="inlineStr"/>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>QUOTA_PENDING</t>
+        </is>
+      </c>
+      <c r="AD17" s="2" t="inlineStr"/>
+      <c r="AE17" s="2" t="inlineStr"/>
+      <c r="AF17" s="2" t="inlineStr"/>
+      <c r="AG17" s="2" t="inlineStr"/>
+      <c r="AH17" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AI17" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ17" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK17" s="2" t="inlineStr"/>
+      <c r="AL17" s="2" t="inlineStr"/>
+      <c r="AM17" s="2" t="inlineStr"/>
+      <c r="AN17" s="2" t="inlineStr"/>
+      <c r="AO17" s="2" t="inlineStr">
+        <is>
+          <t>27ae0e4f67d27857be0e98ca</t>
+        </is>
+      </c>
+      <c r="AP17" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ17" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR17" s="2" t="inlineStr"/>
+      <c r="AS17" s="2" t="inlineStr">
+        <is>
+          <t>8d2bf44846475f369f3134681a465fafc51dc63ac9d90ebf8bca03c554f5390f</t>
+        </is>
+      </c>
+      <c r="AT17" s="2" t="inlineStr">
+        <is>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+        </is>
+      </c>
+      <c r="AU17" s="2" t="inlineStr"/>
+      <c r="AV17" s="2" t="inlineStr">
+        <is>
+          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
+        </is>
+      </c>
+      <c r="AW17" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AT1"/>
+  <autoFilter ref="A1:AW17"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16971,7 +22597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W2"/>
+  <dimension ref="A1:W3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -17119,7 +22745,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -17157,37 +22783,37 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N2" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="O2" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="P2" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -17196,21 +22822,114 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
       <c r="U2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W2" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R3" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W2"/>
+  <autoFilter ref="A1:W3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/news_daily/2026-10-23.xlsx
+++ b/news_daily/2026-10-23.xlsx
@@ -16,9 +16,9 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'完整新聞'!$A$1:$AW$51</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'主要負面事件'!$A$1:$AW$18</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$AW$32</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$AW$17</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$W$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'待人工覆核'!$A$1:$AW$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'待補分析'!$A$1:$AW$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'執行紀錄'!$A$1:$W$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -943,12 +943,12 @@
       <c r="AR2" s="2" t="inlineStr"/>
       <c r="AS2" s="2" t="inlineStr">
         <is>
-          <t>59d0b070ec5a7add0271c3f6ec92358a64eeb2efeec9e4757fb6b90cf9138ea5</t>
+          <t>1a98cdbca58ab019d9282ae07fe1105d0d3727cb89d10bdec72a3b1c9a73b6c6</t>
         </is>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr"/>
@@ -1122,12 +1122,12 @@
       <c r="AR3" s="2" t="inlineStr"/>
       <c r="AS3" s="2" t="inlineStr">
         <is>
-          <t>43e900bf3d1ed6beee750787e09d914b073f9631b302da70437abfd67d31c886</t>
+          <t>3105206721b31ed41e0dbf793d7370d073ecbb3f058416614c21f9115576dccc</t>
         </is>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr"/>
@@ -1325,12 +1325,12 @@
       <c r="AR4" s="2" t="inlineStr"/>
       <c r="AS4" s="2" t="inlineStr">
         <is>
-          <t>65bc54e92abf071a7016f9c0a1f2b7eb8c1c45e55ed56e0b297d04624170137d</t>
+          <t>74f36f7ff784fc6dd497785eeb98a4085a2f388428b2056d6cece7e93496127a</t>
         </is>
       </c>
       <c r="AT4" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU4" s="2" t="inlineStr"/>
@@ -1524,12 +1524,12 @@
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>9c6e12fb3f4675cdd525f4cd8e6728ff928a7a2fe91742feeb2a813c5ad9f3ee</t>
+          <t>bdd24ef76a4546a256b32abb28cf5302a1284bf39f2af20abba1b36fa21f18bb</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr"/>
@@ -1703,12 +1703,12 @@
       <c r="AR6" s="2" t="inlineStr"/>
       <c r="AS6" s="2" t="inlineStr">
         <is>
-          <t>ba85b94389e2d00dfe1eea9ca4ec4c947d71941074fab84daea46686c82f8313</t>
+          <t>4d6c8b7e7d6c2da825bd038a8178b6c9987a58255a01270f95766656ce678a43</t>
         </is>
       </c>
       <c r="AT6" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU6" s="2" t="inlineStr"/>
@@ -1906,12 +1906,12 @@
       <c r="AR7" s="4" t="inlineStr"/>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>4a7b855761fde685d2a95337a008078bd78b73e253b900aa8cc065fb389b2d9e</t>
+          <t>31ac25c21d4bebfbab59df4480f0ddb4c09ea712500f7bdf0468bebdce0a3dfb</t>
         </is>
       </c>
       <c r="AT7" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU7" s="4" t="inlineStr"/>
@@ -2085,12 +2085,12 @@
       <c r="AR8" s="2" t="inlineStr"/>
       <c r="AS8" s="2" t="inlineStr">
         <is>
-          <t>fc0cc2efc8f48a91fffa090920578ebcb4a29fbf2bcc80aa2b69c926176021b6</t>
+          <t>695fb63e1bb75f4694515d67896cc171598cabd881c54d393386eb4ba33be88d</t>
         </is>
       </c>
       <c r="AT8" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU8" s="2" t="inlineStr"/>
@@ -2288,12 +2288,12 @@
       <c r="AR9" s="3" t="inlineStr"/>
       <c r="AS9" s="3" t="inlineStr">
         <is>
-          <t>8e031f92cd74fcfc61bfcf781bcffe51843c9ee2e2e39e51e5453f8f45a99e44</t>
+          <t>9a8b6db6b9fb5ef6fbca7c90bc14efb93749f3f82f0d51ff32cc8e02991479f8</t>
         </is>
       </c>
       <c r="AT9" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU9" s="3" t="inlineStr"/>
@@ -2491,12 +2491,12 @@
       <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>ada338c05fef387e2d7ce197306651f3dbb214c69ecc9866d7a150a731a5a099</t>
+          <t>7ae45cdb4433a4a84f6cef6cb6bc376cd7a669f325e1703a3f7005a0c8de4359</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr"/>
@@ -2670,12 +2670,12 @@
       <c r="AR11" s="2" t="inlineStr"/>
       <c r="AS11" s="2" t="inlineStr">
         <is>
-          <t>21c491be7cb3b2def9edabf23709b08a655e53493a14c78ec977d71204e639af</t>
+          <t>b4f5e9f012bc989693d27c1622d2ebc0f82bc3027570c6eb88919f68612e818b</t>
         </is>
       </c>
       <c r="AT11" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU11" s="2" t="inlineStr"/>
@@ -2869,12 +2869,12 @@
       <c r="AR12" s="3" t="inlineStr"/>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>45f2d58b595adcc6f0026cdea120b6a1f1ec508846f65f6dcdd49a6445c6a164</t>
+          <t>d2d328d3d98076805e6f6b9cb8237e2e9e200e6d9bb5e0fa882c8acf35b97fee</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr"/>
@@ -3052,12 +3052,12 @@
       </c>
       <c r="AS13" s="2" t="inlineStr">
         <is>
-          <t>7fdf39cffff89cb42bdf631c4afa26ea2bb9a9ee2e904623a9711791f419b039</t>
+          <t>f4eb6c4702ab24462aa85a061a50c385a20fa2649060066185f80a5055aff49c</t>
         </is>
       </c>
       <c r="AT13" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU13" s="2" t="inlineStr"/>
@@ -3259,12 +3259,12 @@
       <c r="AR14" s="4" t="inlineStr"/>
       <c r="AS14" s="4" t="inlineStr">
         <is>
-          <t>6293669f1b7b8f8c8534949a5eb967ea7dd751e6cbfdc992fc63a513c3acdf57</t>
+          <t>3f2494e218bc0e1eecba3fd070542744a25a1d2d49b9957593ed742cdfc67af3</t>
         </is>
       </c>
       <c r="AT14" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU14" s="4" t="inlineStr"/>
@@ -3466,12 +3466,12 @@
       <c r="AR15" s="4" t="inlineStr"/>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t>d46ed09b38ab6b5b8ad19b1eecd0637350a911055fa23a5ebad356093eb73fc4</t>
+          <t>ee60dbb626b10b42906c52973342d901ef7b3d71440b43fc63cd28043abbe400</t>
         </is>
       </c>
       <c r="AT15" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU15" s="4" t="inlineStr"/>
@@ -3669,12 +3669,12 @@
       <c r="AR16" s="4" t="inlineStr"/>
       <c r="AS16" s="4" t="inlineStr">
         <is>
-          <t>5648c46d373ce56dbafbf849d726dd446b7e6d674077c822ffadaa589c9222da</t>
+          <t>165aaf928e1ab154225c3474a29df9f97a5300f7b263bdc6622b830e38a6a440</t>
         </is>
       </c>
       <c r="AT16" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU16" s="4" t="inlineStr"/>
@@ -3876,12 +3876,12 @@
       <c r="AR17" s="4" t="inlineStr"/>
       <c r="AS17" s="4" t="inlineStr">
         <is>
-          <t>fc9dd5bd08cceed3630840f06300aa5cad60f28e7fb03a3a1302cae6f3a27c56</t>
+          <t>858cacb37eb67b542539e06c9db58dd953174c1112c39812f19141d474956f9b</t>
         </is>
       </c>
       <c r="AT17" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU17" s="4" t="inlineStr"/>
@@ -4055,12 +4055,12 @@
       <c r="AR18" s="2" t="inlineStr"/>
       <c r="AS18" s="2" t="inlineStr">
         <is>
-          <t>62e0cb1e4e902fe66bee49a5e5e09c6c98815677978087f2f8b17feed7e61d5c</t>
+          <t>2ef7099c2881d6f63f62a0fea8f75b530f8512ca5179af0d55955a14ec110dbe</t>
         </is>
       </c>
       <c r="AT18" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU18" s="2" t="inlineStr"/>
@@ -4238,12 +4238,12 @@
       <c r="AR19" s="2" t="inlineStr"/>
       <c r="AS19" s="2" t="inlineStr">
         <is>
-          <t>f1631fdd74d9fde1bc83f4593243a4786b4bcd2a17a5959906712c24fc2b45b4</t>
+          <t>e748226659831de0bb4541d1da055931db5b8a4e6d4d94283f744d7443920005</t>
         </is>
       </c>
       <c r="AT19" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU19" s="2" t="inlineStr"/>
@@ -4421,12 +4421,12 @@
       <c r="AR20" s="2" t="inlineStr"/>
       <c r="AS20" s="2" t="inlineStr">
         <is>
-          <t>d4aa2f7e089cc5c99dfb6bf4481e563cb84e94d302da081f736f9d2798c5eab9</t>
+          <t>95c7c2a6b8c17b4c70e3b89273c3388b6d6ba20b97f994efaef9bf6d3a42bbf0</t>
         </is>
       </c>
       <c r="AT20" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU20" s="2" t="inlineStr"/>
@@ -4628,12 +4628,12 @@
       <c r="AR21" s="3" t="inlineStr"/>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>877cf279a144f268174ffce46ef0687d7153ebb6c891edad1063064fd98a0fd1</t>
+          <t>cc5e4ca2634ed6b55f67ad0b7f897205979738c904cd55e93372f6ca8ba983df</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr"/>
@@ -4847,12 +4847,12 @@
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>23af1c5424a692b58f6f8424d4d7db4114fd03d481f315e02e607593225853ac</t>
+          <t>0c54163024f73530fe8a69871bef0aa1ec59c0fcaec0fd0089d1f707e67bd6cb</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr"/>
@@ -5054,12 +5054,12 @@
       </c>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>e326e2866abb147a3fb34777e0bc874645fe44846987176be28da779dc413ec3</t>
+          <t>88924c348bff62bff0ac8702762fc6d7b14f97483fccaf0c8739797c7176bb4f</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr"/>
@@ -5261,12 +5261,12 @@
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>01beb5ae9c384c5411ec04c16cb6a5646e5b0cca885791a4e83159dc7625ac6e</t>
+          <t>f0d840da549481f47e5ec484f645ac865679395b49dae53f0b418001a63b3846</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr"/>
@@ -5464,12 +5464,12 @@
       <c r="AR25" s="3" t="inlineStr"/>
       <c r="AS25" s="3" t="inlineStr">
         <is>
-          <t>837ee79400109c77c83c3651332f843b9f4e826d5ea05520c8917c212e482f0e</t>
+          <t>96fe9c4aea452cafb38eb9b316863b8b873d4bac780bc7626045f065fb864e0c</t>
         </is>
       </c>
       <c r="AT25" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU25" s="3" t="inlineStr"/>
@@ -5667,12 +5667,12 @@
       <c r="AR26" s="3" t="inlineStr"/>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>9b64ccbf3b8eec2573fa50d9326de159a3b54a791d0866dc7b95f11253cb093a</t>
+          <t>d0c89ac0978ce4a4da75684fb2fc8361eed3370fa3e36faeffd7772447123b13</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr"/>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="AS27" s="3" t="inlineStr">
         <is>
-          <t>072fda62469150c62037ef694fb92f86f206372bc347cbabaf4f9ce7a5e4ae8a</t>
+          <t>101eb1810e77321e67644d25789ae03393ad85e6b49c0c0e22d2fbaf0b2d4572</t>
         </is>
       </c>
       <c r="AT27" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU27" s="3" t="inlineStr"/>
@@ -6045,12 +6045,12 @@
       <c r="AR28" s="2" t="inlineStr"/>
       <c r="AS28" s="2" t="inlineStr">
         <is>
-          <t>c2b733a875d9b2af7cd5b7f6fec0c25c1dad89c64a7f34579fc58492f51de623</t>
+          <t>636ff7b98c973316542530b9db36c941119ed7b3d4e0a29ff671af38868cf549</t>
         </is>
       </c>
       <c r="AT28" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU28" s="2" t="inlineStr"/>
@@ -6240,12 +6240,12 @@
       <c r="AR29" s="3" t="inlineStr"/>
       <c r="AS29" s="3" t="inlineStr">
         <is>
-          <t>4a1bb79f89b6aab12ef4224737cdbe24df29acad6d217dc6e571fdaa8a3ac6de</t>
+          <t>66f86d7d3aa8fc873a061c7ceda00a72f77e5f42e9f1c60b74e72af9e961e92a</t>
         </is>
       </c>
       <c r="AT29" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU29" s="3" t="inlineStr"/>
@@ -6415,12 +6415,12 @@
       <c r="AR30" s="2" t="inlineStr"/>
       <c r="AS30" s="2" t="inlineStr">
         <is>
-          <t>3b06ef9bf135012a500ef20e1ec38242ff4873bafe105a625576beace15327e0</t>
+          <t>95e7d13ed0dbe46f108916eb1a8e616902b0379935ad571ba5596aff71b5d813</t>
         </is>
       </c>
       <c r="AT30" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU30" s="2" t="inlineStr"/>
@@ -6594,12 +6594,12 @@
       <c r="AR31" s="2" t="inlineStr"/>
       <c r="AS31" s="2" t="inlineStr">
         <is>
-          <t>5ec281d9984561f238970a22d7f6d429bcdacf1346d40dedbfead923c141b184</t>
+          <t>5c6e5e1338211ad9ff12890c09dea50568a68fb8a73cb5671e7f1edfdeae2c60</t>
         </is>
       </c>
       <c r="AT31" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU31" s="2" t="inlineStr"/>
@@ -6769,12 +6769,12 @@
       <c r="AR32" s="2" t="inlineStr"/>
       <c r="AS32" s="2" t="inlineStr">
         <is>
-          <t>2fa7566bd35239182d98b2bd93680cee99ad9b293f1fd8b19fe33e8fcdceacaa</t>
+          <t>13b14efb0652327cd3fa331170283475c7ba9b53bd3863784fda7f0121dd7e28</t>
         </is>
       </c>
       <c r="AT32" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU32" s="2" t="inlineStr"/>
@@ -6932,12 +6932,12 @@
       <c r="AR33" s="2" t="inlineStr"/>
       <c r="AS33" s="2" t="inlineStr">
         <is>
-          <t>0e5c70db7b6b4f316d00fc7eb40f668750b8ed08e472edc429651639c5b38f20</t>
+          <t>a0d00b59e76935d81428a91f3258118f0cfecaecf3ded0e60172850efedbba04</t>
         </is>
       </c>
       <c r="AT33" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU33" s="2" t="inlineStr"/>
@@ -7107,12 +7107,12 @@
       <c r="AR34" s="2" t="inlineStr"/>
       <c r="AS34" s="2" t="inlineStr">
         <is>
-          <t>4784da4cbce731f9ee8a50b210b9ecb9a9c70b89799faeeac11bdd634f63105c</t>
+          <t>f16e643da6decfa9cfa028489943f1f58dead9ac1463b0c7049f61a6a5091721</t>
         </is>
       </c>
       <c r="AT34" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU34" s="2" t="inlineStr"/>
@@ -7178,8 +7178,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O35" s="2" t="n">
-        <v>-0.954</v>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>'-0.954</t>
+        </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
@@ -7250,11 +7252,15 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK35" s="2" t="n">
-        <v>1449</v>
-      </c>
-      <c r="AL35" s="2" t="n">
-        <v>86</v>
+      <c r="AK35" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AL35" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="AM35" s="2" t="inlineStr"/>
       <c r="AN35" s="2" t="inlineStr"/>
@@ -7276,12 +7282,12 @@
       <c r="AR35" s="2" t="inlineStr"/>
       <c r="AS35" s="2" t="inlineStr">
         <is>
-          <t>5561c485d0bf6a8f7f3c02db776ad98b37ba9deae1b4991a83a6428d34222d39</t>
+          <t>3b3ecec0bb0d4667d56b8eca57711b8f7fc32ca367c1d3a3c0daf724e7aa6deb</t>
         </is>
       </c>
       <c r="AT35" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU35" s="2" t="inlineStr"/>
@@ -7323,18 +7329,22 @@
           <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 的股價下跌並未顯示任何明確的信用風險事件。</t>
+        </is>
+      </c>
       <c r="H36" s="2" t="inlineStr"/>
       <c r="I36" s="2" t="inlineStr"/>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
@@ -7347,8 +7357,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O36" s="2" t="n">
-        <v>-0.9330000000000001</v>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>'-0.933</t>
+        </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
@@ -7357,7 +7369,11 @@
       </c>
       <c r="Q36" s="2" t="inlineStr"/>
       <c r="R36" s="2" t="inlineStr"/>
-      <c r="S36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -7385,16 +7401,24 @@
       <c r="AB36" s="2" t="inlineStr"/>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD36" s="2" t="inlineStr"/>
-      <c r="AE36" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF36" s="2" t="inlineStr"/>
       <c r="AG36" s="2" t="inlineStr"/>
       <c r="AH36" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI36" s="2" t="inlineStr">
@@ -7407,8 +7431,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK36" s="2" t="inlineStr"/>
-      <c r="AL36" s="2" t="inlineStr"/>
+      <c r="AK36" s="2" t="n">
+        <v>1448</v>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>88</v>
+      </c>
       <c r="AM36" s="2" t="inlineStr"/>
       <c r="AN36" s="2" t="inlineStr"/>
       <c r="AO36" s="2" t="inlineStr">
@@ -7429,12 +7457,12 @@
       <c r="AR36" s="2" t="inlineStr"/>
       <c r="AS36" s="2" t="inlineStr">
         <is>
-          <t>703f213218315ca169df93ed957d57b06b6c1dd9d90f95dcae08448b5366a4d2</t>
+          <t>e80328332c4f74df8e9629757ce5aca0978b96338cf043ff9bf41b5a74327514</t>
         </is>
       </c>
       <c r="AT36" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU36" s="2" t="inlineStr"/>
@@ -7476,18 +7504,22 @@
           <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 相關新聞未提及任何信用風險事件，無法判斷是否存在違約或其他信用事件。</t>
+        </is>
+      </c>
       <c r="H37" s="2" t="inlineStr"/>
       <c r="I37" s="2" t="inlineStr"/>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
@@ -7500,8 +7532,10 @@
           <t>方法一</t>
         </is>
       </c>
-      <c r="O37" s="2" t="n">
-        <v>-0.873</v>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>'-0.873</t>
+        </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
@@ -7514,7 +7548,11 @@
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr"/>
-      <c r="S37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -7542,16 +7580,24 @@
       <c r="AB37" s="2" t="inlineStr"/>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD37" s="2" t="inlineStr"/>
-      <c r="AE37" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF37" s="2" t="inlineStr"/>
       <c r="AG37" s="2" t="inlineStr"/>
       <c r="AH37" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI37" s="2" t="inlineStr">
@@ -7564,8 +7610,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK37" s="2" t="inlineStr"/>
-      <c r="AL37" s="2" t="inlineStr"/>
+      <c r="AK37" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="AL37" s="2" t="n">
+        <v>94</v>
+      </c>
       <c r="AM37" s="2" t="inlineStr"/>
       <c r="AN37" s="2" t="inlineStr"/>
       <c r="AO37" s="2" t="inlineStr">
@@ -7586,12 +7636,12 @@
       <c r="AR37" s="2" t="inlineStr"/>
       <c r="AS37" s="2" t="inlineStr">
         <is>
-          <t>3b9ae9feaec50aeeb331e95a5ee2a1e3c8322512f70ac97854f13f8a8a230dbf</t>
+          <t>96228df4d354588d61a5e4fee402dae26f2644c637ffd31d091328d77cef2bdb</t>
         </is>
       </c>
       <c r="AT37" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU37" s="2" t="inlineStr">
@@ -7637,18 +7687,22 @@
           <t>巴西總統指控Meta操縱大選</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選，但未涉及任何信用風險或債務違約訊息。</t>
+        </is>
+      </c>
       <c r="H38" s="2" t="inlineStr"/>
       <c r="I38" s="2" t="inlineStr"/>
       <c r="J38" s="2" t="inlineStr"/>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
@@ -7661,8 +7715,10 @@
           <t>方法一</t>
         </is>
       </c>
-      <c r="O38" s="2" t="n">
-        <v>-0.824</v>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>'-0.824</t>
+        </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
         <is>
@@ -7671,7 +7727,11 @@
       </c>
       <c r="Q38" s="2" t="inlineStr"/>
       <c r="R38" s="2" t="inlineStr"/>
-      <c r="S38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -7699,16 +7759,24 @@
       <c r="AB38" s="2" t="inlineStr"/>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD38" s="2" t="inlineStr"/>
-      <c r="AE38" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF38" s="2" t="inlineStr"/>
       <c r="AG38" s="2" t="inlineStr"/>
       <c r="AH38" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI38" s="2" t="inlineStr">
@@ -7721,8 +7789,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK38" s="2" t="inlineStr"/>
-      <c r="AL38" s="2" t="inlineStr"/>
+      <c r="AK38" s="2" t="n">
+        <v>1442</v>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>174</v>
+      </c>
       <c r="AM38" s="2" t="inlineStr"/>
       <c r="AN38" s="2" t="inlineStr"/>
       <c r="AO38" s="2" t="inlineStr">
@@ -7743,12 +7815,12 @@
       <c r="AR38" s="2" t="inlineStr"/>
       <c r="AS38" s="2" t="inlineStr">
         <is>
-          <t>1f1b7d07ae6f5f91e714914b3b662be882027be3a6ebc1733cfc29a4f725c9d0</t>
+          <t>da1d8d50a8880e36b4c6f7fe3437a374f0f1c55828e104ac239cb9cfd44548d5</t>
         </is>
       </c>
       <c r="AT38" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU38" s="2" t="inlineStr">
@@ -7794,18 +7866,22 @@
           <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 目前沒有任何明確的違約或信用風險事件。</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
       <c r="I39" s="2" t="inlineStr"/>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
@@ -7818,8 +7894,10 @@
           <t>方法一</t>
         </is>
       </c>
-      <c r="O39" s="2" t="n">
-        <v>-0.745</v>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>'-0.745</t>
+        </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
@@ -7828,7 +7906,11 @@
       </c>
       <c r="Q39" s="2" t="inlineStr"/>
       <c r="R39" s="2" t="inlineStr"/>
-      <c r="S39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -7856,16 +7938,24 @@
       <c r="AB39" s="2" t="inlineStr"/>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD39" s="2" t="inlineStr"/>
-      <c r="AE39" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF39" s="2" t="inlineStr"/>
       <c r="AG39" s="2" t="inlineStr"/>
       <c r="AH39" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI39" s="2" t="inlineStr">
@@ -7878,8 +7968,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK39" s="2" t="inlineStr"/>
-      <c r="AL39" s="2" t="inlineStr"/>
+      <c r="AK39" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AL39" s="2" t="n">
+        <v>78</v>
+      </c>
       <c r="AM39" s="2" t="inlineStr"/>
       <c r="AN39" s="2" t="inlineStr"/>
       <c r="AO39" s="2" t="inlineStr">
@@ -7900,12 +7994,12 @@
       <c r="AR39" s="2" t="inlineStr"/>
       <c r="AS39" s="2" t="inlineStr">
         <is>
-          <t>1f591b90e9b440b67c36a5eb4472a728985b298e24dc706d0798748c6426b66a</t>
+          <t>9a4374bb2beaeb0b1ed12ac500e3d948f565b7eee6a6daecbeaefe1dd6133486</t>
         </is>
       </c>
       <c r="AT39" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU39" s="2" t="inlineStr">
@@ -7951,18 +8045,22 @@
           <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠資訊顯示 Meta Platforms 相關的信用風險事件。</t>
+        </is>
+      </c>
       <c r="H40" s="2" t="inlineStr"/>
       <c r="I40" s="2" t="inlineStr"/>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
@@ -7975,8 +8073,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O40" s="2" t="n">
-        <v>-0.378</v>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>'-0.378</t>
+        </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
@@ -7985,7 +8085,11 @@
       </c>
       <c r="Q40" s="2" t="inlineStr"/>
       <c r="R40" s="2" t="inlineStr"/>
-      <c r="S40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -8013,16 +8117,24 @@
       <c r="AB40" s="2" t="inlineStr"/>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD40" s="2" t="inlineStr"/>
-      <c r="AE40" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF40" s="2" t="inlineStr"/>
       <c r="AG40" s="2" t="inlineStr"/>
       <c r="AH40" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI40" s="2" t="inlineStr">
@@ -8035,8 +8147,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK40" s="2" t="inlineStr"/>
-      <c r="AL40" s="2" t="inlineStr"/>
+      <c r="AK40" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="AL40" s="2" t="n">
+        <v>85</v>
+      </c>
       <c r="AM40" s="2" t="inlineStr"/>
       <c r="AN40" s="2" t="inlineStr"/>
       <c r="AO40" s="2" t="inlineStr">
@@ -8057,12 +8173,12 @@
       <c r="AR40" s="2" t="inlineStr"/>
       <c r="AS40" s="2" t="inlineStr">
         <is>
-          <t>70d3c8f7cedf509a0d49a31d514c14f40cdbe72f4eeffa852820c7c46d87a158</t>
+          <t>21528d2dd40eb81f0d101c585a9eb53e9dd572004397a890ae760bf47f3ae0c9</t>
         </is>
       </c>
       <c r="AT40" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU40" s="2" t="inlineStr"/>
@@ -8104,18 +8220,22 @@
           <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>無足夠資訊表明 Meta Platforms 之信用風險事件。</t>
+        </is>
+      </c>
       <c r="H41" s="2" t="inlineStr"/>
       <c r="I41" s="2" t="inlineStr"/>
       <c r="J41" s="2" t="inlineStr"/>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
@@ -8128,8 +8248,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O41" s="2" t="n">
-        <v>0.008999999999999999</v>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.009</t>
+        </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
@@ -8138,7 +8260,11 @@
       </c>
       <c r="Q41" s="2" t="inlineStr"/>
       <c r="R41" s="2" t="inlineStr"/>
-      <c r="S41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -8166,16 +8292,24 @@
       <c r="AB41" s="2" t="inlineStr"/>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD41" s="2" t="inlineStr"/>
-      <c r="AE41" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF41" s="2" t="inlineStr"/>
       <c r="AG41" s="2" t="inlineStr"/>
       <c r="AH41" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI41" s="2" t="inlineStr">
@@ -8188,8 +8322,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK41" s="2" t="inlineStr"/>
-      <c r="AL41" s="2" t="inlineStr"/>
+      <c r="AK41" s="2" t="n">
+        <v>1446</v>
+      </c>
+      <c r="AL41" s="2" t="n">
+        <v>76</v>
+      </c>
       <c r="AM41" s="2" t="inlineStr"/>
       <c r="AN41" s="2" t="inlineStr"/>
       <c r="AO41" s="2" t="inlineStr">
@@ -8210,12 +8348,12 @@
       <c r="AR41" s="2" t="inlineStr"/>
       <c r="AS41" s="2" t="inlineStr">
         <is>
-          <t>e75e8c8129bbdb2191154bec165f56eaf1d00c270b682a696164f93458fff26e</t>
+          <t>db65943cb30691cbfcfe6b2a7090d142ae715f7a8ef19d34e1151ebf7ddcd53a</t>
         </is>
       </c>
       <c r="AT41" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU41" s="2" t="inlineStr"/>
@@ -8257,18 +8395,22 @@
           <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 相關的信用風險事件。</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr"/>
       <c r="I42" s="2" t="inlineStr"/>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
@@ -8281,8 +8423,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O42" s="2" t="n">
-        <v>0.011</v>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
@@ -8291,7 +8435,11 @@
       </c>
       <c r="Q42" s="2" t="inlineStr"/>
       <c r="R42" s="2" t="inlineStr"/>
-      <c r="S42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -8319,16 +8467,24 @@
       <c r="AB42" s="2" t="inlineStr"/>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD42" s="2" t="inlineStr"/>
-      <c r="AE42" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF42" s="2" t="inlineStr"/>
       <c r="AG42" s="2" t="inlineStr"/>
       <c r="AH42" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI42" s="2" t="inlineStr">
@@ -8341,8 +8497,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK42" s="2" t="inlineStr"/>
-      <c r="AL42" s="2" t="inlineStr"/>
+      <c r="AK42" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>87</v>
+      </c>
       <c r="AM42" s="2" t="inlineStr"/>
       <c r="AN42" s="2" t="inlineStr"/>
       <c r="AO42" s="2" t="inlineStr">
@@ -8363,12 +8523,12 @@
       <c r="AR42" s="2" t="inlineStr"/>
       <c r="AS42" s="2" t="inlineStr">
         <is>
-          <t>6d610b7eb950150470f57c0b234a95303c318c7975b534d2cd2e804370ec4b99</t>
+          <t>3d2f7d8d1cc6978ee5580259eb22d769f60414435b4966fccc4a7efcfab3006b</t>
         </is>
       </c>
       <c r="AT42" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU42" s="2" t="inlineStr"/>
@@ -8410,18 +8570,22 @@
           <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>此新聞未提及任何信用風險事件。</t>
+        </is>
+      </c>
       <c r="H43" s="2" t="inlineStr"/>
       <c r="I43" s="2" t="inlineStr"/>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
@@ -8434,8 +8598,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O43" s="2" t="n">
-        <v>0.024</v>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
         <is>
@@ -8444,7 +8610,11 @@
       </c>
       <c r="Q43" s="2" t="inlineStr"/>
       <c r="R43" s="2" t="inlineStr"/>
-      <c r="S43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -8472,16 +8642,24 @@
       <c r="AB43" s="2" t="inlineStr"/>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD43" s="2" t="inlineStr"/>
-      <c r="AE43" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF43" s="2" t="inlineStr"/>
       <c r="AG43" s="2" t="inlineStr"/>
       <c r="AH43" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI43" s="2" t="inlineStr">
@@ -8494,8 +8672,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK43" s="2" t="inlineStr"/>
-      <c r="AL43" s="2" t="inlineStr"/>
+      <c r="AK43" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="AL43" s="2" t="n">
+        <v>71</v>
+      </c>
       <c r="AM43" s="2" t="inlineStr"/>
       <c r="AN43" s="2" t="inlineStr"/>
       <c r="AO43" s="2" t="inlineStr">
@@ -8516,12 +8698,12 @@
       <c r="AR43" s="2" t="inlineStr"/>
       <c r="AS43" s="2" t="inlineStr">
         <is>
-          <t>61557616d68c76cf4c34a0623191d34058d3274ed70d8fc1e86334c98f7433ca</t>
+          <t>4f99cded53ff3e3c49b05cb98ccb3dbdabe3155f942fa5ce4ab5675ff0792f09</t>
         </is>
       </c>
       <c r="AT43" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU43" s="2" t="inlineStr"/>
@@ -8563,18 +8745,22 @@
           <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 發生任何信用風險事件。</t>
+        </is>
+      </c>
       <c r="H44" s="2" t="inlineStr"/>
       <c r="I44" s="2" t="inlineStr"/>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
@@ -8587,8 +8773,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O44" s="2" t="n">
-        <v>0.024</v>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
         <is>
@@ -8597,7 +8785,11 @@
       </c>
       <c r="Q44" s="2" t="inlineStr"/>
       <c r="R44" s="2" t="inlineStr"/>
-      <c r="S44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T44" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -8625,16 +8817,24 @@
       <c r="AB44" s="2" t="inlineStr"/>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD44" s="2" t="inlineStr"/>
-      <c r="AE44" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF44" s="2" t="inlineStr"/>
       <c r="AG44" s="2" t="inlineStr"/>
       <c r="AH44" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI44" s="2" t="inlineStr">
@@ -8647,8 +8847,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK44" s="2" t="inlineStr"/>
-      <c r="AL44" s="2" t="inlineStr"/>
+      <c r="AK44" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="AL44" s="2" t="n">
+        <v>86</v>
+      </c>
       <c r="AM44" s="2" t="inlineStr"/>
       <c r="AN44" s="2" t="inlineStr"/>
       <c r="AO44" s="2" t="inlineStr">
@@ -8669,12 +8873,12 @@
       <c r="AR44" s="2" t="inlineStr"/>
       <c r="AS44" s="2" t="inlineStr">
         <is>
-          <t>b36d9804e90e3ff91df4cf736f0b68d3b88ee6026366e5b8f3336a9db6b54010</t>
+          <t>c702ff49b27d3a36cd9fc7128dcc888df5333e430bd9d1a59bb0c0b3297250f2</t>
         </is>
       </c>
       <c r="AT44" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU44" s="2" t="inlineStr"/>
@@ -8716,18 +8920,22 @@
           <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 將於 11 月 20 日實施新的商業條款，並未涉及任何信用風險事件。</t>
+        </is>
+      </c>
       <c r="H45" s="2" t="inlineStr"/>
       <c r="I45" s="2" t="inlineStr"/>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M45" s="2" t="inlineStr">
@@ -8740,8 +8948,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O45" s="2" t="n">
-        <v>0.079</v>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.079</t>
+        </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
@@ -8750,7 +8960,11 @@
       </c>
       <c r="Q45" s="2" t="inlineStr"/>
       <c r="R45" s="2" t="inlineStr"/>
-      <c r="S45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T45" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -8778,16 +8992,24 @@
       <c r="AB45" s="2" t="inlineStr"/>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD45" s="2" t="inlineStr"/>
-      <c r="AE45" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF45" s="2" t="inlineStr"/>
       <c r="AG45" s="2" t="inlineStr"/>
       <c r="AH45" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI45" s="2" t="inlineStr">
@@ -8800,8 +9022,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK45" s="2" t="inlineStr"/>
-      <c r="AL45" s="2" t="inlineStr"/>
+      <c r="AK45" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="AL45" s="2" t="n">
+        <v>88</v>
+      </c>
       <c r="AM45" s="2" t="inlineStr"/>
       <c r="AN45" s="2" t="inlineStr"/>
       <c r="AO45" s="2" t="inlineStr">
@@ -8822,12 +9048,12 @@
       <c r="AR45" s="2" t="inlineStr"/>
       <c r="AS45" s="2" t="inlineStr">
         <is>
-          <t>7460bf9f6be0b4f2f93f68a081035b7483fdc8361ea4c7c337c2c96d815d773e</t>
+          <t>fa06725b52e12ba1dac5240c7b40621c70203942309f18bf710efb12eb141cfc</t>
         </is>
       </c>
       <c r="AT45" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU45" s="2" t="inlineStr"/>
@@ -8869,18 +9095,22 @@
           <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>目前無足夠證據顯示 Meta Platforms 相關信用風險事件。</t>
+        </is>
+      </c>
       <c r="H46" s="2" t="inlineStr"/>
       <c r="I46" s="2" t="inlineStr"/>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M46" s="2" t="inlineStr">
@@ -8893,8 +9123,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O46" s="2" t="n">
-        <v>0.079</v>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.079</t>
+        </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
@@ -8903,7 +9135,11 @@
       </c>
       <c r="Q46" s="2" t="inlineStr"/>
       <c r="R46" s="2" t="inlineStr"/>
-      <c r="S46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T46" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -8931,16 +9167,24 @@
       <c r="AB46" s="2" t="inlineStr"/>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD46" s="2" t="inlineStr"/>
-      <c r="AE46" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF46" s="2" t="inlineStr"/>
       <c r="AG46" s="2" t="inlineStr"/>
       <c r="AH46" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI46" s="2" t="inlineStr">
@@ -8953,8 +9197,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK46" s="2" t="inlineStr"/>
-      <c r="AL46" s="2" t="inlineStr"/>
+      <c r="AK46" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>79</v>
+      </c>
       <c r="AM46" s="2" t="inlineStr"/>
       <c r="AN46" s="2" t="inlineStr"/>
       <c r="AO46" s="2" t="inlineStr">
@@ -8975,12 +9223,12 @@
       <c r="AR46" s="2" t="inlineStr"/>
       <c r="AS46" s="2" t="inlineStr">
         <is>
-          <t>0517b27ea681c43f5c5a7dc8767c5d0bfb6b5ca885d47a82bbe3196b354fc837</t>
+          <t>4ef9cf41dc72910c07585b78c215ad5d73cf5f5066d0f549bf40ee5ecd2443d9</t>
         </is>
       </c>
       <c r="AT46" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU46" s="2" t="inlineStr"/>
@@ -9022,18 +9270,22 @@
           <t>$Meta Platforms (META.US)$ ...</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>目前無足夠資訊判斷 Meta Platforms 是否存在信用風險事件。</t>
+        </is>
+      </c>
       <c r="H47" s="2" t="inlineStr"/>
       <c r="I47" s="2" t="inlineStr"/>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M47" s="2" t="inlineStr">
@@ -9046,8 +9298,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O47" s="2" t="n">
-        <v>0.148</v>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.148</t>
+        </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -9056,7 +9310,11 @@
       </c>
       <c r="Q47" s="2" t="inlineStr"/>
       <c r="R47" s="2" t="inlineStr"/>
-      <c r="S47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T47" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -9084,16 +9342,24 @@
       <c r="AB47" s="2" t="inlineStr"/>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD47" s="2" t="inlineStr"/>
-      <c r="AE47" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF47" s="2" t="inlineStr"/>
       <c r="AG47" s="2" t="inlineStr"/>
       <c r="AH47" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI47" s="2" t="inlineStr">
@@ -9106,8 +9372,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK47" s="2" t="inlineStr"/>
-      <c r="AL47" s="2" t="inlineStr"/>
+      <c r="AK47" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="AL47" s="2" t="n">
+        <v>84</v>
+      </c>
       <c r="AM47" s="2" t="inlineStr"/>
       <c r="AN47" s="2" t="inlineStr"/>
       <c r="AO47" s="2" t="inlineStr">
@@ -9128,12 +9398,12 @@
       <c r="AR47" s="2" t="inlineStr"/>
       <c r="AS47" s="2" t="inlineStr">
         <is>
-          <t>39a874f75cef45cadda21059624f246da76bcea88d3705c5c291469f18417643</t>
+          <t>cd41978c9789b32ffc7b5d3c66226f253f4d8249a787a7cdb6610e88ba8266b7</t>
         </is>
       </c>
       <c r="AT47" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU47" s="2" t="inlineStr"/>
@@ -9175,18 +9445,22 @@
           <t>小摩上調Meta目標價至940美元</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 的目標價被小摩上調至 940 美元，並未涉及任何信用風險或違約訊息。</t>
+        </is>
+      </c>
       <c r="H48" s="2" t="inlineStr"/>
       <c r="I48" s="2" t="inlineStr"/>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
@@ -9199,8 +9473,10 @@
           <t>方法一</t>
         </is>
       </c>
-      <c r="O48" s="2" t="n">
-        <v>0.619</v>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.619</t>
+        </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
         <is>
@@ -9209,7 +9485,11 @@
       </c>
       <c r="Q48" s="2" t="inlineStr"/>
       <c r="R48" s="2" t="inlineStr"/>
-      <c r="S48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T48" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -9237,16 +9517,24 @@
       <c r="AB48" s="2" t="inlineStr"/>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD48" s="2" t="inlineStr"/>
-      <c r="AE48" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF48" s="2" t="inlineStr"/>
       <c r="AG48" s="2" t="inlineStr"/>
       <c r="AH48" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI48" s="2" t="inlineStr">
@@ -9259,8 +9547,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK48" s="2" t="inlineStr"/>
-      <c r="AL48" s="2" t="inlineStr"/>
+      <c r="AK48" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="AL48" s="2" t="n">
+        <v>166</v>
+      </c>
       <c r="AM48" s="2" t="inlineStr"/>
       <c r="AN48" s="2" t="inlineStr"/>
       <c r="AO48" s="2" t="inlineStr">
@@ -9281,12 +9573,12 @@
       <c r="AR48" s="2" t="inlineStr"/>
       <c r="AS48" s="2" t="inlineStr">
         <is>
-          <t>3fb9a23409e8708ea25ee8cb1bc2c57d982f0b2f9aece44cf25ef07e40b312e8</t>
+          <t>2902f0283f78587c48ffddceaf65e4f00ab9320a538b70310b7a65cb2e66c32c</t>
         </is>
       </c>
       <c r="AT48" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU48" s="2" t="inlineStr">
@@ -9332,18 +9624,22 @@
           <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 相關的信用風險事件。</t>
+        </is>
+      </c>
       <c r="H49" s="2" t="inlineStr"/>
       <c r="I49" s="2" t="inlineStr"/>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M49" s="2" t="inlineStr">
@@ -9356,8 +9652,10 @@
           <t>方法一</t>
         </is>
       </c>
-      <c r="O49" s="2" t="n">
-        <v>0.724</v>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>0.724</t>
+        </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
@@ -9366,7 +9664,11 @@
       </c>
       <c r="Q49" s="2" t="inlineStr"/>
       <c r="R49" s="2" t="inlineStr"/>
-      <c r="S49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T49" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -9394,16 +9696,24 @@
       <c r="AB49" s="2" t="inlineStr"/>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD49" s="2" t="inlineStr"/>
-      <c r="AE49" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD49" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE49" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF49" s="2" t="inlineStr"/>
       <c r="AG49" s="2" t="inlineStr"/>
       <c r="AH49" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI49" s="2" t="inlineStr">
@@ -9416,8 +9726,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK49" s="2" t="inlineStr"/>
-      <c r="AL49" s="2" t="inlineStr"/>
+      <c r="AK49" s="2" t="n">
+        <v>1465</v>
+      </c>
+      <c r="AL49" s="2" t="n">
+        <v>86</v>
+      </c>
       <c r="AM49" s="2" t="inlineStr"/>
       <c r="AN49" s="2" t="inlineStr"/>
       <c r="AO49" s="2" t="inlineStr">
@@ -9438,12 +9752,12 @@
       <c r="AR49" s="2" t="inlineStr"/>
       <c r="AS49" s="2" t="inlineStr">
         <is>
-          <t>4b5ef37f6c305b434f4c1c87831cc70b581ac080fa1eb75cf03d769479d206b7</t>
+          <t>7a654fc0a5274169b4f9fe947b8b8ec03dde033c6251e2de209d9ba7c3c6001a</t>
         </is>
       </c>
       <c r="AT49" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU49" s="2" t="inlineStr">
@@ -9489,18 +9803,22 @@
           <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>無足夠證據表明 Meta Platforms 目前存在任何信用風險事件。</t>
+        </is>
+      </c>
       <c r="H50" s="2" t="inlineStr"/>
       <c r="I50" s="2" t="inlineStr"/>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M50" s="2" t="inlineStr">
@@ -9513,8 +9831,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O50" s="2" t="n">
-        <v>0.899</v>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
         <is>
@@ -9523,7 +9843,11 @@
       </c>
       <c r="Q50" s="2" t="inlineStr"/>
       <c r="R50" s="2" t="inlineStr"/>
-      <c r="S50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T50" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -9551,16 +9875,24 @@
       <c r="AB50" s="2" t="inlineStr"/>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD50" s="2" t="inlineStr"/>
-      <c r="AE50" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD50" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE50" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF50" s="2" t="inlineStr"/>
       <c r="AG50" s="2" t="inlineStr"/>
       <c r="AH50" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI50" s="2" t="inlineStr">
@@ -9573,8 +9905,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK50" s="2" t="inlineStr"/>
-      <c r="AL50" s="2" t="inlineStr"/>
+      <c r="AK50" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="AL50" s="2" t="n">
+        <v>79</v>
+      </c>
       <c r="AM50" s="2" t="inlineStr"/>
       <c r="AN50" s="2" t="inlineStr"/>
       <c r="AO50" s="2" t="inlineStr">
@@ -9595,12 +9931,12 @@
       <c r="AR50" s="2" t="inlineStr"/>
       <c r="AS50" s="2" t="inlineStr">
         <is>
-          <t>29d466f90bfdbdf0f7a04f87c9e7bf26725f4409800afedde98bde36f1864b93</t>
+          <t>16a4321cafcedd1de655faef6363e09c943abbfca2e21020dcd4978852904046</t>
         </is>
       </c>
       <c r="AT50" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU50" s="2" t="inlineStr"/>
@@ -9642,18 +9978,22 @@
           <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>此新聞未提及任何與信用風險相關的事件，無法判斷是否存在違約或其他信用風險指標。</t>
+        </is>
+      </c>
       <c r="H51" s="2" t="inlineStr"/>
       <c r="I51" s="2" t="inlineStr"/>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>LLM</t>
         </is>
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>待補分析</t>
+          <t>待人工覆核</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
@@ -9666,8 +10006,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O51" s="2" t="n">
-        <v>0.9330000000000001</v>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
         <is>
@@ -9676,7 +10018,11 @@
       </c>
       <c r="Q51" s="2" t="inlineStr"/>
       <c r="R51" s="2" t="inlineStr"/>
-      <c r="S51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
       <c r="T51" s="2" t="inlineStr">
         <is>
           <t>公司清單／原始紀錄</t>
@@ -9704,16 +10050,24 @@
       <c r="AB51" s="2" t="inlineStr"/>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD51" s="2" t="inlineStr"/>
-      <c r="AE51" s="2" t="inlineStr"/>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD51" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE51" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
       <c r="AF51" s="2" t="inlineStr"/>
       <c r="AG51" s="2" t="inlineStr"/>
       <c r="AH51" s="2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AI51" s="2" t="inlineStr">
@@ -9726,8 +10080,12 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK51" s="2" t="inlineStr"/>
-      <c r="AL51" s="2" t="inlineStr"/>
+      <c r="AK51" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AL51" s="2" t="n">
+        <v>98</v>
+      </c>
       <c r="AM51" s="2" t="inlineStr"/>
       <c r="AN51" s="2" t="inlineStr"/>
       <c r="AO51" s="2" t="inlineStr">
@@ -9748,12 +10106,12 @@
       <c r="AR51" s="2" t="inlineStr"/>
       <c r="AS51" s="2" t="inlineStr">
         <is>
-          <t>8d2bf44846475f369f3134681a465fafc51dc63ac9d90ebf8bca03c554f5390f</t>
+          <t>47c1b31266d05ddaa22517da130de1c8045ed17424f50ac7a377447ca0860fa0</t>
         </is>
       </c>
       <c r="AT51" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU51" s="2" t="inlineStr"/>
@@ -10264,12 +10622,12 @@
       <c r="AR2" s="3" t="inlineStr"/>
       <c r="AS2" s="3" t="inlineStr">
         <is>
-          <t>9c6e12fb3f4675cdd525f4cd8e6728ff928a7a2fe91742feeb2a813c5ad9f3ee</t>
+          <t>bdd24ef76a4546a256b32abb28cf5302a1284bf39f2af20abba1b36fa21f18bb</t>
         </is>
       </c>
       <c r="AT2" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU2" s="3" t="inlineStr"/>
@@ -10467,12 +10825,12 @@
       <c r="AR3" s="4" t="inlineStr"/>
       <c r="AS3" s="4" t="inlineStr">
         <is>
-          <t>4a7b855761fde685d2a95337a008078bd78b73e253b900aa8cc065fb389b2d9e</t>
+          <t>31ac25c21d4bebfbab59df4480f0ddb4c09ea712500f7bdf0468bebdce0a3dfb</t>
         </is>
       </c>
       <c r="AT3" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU3" s="4" t="inlineStr"/>
@@ -10670,12 +11028,12 @@
       <c r="AR4" s="3" t="inlineStr"/>
       <c r="AS4" s="3" t="inlineStr">
         <is>
-          <t>8e031f92cd74fcfc61bfcf781bcffe51843c9ee2e2e39e51e5453f8f45a99e44</t>
+          <t>9a8b6db6b9fb5ef6fbca7c90bc14efb93749f3f82f0d51ff32cc8e02991479f8</t>
         </is>
       </c>
       <c r="AT4" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU4" s="3" t="inlineStr"/>
@@ -10873,12 +11231,12 @@
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>ada338c05fef387e2d7ce197306651f3dbb214c69ecc9866d7a150a731a5a099</t>
+          <t>7ae45cdb4433a4a84f6cef6cb6bc376cd7a669f325e1703a3f7005a0c8de4359</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr"/>
@@ -11072,12 +11430,12 @@
       <c r="AR6" s="3" t="inlineStr"/>
       <c r="AS6" s="3" t="inlineStr">
         <is>
-          <t>45f2d58b595adcc6f0026cdea120b6a1f1ec508846f65f6dcdd49a6445c6a164</t>
+          <t>d2d328d3d98076805e6f6b9cb8237e2e9e200e6d9bb5e0fa882c8acf35b97fee</t>
         </is>
       </c>
       <c r="AT6" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU6" s="3" t="inlineStr"/>
@@ -11279,12 +11637,12 @@
       <c r="AR7" s="4" t="inlineStr"/>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>6293669f1b7b8f8c8534949a5eb967ea7dd751e6cbfdc992fc63a513c3acdf57</t>
+          <t>3f2494e218bc0e1eecba3fd070542744a25a1d2d49b9957593ed742cdfc67af3</t>
         </is>
       </c>
       <c r="AT7" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU7" s="4" t="inlineStr"/>
@@ -11486,12 +11844,12 @@
       <c r="AR8" s="4" t="inlineStr"/>
       <c r="AS8" s="4" t="inlineStr">
         <is>
-          <t>d46ed09b38ab6b5b8ad19b1eecd0637350a911055fa23a5ebad356093eb73fc4</t>
+          <t>ee60dbb626b10b42906c52973342d901ef7b3d71440b43fc63cd28043abbe400</t>
         </is>
       </c>
       <c r="AT8" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU8" s="4" t="inlineStr"/>
@@ -11689,12 +12047,12 @@
       <c r="AR9" s="4" t="inlineStr"/>
       <c r="AS9" s="4" t="inlineStr">
         <is>
-          <t>5648c46d373ce56dbafbf849d726dd446b7e6d674077c822ffadaa589c9222da</t>
+          <t>165aaf928e1ab154225c3474a29df9f97a5300f7b263bdc6622b830e38a6a440</t>
         </is>
       </c>
       <c r="AT9" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU9" s="4" t="inlineStr"/>
@@ -11896,12 +12254,12 @@
       <c r="AR10" s="4" t="inlineStr"/>
       <c r="AS10" s="4" t="inlineStr">
         <is>
-          <t>fc9dd5bd08cceed3630840f06300aa5cad60f28e7fb03a3a1302cae6f3a27c56</t>
+          <t>858cacb37eb67b542539e06c9db58dd953174c1112c39812f19141d474956f9b</t>
         </is>
       </c>
       <c r="AT10" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU10" s="4" t="inlineStr"/>
@@ -12103,12 +12461,12 @@
       <c r="AR11" s="3" t="inlineStr"/>
       <c r="AS11" s="3" t="inlineStr">
         <is>
-          <t>877cf279a144f268174ffce46ef0687d7153ebb6c891edad1063064fd98a0fd1</t>
+          <t>cc5e4ca2634ed6b55f67ad0b7f897205979738c904cd55e93372f6ca8ba983df</t>
         </is>
       </c>
       <c r="AT11" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU11" s="3" t="inlineStr"/>
@@ -12322,12 +12680,12 @@
       </c>
       <c r="AS12" s="3" t="inlineStr">
         <is>
-          <t>23af1c5424a692b58f6f8424d4d7db4114fd03d481f315e02e607593225853ac</t>
+          <t>0c54163024f73530fe8a69871bef0aa1ec59c0fcaec0fd0089d1f707e67bd6cb</t>
         </is>
       </c>
       <c r="AT12" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU12" s="3" t="inlineStr"/>
@@ -12529,12 +12887,12 @@
       </c>
       <c r="AS13" s="3" t="inlineStr">
         <is>
-          <t>e326e2866abb147a3fb34777e0bc874645fe44846987176be28da779dc413ec3</t>
+          <t>88924c348bff62bff0ac8702762fc6d7b14f97483fccaf0c8739797c7176bb4f</t>
         </is>
       </c>
       <c r="AT13" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU13" s="3" t="inlineStr"/>
@@ -12736,12 +13094,12 @@
       </c>
       <c r="AS14" s="3" t="inlineStr">
         <is>
-          <t>01beb5ae9c384c5411ec04c16cb6a5646e5b0cca885791a4e83159dc7625ac6e</t>
+          <t>f0d840da549481f47e5ec484f645ac865679395b49dae53f0b418001a63b3846</t>
         </is>
       </c>
       <c r="AT14" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU14" s="3" t="inlineStr"/>
@@ -12939,12 +13297,12 @@
       <c r="AR15" s="3" t="inlineStr"/>
       <c r="AS15" s="3" t="inlineStr">
         <is>
-          <t>837ee79400109c77c83c3651332f843b9f4e826d5ea05520c8917c212e482f0e</t>
+          <t>96fe9c4aea452cafb38eb9b316863b8b873d4bac780bc7626045f065fb864e0c</t>
         </is>
       </c>
       <c r="AT15" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU15" s="3" t="inlineStr"/>
@@ -13142,12 +13500,12 @@
       <c r="AR16" s="3" t="inlineStr"/>
       <c r="AS16" s="3" t="inlineStr">
         <is>
-          <t>9b64ccbf3b8eec2573fa50d9326de159a3b54a791d0866dc7b95f11253cb093a</t>
+          <t>d0c89ac0978ce4a4da75684fb2fc8361eed3370fa3e36faeffd7772447123b13</t>
         </is>
       </c>
       <c r="AT16" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU16" s="3" t="inlineStr"/>
@@ -13357,12 +13715,12 @@
       </c>
       <c r="AS17" s="3" t="inlineStr">
         <is>
-          <t>072fda62469150c62037ef694fb92f86f206372bc347cbabaf4f9ce7a5e4ae8a</t>
+          <t>101eb1810e77321e67644d25789ae03393ad85e6b49c0c0e22d2fbaf0b2d4572</t>
         </is>
       </c>
       <c r="AT17" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU17" s="3" t="inlineStr"/>
@@ -13552,12 +13910,12 @@
       <c r="AR18" s="3" t="inlineStr"/>
       <c r="AS18" s="3" t="inlineStr">
         <is>
-          <t>4a1bb79f89b6aab12ef4224737cdbe24df29acad6d217dc6e571fdaa8a3ac6de</t>
+          <t>66f86d7d3aa8fc873a061c7ceda00a72f77e5f42e9f1c60b74e72af9e961e92a</t>
         </is>
       </c>
       <c r="AT18" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU18" s="3" t="inlineStr"/>
@@ -13576,7 +13934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW32"/>
+  <dimension ref="A1:AW48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -14056,12 +14414,12 @@
       <c r="AR2" s="2" t="inlineStr"/>
       <c r="AS2" s="2" t="inlineStr">
         <is>
-          <t>59d0b070ec5a7add0271c3f6ec92358a64eeb2efeec9e4757fb6b90cf9138ea5</t>
+          <t>1a98cdbca58ab019d9282ae07fe1105d0d3727cb89d10bdec72a3b1c9a73b6c6</t>
         </is>
       </c>
       <c r="AT2" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU2" s="2" t="inlineStr"/>
@@ -14235,12 +14593,12 @@
       <c r="AR3" s="2" t="inlineStr"/>
       <c r="AS3" s="2" t="inlineStr">
         <is>
-          <t>43e900bf3d1ed6beee750787e09d914b073f9631b302da70437abfd67d31c886</t>
+          <t>3105206721b31ed41e0dbf793d7370d073ecbb3f058416614c21f9115576dccc</t>
         </is>
       </c>
       <c r="AT3" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU3" s="2" t="inlineStr"/>
@@ -14438,12 +14796,12 @@
       <c r="AR4" s="2" t="inlineStr"/>
       <c r="AS4" s="2" t="inlineStr">
         <is>
-          <t>65bc54e92abf071a7016f9c0a1f2b7eb8c1c45e55ed56e0b297d04624170137d</t>
+          <t>74f36f7ff784fc6dd497785eeb98a4085a2f388428b2056d6cece7e93496127a</t>
         </is>
       </c>
       <c r="AT4" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU4" s="2" t="inlineStr"/>
@@ -14637,12 +14995,12 @@
       <c r="AR5" s="3" t="inlineStr"/>
       <c r="AS5" s="3" t="inlineStr">
         <is>
-          <t>9c6e12fb3f4675cdd525f4cd8e6728ff928a7a2fe91742feeb2a813c5ad9f3ee</t>
+          <t>bdd24ef76a4546a256b32abb28cf5302a1284bf39f2af20abba1b36fa21f18bb</t>
         </is>
       </c>
       <c r="AT5" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU5" s="3" t="inlineStr"/>
@@ -14816,12 +15174,12 @@
       <c r="AR6" s="2" t="inlineStr"/>
       <c r="AS6" s="2" t="inlineStr">
         <is>
-          <t>ba85b94389e2d00dfe1eea9ca4ec4c947d71941074fab84daea46686c82f8313</t>
+          <t>4d6c8b7e7d6c2da825bd038a8178b6c9987a58255a01270f95766656ce678a43</t>
         </is>
       </c>
       <c r="AT6" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU6" s="2" t="inlineStr"/>
@@ -15019,12 +15377,12 @@
       <c r="AR7" s="4" t="inlineStr"/>
       <c r="AS7" s="4" t="inlineStr">
         <is>
-          <t>4a7b855761fde685d2a95337a008078bd78b73e253b900aa8cc065fb389b2d9e</t>
+          <t>31ac25c21d4bebfbab59df4480f0ddb4c09ea712500f7bdf0468bebdce0a3dfb</t>
         </is>
       </c>
       <c r="AT7" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU7" s="4" t="inlineStr"/>
@@ -15198,12 +15556,12 @@
       <c r="AR8" s="2" t="inlineStr"/>
       <c r="AS8" s="2" t="inlineStr">
         <is>
-          <t>fc0cc2efc8f48a91fffa090920578ebcb4a29fbf2bcc80aa2b69c926176021b6</t>
+          <t>695fb63e1bb75f4694515d67896cc171598cabd881c54d393386eb4ba33be88d</t>
         </is>
       </c>
       <c r="AT8" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU8" s="2" t="inlineStr"/>
@@ -15377,12 +15735,12 @@
       <c r="AR9" s="2" t="inlineStr"/>
       <c r="AS9" s="2" t="inlineStr">
         <is>
-          <t>21c491be7cb3b2def9edabf23709b08a655e53493a14c78ec977d71204e639af</t>
+          <t>b4f5e9f012bc989693d27c1622d2ebc0f82bc3027570c6eb88919f68612e818b</t>
         </is>
       </c>
       <c r="AT9" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU9" s="2" t="inlineStr"/>
@@ -15576,12 +15934,12 @@
       <c r="AR10" s="3" t="inlineStr"/>
       <c r="AS10" s="3" t="inlineStr">
         <is>
-          <t>45f2d58b595adcc6f0026cdea120b6a1f1ec508846f65f6dcdd49a6445c6a164</t>
+          <t>d2d328d3d98076805e6f6b9cb8237e2e9e200e6d9bb5e0fa882c8acf35b97fee</t>
         </is>
       </c>
       <c r="AT10" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU10" s="3" t="inlineStr"/>
@@ -15759,12 +16117,12 @@
       </c>
       <c r="AS11" s="2" t="inlineStr">
         <is>
-          <t>7fdf39cffff89cb42bdf631c4afa26ea2bb9a9ee2e904623a9711791f419b039</t>
+          <t>f4eb6c4702ab24462aa85a061a50c385a20fa2649060066185f80a5055aff49c</t>
         </is>
       </c>
       <c r="AT11" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU11" s="2" t="inlineStr"/>
@@ -15966,12 +16324,12 @@
       <c r="AR12" s="4" t="inlineStr"/>
       <c r="AS12" s="4" t="inlineStr">
         <is>
-          <t>6293669f1b7b8f8c8534949a5eb967ea7dd751e6cbfdc992fc63a513c3acdf57</t>
+          <t>3f2494e218bc0e1eecba3fd070542744a25a1d2d49b9957593ed742cdfc67af3</t>
         </is>
       </c>
       <c r="AT12" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU12" s="4" t="inlineStr"/>
@@ -16173,12 +16531,12 @@
       <c r="AR13" s="4" t="inlineStr"/>
       <c r="AS13" s="4" t="inlineStr">
         <is>
-          <t>d46ed09b38ab6b5b8ad19b1eecd0637350a911055fa23a5ebad356093eb73fc4</t>
+          <t>ee60dbb626b10b42906c52973342d901ef7b3d71440b43fc63cd28043abbe400</t>
         </is>
       </c>
       <c r="AT13" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU13" s="4" t="inlineStr"/>
@@ -16376,12 +16734,12 @@
       <c r="AR14" s="4" t="inlineStr"/>
       <c r="AS14" s="4" t="inlineStr">
         <is>
-          <t>5648c46d373ce56dbafbf849d726dd446b7e6d674077c822ffadaa589c9222da</t>
+          <t>165aaf928e1ab154225c3474a29df9f97a5300f7b263bdc6622b830e38a6a440</t>
         </is>
       </c>
       <c r="AT14" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU14" s="4" t="inlineStr"/>
@@ -16583,12 +16941,12 @@
       <c r="AR15" s="4" t="inlineStr"/>
       <c r="AS15" s="4" t="inlineStr">
         <is>
-          <t>fc9dd5bd08cceed3630840f06300aa5cad60f28e7fb03a3a1302cae6f3a27c56</t>
+          <t>858cacb37eb67b542539e06c9db58dd953174c1112c39812f19141d474956f9b</t>
         </is>
       </c>
       <c r="AT15" s="4" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU15" s="4" t="inlineStr"/>
@@ -16762,12 +17120,12 @@
       <c r="AR16" s="2" t="inlineStr"/>
       <c r="AS16" s="2" t="inlineStr">
         <is>
-          <t>62e0cb1e4e902fe66bee49a5e5e09c6c98815677978087f2f8b17feed7e61d5c</t>
+          <t>2ef7099c2881d6f63f62a0fea8f75b530f8512ca5179af0d55955a14ec110dbe</t>
         </is>
       </c>
       <c r="AT16" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU16" s="2" t="inlineStr"/>
@@ -16945,12 +17303,12 @@
       <c r="AR17" s="2" t="inlineStr"/>
       <c r="AS17" s="2" t="inlineStr">
         <is>
-          <t>f1631fdd74d9fde1bc83f4593243a4786b4bcd2a17a5959906712c24fc2b45b4</t>
+          <t>e748226659831de0bb4541d1da055931db5b8a4e6d4d94283f744d7443920005</t>
         </is>
       </c>
       <c r="AT17" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU17" s="2" t="inlineStr"/>
@@ -17128,12 +17486,12 @@
       <c r="AR18" s="2" t="inlineStr"/>
       <c r="AS18" s="2" t="inlineStr">
         <is>
-          <t>d4aa2f7e089cc5c99dfb6bf4481e563cb84e94d302da081f736f9d2798c5eab9</t>
+          <t>95c7c2a6b8c17b4c70e3b89273c3388b6d6ba20b97f994efaef9bf6d3a42bbf0</t>
         </is>
       </c>
       <c r="AT18" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU18" s="2" t="inlineStr"/>
@@ -17335,12 +17693,12 @@
       <c r="AR19" s="3" t="inlineStr"/>
       <c r="AS19" s="3" t="inlineStr">
         <is>
-          <t>877cf279a144f268174ffce46ef0687d7153ebb6c891edad1063064fd98a0fd1</t>
+          <t>cc5e4ca2634ed6b55f67ad0b7f897205979738c904cd55e93372f6ca8ba983df</t>
         </is>
       </c>
       <c r="AT19" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU19" s="3" t="inlineStr"/>
@@ -17554,12 +17912,12 @@
       </c>
       <c r="AS20" s="3" t="inlineStr">
         <is>
-          <t>23af1c5424a692b58f6f8424d4d7db4114fd03d481f315e02e607593225853ac</t>
+          <t>0c54163024f73530fe8a69871bef0aa1ec59c0fcaec0fd0089d1f707e67bd6cb</t>
         </is>
       </c>
       <c r="AT20" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU20" s="3" t="inlineStr"/>
@@ -17761,12 +18119,12 @@
       </c>
       <c r="AS21" s="3" t="inlineStr">
         <is>
-          <t>e326e2866abb147a3fb34777e0bc874645fe44846987176be28da779dc413ec3</t>
+          <t>88924c348bff62bff0ac8702762fc6d7b14f97483fccaf0c8739797c7176bb4f</t>
         </is>
       </c>
       <c r="AT21" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU21" s="3" t="inlineStr"/>
@@ -17968,12 +18326,12 @@
       </c>
       <c r="AS22" s="3" t="inlineStr">
         <is>
-          <t>01beb5ae9c384c5411ec04c16cb6a5646e5b0cca885791a4e83159dc7625ac6e</t>
+          <t>f0d840da549481f47e5ec484f645ac865679395b49dae53f0b418001a63b3846</t>
         </is>
       </c>
       <c r="AT22" s="3" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU22" s="3" t="inlineStr"/>
@@ -18175,12 +18533,12 @@
       <c r="AR23" s="3" t="inlineStr"/>
       <c r="AS23" s="3" t="inlineStr">
         <is>
-          <t>9b64ccbf3b8eec2573fa50d9326de159a3b54a791d0866dc7b95f11253cb093a</t>
+          <t>d0c89ac0978ce4a4da75684fb2fc8361eed3370fa3e36faeffd7772447123b13</t>
         </is>
       </c>
       <c r="AT23" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU23" s="3" t="inlineStr"/>
@@ -18390,12 +18748,12 @@
       </c>
       <c r="AS24" s="3" t="inlineStr">
         <is>
-          <t>072fda62469150c62037ef694fb92f86f206372bc347cbabaf4f9ce7a5e4ae8a</t>
+          <t>101eb1810e77321e67644d25789ae03393ad85e6b49c0c0e22d2fbaf0b2d4572</t>
         </is>
       </c>
       <c r="AT24" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU24" s="3" t="inlineStr"/>
@@ -18553,12 +18911,12 @@
       <c r="AR25" s="2" t="inlineStr"/>
       <c r="AS25" s="2" t="inlineStr">
         <is>
-          <t>c2b733a875d9b2af7cd5b7f6fec0c25c1dad89c64a7f34579fc58492f51de623</t>
+          <t>636ff7b98c973316542530b9db36c941119ed7b3d4e0a29ff671af38868cf549</t>
         </is>
       </c>
       <c r="AT25" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU25" s="2" t="inlineStr"/>
@@ -18748,12 +19106,12 @@
       <c r="AR26" s="3" t="inlineStr"/>
       <c r="AS26" s="3" t="inlineStr">
         <is>
-          <t>4a1bb79f89b6aab12ef4224737cdbe24df29acad6d217dc6e571fdaa8a3ac6de</t>
+          <t>66f86d7d3aa8fc873a061c7ceda00a72f77e5f42e9f1c60b74e72af9e961e92a</t>
         </is>
       </c>
       <c r="AT26" s="3" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU26" s="3" t="inlineStr"/>
@@ -18923,12 +19281,12 @@
       <c r="AR27" s="2" t="inlineStr"/>
       <c r="AS27" s="2" t="inlineStr">
         <is>
-          <t>3b06ef9bf135012a500ef20e1ec38242ff4873bafe105a625576beace15327e0</t>
+          <t>95e7d13ed0dbe46f108916eb1a8e616902b0379935ad571ba5596aff71b5d813</t>
         </is>
       </c>
       <c r="AT27" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU27" s="2" t="inlineStr"/>
@@ -19102,12 +19460,12 @@
       <c r="AR28" s="2" t="inlineStr"/>
       <c r="AS28" s="2" t="inlineStr">
         <is>
-          <t>5ec281d9984561f238970a22d7f6d429bcdacf1346d40dedbfead923c141b184</t>
+          <t>5c6e5e1338211ad9ff12890c09dea50568a68fb8a73cb5671e7f1edfdeae2c60</t>
         </is>
       </c>
       <c r="AT28" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU28" s="2" t="inlineStr"/>
@@ -19277,12 +19635,12 @@
       <c r="AR29" s="2" t="inlineStr"/>
       <c r="AS29" s="2" t="inlineStr">
         <is>
-          <t>2fa7566bd35239182d98b2bd93680cee99ad9b293f1fd8b19fe33e8fcdceacaa</t>
+          <t>13b14efb0652327cd3fa331170283475c7ba9b53bd3863784fda7f0121dd7e28</t>
         </is>
       </c>
       <c r="AT29" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU29" s="2" t="inlineStr"/>
@@ -19440,12 +19798,12 @@
       <c r="AR30" s="2" t="inlineStr"/>
       <c r="AS30" s="2" t="inlineStr">
         <is>
-          <t>0e5c70db7b6b4f316d00fc7eb40f668750b8ed08e472edc429651639c5b38f20</t>
+          <t>a0d00b59e76935d81428a91f3258118f0cfecaecf3ded0e60172850efedbba04</t>
         </is>
       </c>
       <c r="AT30" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU30" s="2" t="inlineStr"/>
@@ -19615,12 +19973,12 @@
       <c r="AR31" s="2" t="inlineStr"/>
       <c r="AS31" s="2" t="inlineStr">
         <is>
-          <t>4784da4cbce731f9ee8a50b210b9ecb9a9c70b89799faeeac11bdd634f63105c</t>
+          <t>f16e643da6decfa9cfa028489943f1f58dead9ac1463b0c7049f61a6a5091721</t>
         </is>
       </c>
       <c r="AT31" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU31" s="2" t="inlineStr"/>
@@ -19686,8 +20044,10 @@
           <t>方法二</t>
         </is>
       </c>
-      <c r="O32" s="2" t="n">
-        <v>-0.954</v>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>'-0.954</t>
+        </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
@@ -19758,11 +20118,15 @@
           <t>financial_events_v1.0</t>
         </is>
       </c>
-      <c r="AK32" s="2" t="n">
-        <v>1449</v>
-      </c>
-      <c r="AL32" s="2" t="n">
-        <v>86</v>
+      <c r="AK32" s="2" t="inlineStr">
+        <is>
+          <t>1449</t>
+        </is>
+      </c>
+      <c r="AL32" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="AM32" s="2" t="inlineStr"/>
       <c r="AN32" s="2" t="inlineStr"/>
@@ -19784,12 +20148,12 @@
       <c r="AR32" s="2" t="inlineStr"/>
       <c r="AS32" s="2" t="inlineStr">
         <is>
-          <t>5561c485d0bf6a8f7f3c02db776ad98b37ba9deae1b4991a83a6428d34222d39</t>
+          <t>3b3ecec0bb0d4667d56b8eca57711b8f7fc32ca367c1d3a3c0daf724e7aa6deb</t>
         </is>
       </c>
       <c r="AT32" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="AU32" s="2" t="inlineStr"/>
@@ -19800,8 +20164,2832 @@
       </c>
       <c r="AW32" s="2" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:15:00+08:00</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 的股價下跌並未顯示任何明確的信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="2" t="inlineStr"/>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>'-0.933</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T33" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQeWhsa1VSYXhEM3JSbUNSMEZWTEFqd3A5NGd5SFJWdEZoZmpTRlNzUmM1RVFYT3cwb2JrNzRPMUFfUHlETHI5S1AyajJJdmF0YW5XbnU3MzBGREZOREo4YUszYUl3b3Y1TEdsMXpTWmxqX18zNUlSS2RwcjA0ZkJ6SXo1ek1IcWlhVl9IU1lJTVJqQQ?oc=5</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>ec4ba7c19aafcde2fbd710f7</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr"/>
+      <c r="Y33" s="2" t="inlineStr"/>
+      <c r="Z33" s="2" t="inlineStr"/>
+      <c r="AA33" s="2" t="inlineStr"/>
+      <c r="AB33" s="2" t="inlineStr"/>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD33" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE33" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF33" s="2" t="inlineStr"/>
+      <c r="AG33" s="2" t="inlineStr"/>
+      <c r="AH33" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI33" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ33" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK33" s="2" t="n">
+        <v>1448</v>
+      </c>
+      <c r="AL33" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="AM33" s="2" t="inlineStr"/>
+      <c r="AN33" s="2" t="inlineStr"/>
+      <c r="AO33" s="2" t="inlineStr">
+        <is>
+          <t>0c52c54c8a0e83fbafe6b0e1</t>
+        </is>
+      </c>
+      <c r="AP33" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ33" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR33" s="2" t="inlineStr"/>
+      <c r="AS33" s="2" t="inlineStr">
+        <is>
+          <t>e80328332c4f74df8e9629757ce5aca0978b96338cf043ff9bf41b5a74327514</t>
+        </is>
+      </c>
+      <c r="AT33" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU33" s="2" t="inlineStr"/>
+      <c r="AV33" s="2" t="inlineStr">
+        <is>
+          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
+        </is>
+      </c>
+      <c r="AW33" s="2" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:30:04+08:00</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 相關新聞未提及任何信用風險事件，無法判斷是否存在違約或其他信用事件。</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr"/>
+      <c r="I34" s="2" t="inlineStr"/>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>'-0.873</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>ANTITRUST_INVESTIGATION</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T34" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2724913</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>d1348ad94c5e9aa7d9188003</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr"/>
+      <c r="Y34" s="2" t="inlineStr"/>
+      <c r="Z34" s="2" t="inlineStr"/>
+      <c r="AA34" s="2" t="inlineStr"/>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD34" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE34" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF34" s="2" t="inlineStr"/>
+      <c r="AG34" s="2" t="inlineStr"/>
+      <c r="AH34" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI34" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ34" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK34" s="2" t="n">
+        <v>1464</v>
+      </c>
+      <c r="AL34" s="2" t="n">
+        <v>94</v>
+      </c>
+      <c r="AM34" s="2" t="inlineStr"/>
+      <c r="AN34" s="2" t="inlineStr"/>
+      <c r="AO34" s="2" t="inlineStr">
+        <is>
+          <t>2ff90a8d58ba249a9252028a</t>
+        </is>
+      </c>
+      <c r="AP34" s="2" t="inlineStr">
+        <is>
+          <t>通知、檢視授信及自營部位、持續追蹤</t>
+        </is>
+      </c>
+      <c r="AQ34" s="2" t="inlineStr">
+        <is>
+          <t>反壟斷調查</t>
+        </is>
+      </c>
+      <c r="AR34" s="2" t="inlineStr"/>
+      <c r="AS34" s="2" t="inlineStr">
+        <is>
+          <t>96228df4d354588d61a5e4fee402dae26f2644c637ffd31d091328d77cef2bdb</t>
+        </is>
+      </c>
+      <c r="AT34" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU34" s="2" t="inlineStr">
+        <is>
+          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
+        </is>
+      </c>
+      <c r="AV34" s="2" t="inlineStr">
+        <is>
+          <t>Publishers and advertisers call on EU and UK antitrust regulators to suspend Meta's new business terms</t>
+        </is>
+      </c>
+      <c r="AW34" s="2" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:24:10+08:00</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選，但未涉及任何信用風險或債務違約訊息。</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr"/>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>'-0.824</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T35" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2726833</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>f25a40e5e491828684fad933</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr"/>
+      <c r="Y35" s="2" t="inlineStr"/>
+      <c r="Z35" s="2" t="inlineStr"/>
+      <c r="AA35" s="2" t="inlineStr"/>
+      <c r="AB35" s="2" t="inlineStr"/>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD35" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE35" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF35" s="2" t="inlineStr"/>
+      <c r="AG35" s="2" t="inlineStr"/>
+      <c r="AH35" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI35" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ35" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK35" s="2" t="n">
+        <v>1442</v>
+      </c>
+      <c r="AL35" s="2" t="n">
+        <v>174</v>
+      </c>
+      <c r="AM35" s="2" t="inlineStr"/>
+      <c r="AN35" s="2" t="inlineStr"/>
+      <c r="AO35" s="2" t="inlineStr">
+        <is>
+          <t>0e55b465fd7b98d6d05db82c</t>
+        </is>
+      </c>
+      <c r="AP35" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ35" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR35" s="2" t="inlineStr"/>
+      <c r="AS35" s="2" t="inlineStr">
+        <is>
+          <t>da1d8d50a8880e36b4c6f7fe3437a374f0f1c55828e104ac239cb9cfd44548d5</t>
+        </is>
+      </c>
+      <c r="AT35" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU35" s="2" t="inlineStr">
+        <is>
+          <t>巴西總統指控Meta操縱大選</t>
+        </is>
+      </c>
+      <c r="AV35" s="2" t="inlineStr">
+        <is>
+          <t>Brazilian president accuses Meta of rigging election</t>
+        </is>
+      </c>
+      <c r="AW35" s="2" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T14:15:46+08:00</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 目前沒有任何明確的違約或信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="inlineStr"/>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>'-0.745</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T36" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>https://tw.tradingview.com/symbols/NASDAQ-META/news/</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>a37f44666d6b93b23fa84c03</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr"/>
+      <c r="Y36" s="2" t="inlineStr"/>
+      <c r="Z36" s="2" t="inlineStr"/>
+      <c r="AA36" s="2" t="inlineStr"/>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD36" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE36" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF36" s="2" t="inlineStr"/>
+      <c r="AG36" s="2" t="inlineStr"/>
+      <c r="AH36" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI36" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ36" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK36" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AL36" s="2" t="n">
+        <v>78</v>
+      </c>
+      <c r="AM36" s="2" t="inlineStr"/>
+      <c r="AN36" s="2" t="inlineStr"/>
+      <c r="AO36" s="2" t="inlineStr">
+        <is>
+          <t>c9eb84ac77729681440eb57a</t>
+        </is>
+      </c>
+      <c r="AP36" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ36" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR36" s="2" t="inlineStr"/>
+      <c r="AS36" s="2" t="inlineStr">
+        <is>
+          <t>9a4374bb2beaeb0b1ed12ac500e3d948f565b7eee6a6daecbeaefe1dd6133486</t>
+        </is>
+      </c>
+      <c r="AT36" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU36" s="2" t="inlineStr">
+        <is>
+          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
+        </is>
+      </c>
+      <c r="AV36" s="2" t="inlineStr">
+        <is>
+          <t>Greece passes social media ban for children under 15</t>
+        </is>
+      </c>
+      <c r="AW36" s="2" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T18:13:48+08:00</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠資訊顯示 Meta Platforms 相關的信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>'-0.378</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>UNKNOWN</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T37" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxON0pWLThkWllqVTRvcVRMY1NVeUN0UVNxa08tNkRhbzQxTUFlaTZON1BOYkh4bDEtaHB4X2d6dHk3VS1sVDhYMEhhZ0IyMVpjTXJjWVJ3WE9ZTDdWWG9paC1zdHZpbFpFNVZNTk9aYXhQRnRtWVlXRE0tZ2hOaDFmc2RIQUV5aTRBbEJaaDNsWUNxUXc?oc=5</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W37" s="2" t="inlineStr">
+        <is>
+          <t>464a7cf6ed8a0d8eb8b7128c</t>
+        </is>
+      </c>
+      <c r="X37" s="2" t="inlineStr"/>
+      <c r="Y37" s="2" t="inlineStr"/>
+      <c r="Z37" s="2" t="inlineStr"/>
+      <c r="AA37" s="2" t="inlineStr"/>
+      <c r="AB37" s="2" t="inlineStr"/>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD37" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE37" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF37" s="2" t="inlineStr"/>
+      <c r="AG37" s="2" t="inlineStr"/>
+      <c r="AH37" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI37" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ37" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK37" s="2" t="n">
+        <v>1463</v>
+      </c>
+      <c r="AL37" s="2" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM37" s="2" t="inlineStr"/>
+      <c r="AN37" s="2" t="inlineStr"/>
+      <c r="AO37" s="2" t="inlineStr">
+        <is>
+          <t>2030e51b7ee960a291545c4e</t>
+        </is>
+      </c>
+      <c r="AP37" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ37" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="AR37" s="2" t="inlineStr"/>
+      <c r="AS37" s="2" t="inlineStr">
+        <is>
+          <t>21528d2dd40eb81f0d101c585a9eb53e9dd572004397a890ae760bf47f3ae0c9</t>
+        </is>
+      </c>
+      <c r="AT37" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU37" s="2" t="inlineStr"/>
+      <c r="AV37" s="2" t="inlineStr">
+        <is>
+          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
+        </is>
+      </c>
+      <c r="AW37" s="2" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:02:10+08:00</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>無足夠資訊表明 Meta Platforms 之信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr"/>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>0.009</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQTm1ESVJlZTFrQ2dzbzNrYXVrSWxNSmpkMkNVa2FKMG1WZ0Q5WDJpemo5dnR4Vzl3TXNORk9pa2hWQWZfUDJxS0ljT28xeW9yN2JyODJFRUZDX21QSVM3Yi1SSkZhNE5yOG4zUEJ1V2VGazJ1M3dQVEZVU2tBY0E5N1BmYlgweGJRUHlXRlRUXzh3b3F1dHdnUUJ6UWU?oc=5</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>36137dc64507e498c5a8b4a3</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr"/>
+      <c r="Y38" s="2" t="inlineStr"/>
+      <c r="Z38" s="2" t="inlineStr"/>
+      <c r="AA38" s="2" t="inlineStr"/>
+      <c r="AB38" s="2" t="inlineStr"/>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD38" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE38" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF38" s="2" t="inlineStr"/>
+      <c r="AG38" s="2" t="inlineStr"/>
+      <c r="AH38" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI38" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ38" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK38" s="2" t="n">
+        <v>1446</v>
+      </c>
+      <c r="AL38" s="2" t="n">
+        <v>76</v>
+      </c>
+      <c r="AM38" s="2" t="inlineStr"/>
+      <c r="AN38" s="2" t="inlineStr"/>
+      <c r="AO38" s="2" t="inlineStr">
+        <is>
+          <t>db841bab92ab7c46294c18f6</t>
+        </is>
+      </c>
+      <c r="AP38" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ38" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR38" s="2" t="inlineStr"/>
+      <c r="AS38" s="2" t="inlineStr">
+        <is>
+          <t>db65943cb30691cbfcfe6b2a7090d142ae715f7a8ef19d34e1151ebf7ddcd53a</t>
+        </is>
+      </c>
+      <c r="AT38" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU38" s="2" t="inlineStr"/>
+      <c r="AV38" s="2" t="inlineStr">
+        <is>
+          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
+        </is>
+      </c>
+      <c r="AW38" s="2" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:23:56+08:00</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 相關的信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>0.011</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T39" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVW91c2d5NHc5a2FWRXBqWktkSEVlTnQ4dzRiT1dYZzNoNUpjQ3dJMUduVzVScDVBbk9Ock5ERGVIRlJtUEQ4WS1GTnF5dFRjTTRKU3Q0RjVhVW13cGhWbmZVcEhuU0lzQ1VKTmJsbF9saWZQa1ZiSVJJRkVBV3BBejdHeUFPVlhhUDROb0N4YVhzdGdzUFNwV05ZLXk?oc=5</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>785b78480c14b20eb1f594f0</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr"/>
+      <c r="Y39" s="2" t="inlineStr"/>
+      <c r="Z39" s="2" t="inlineStr"/>
+      <c r="AA39" s="2" t="inlineStr"/>
+      <c r="AB39" s="2" t="inlineStr"/>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD39" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE39" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF39" s="2" t="inlineStr"/>
+      <c r="AG39" s="2" t="inlineStr"/>
+      <c r="AH39" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI39" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ39" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK39" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="AL39" s="2" t="n">
+        <v>87</v>
+      </c>
+      <c r="AM39" s="2" t="inlineStr"/>
+      <c r="AN39" s="2" t="inlineStr"/>
+      <c r="AO39" s="2" t="inlineStr">
+        <is>
+          <t>5c22badffe5cdc021e3009ee</t>
+        </is>
+      </c>
+      <c r="AP39" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ39" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR39" s="2" t="inlineStr"/>
+      <c r="AS39" s="2" t="inlineStr">
+        <is>
+          <t>3d2f7d8d1cc6978ee5580259eb22d769f60414435b4966fccc4a7efcfab3006b</t>
+        </is>
+      </c>
+      <c r="AT39" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU39" s="2" t="inlineStr"/>
+      <c r="AV39" s="2" t="inlineStr">
+        <is>
+          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="AW39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:40:12+08:00</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>此新聞未提及任何信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNb3BSbEJKZ3ZoRHcwbURvdW96Sm1iS3I5WXNSOWRTdHZJaC1GVWJYaVpuWHVUVVdwbGE3QlVrdlg3VGFrS0tpX05PM3FDVzFpX1FBcnJGT1dmZmxJQ2V6NTV6Uklsci02dFlvNFl1cUVjeDNmNTFjMFJqdEpBcFlPX3otemVOcVlQckNDT2pfZ2lCODZlQnQyWENyZThHQ3RMcmV3Wnh2ZTREeEJhS3R6a045b20xUXByZlpFTg?oc=5</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Barchart.com</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>802f478a954c806c1d45e5e7</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr"/>
+      <c r="Y40" s="2" t="inlineStr"/>
+      <c r="Z40" s="2" t="inlineStr"/>
+      <c r="AA40" s="2" t="inlineStr"/>
+      <c r="AB40" s="2" t="inlineStr"/>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD40" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE40" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF40" s="2" t="inlineStr"/>
+      <c r="AG40" s="2" t="inlineStr"/>
+      <c r="AH40" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI40" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ40" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK40" s="2" t="n">
+        <v>1449</v>
+      </c>
+      <c r="AL40" s="2" t="n">
+        <v>71</v>
+      </c>
+      <c r="AM40" s="2" t="inlineStr"/>
+      <c r="AN40" s="2" t="inlineStr"/>
+      <c r="AO40" s="2" t="inlineStr">
+        <is>
+          <t>7a52a62180c5bc31721f420f</t>
+        </is>
+      </c>
+      <c r="AP40" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ40" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR40" s="2" t="inlineStr"/>
+      <c r="AS40" s="2" t="inlineStr">
+        <is>
+          <t>4f99cded53ff3e3c49b05cb98ccb3dbdabe3155f942fa5ce4ab5675ff0792f09</t>
+        </is>
+      </c>
+      <c r="AT40" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU40" s="2" t="inlineStr"/>
+      <c r="AV40" s="2" t="inlineStr">
+        <is>
+          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
+        </is>
+      </c>
+      <c r="AW40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:33:47+08:00</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 發生任何信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>0.024</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQQXhDOGpZb054SmlrVEdRLUdPNmMxWEhWc3Z1Um9vLWVXZnBrdVJYRWpWSTRaSG1YNC1xcjBnemZlZGEzOGo5NGhvRllmcHRPZm5RMFpQSWdRX1NWRUEzNFpsUzNBclZDem1aT3lYMHpYMHU3NUlSZ3g0dVNBVDJHeDYzMVRHT2FZVEE?oc=5</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Seeking Alpha</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>097dc8c2b12cafa6727c9bbb</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr"/>
+      <c r="Y41" s="2" t="inlineStr"/>
+      <c r="Z41" s="2" t="inlineStr"/>
+      <c r="AA41" s="2" t="inlineStr"/>
+      <c r="AB41" s="2" t="inlineStr"/>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD41" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE41" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF41" s="2" t="inlineStr"/>
+      <c r="AG41" s="2" t="inlineStr"/>
+      <c r="AH41" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI41" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ41" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK41" s="2" t="n">
+        <v>1445</v>
+      </c>
+      <c r="AL41" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AM41" s="2" t="inlineStr"/>
+      <c r="AN41" s="2" t="inlineStr"/>
+      <c r="AO41" s="2" t="inlineStr">
+        <is>
+          <t>2c57a52603540bb61b3bf4fa</t>
+        </is>
+      </c>
+      <c r="AP41" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ41" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR41" s="2" t="inlineStr"/>
+      <c r="AS41" s="2" t="inlineStr">
+        <is>
+          <t>c702ff49b27d3a36cd9fc7128dcc888df5333e430bd9d1a59bb0c0b3297250f2</t>
+        </is>
+      </c>
+      <c r="AT41" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU41" s="2" t="inlineStr"/>
+      <c r="AV41" s="2" t="inlineStr">
+        <is>
+          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
+        </is>
+      </c>
+      <c r="AW41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T22:15:24+08:00</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 將於 11 月 20 日實施新的商業條款，並未涉及任何信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T42" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQYm8yUUVkOEpqVThyY3FUNkxnSEVKT2tzSEpVVnZrci1yYjlKMlZtZHpxeHFYQmlYbzdkRmZzOUl6aGxJeXZNU0x4Ny1QUUtZbnpNc0RfazVMMDA5R0dCdy1nak5DekZMWEVtUTFacWtuWXp2Z2dLTFhsamRjUGRhem94ckVfcHZyalV2ZVVrNnNORnBIdmFPdEYwaVNRcklDbV91RUNyZlo2dGpk?oc=5</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>marketscreener.com</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>9abb1549a2b10e0057938029</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr"/>
+      <c r="Y42" s="2" t="inlineStr"/>
+      <c r="Z42" s="2" t="inlineStr"/>
+      <c r="AA42" s="2" t="inlineStr"/>
+      <c r="AB42" s="2" t="inlineStr"/>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD42" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE42" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF42" s="2" t="inlineStr"/>
+      <c r="AG42" s="2" t="inlineStr"/>
+      <c r="AH42" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI42" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ42" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK42" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="AL42" s="2" t="n">
+        <v>88</v>
+      </c>
+      <c r="AM42" s="2" t="inlineStr"/>
+      <c r="AN42" s="2" t="inlineStr"/>
+      <c r="AO42" s="2" t="inlineStr">
+        <is>
+          <t>b7806ae6c60efbb0fc8012c9</t>
+        </is>
+      </c>
+      <c r="AP42" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ42" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR42" s="2" t="inlineStr"/>
+      <c r="AS42" s="2" t="inlineStr">
+        <is>
+          <t>fa06725b52e12ba1dac5240c7b40621c70203942309f18bf710efb12eb141cfc</t>
+        </is>
+      </c>
+      <c r="AT42" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU42" s="2" t="inlineStr"/>
+      <c r="AV42" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
+        </is>
+      </c>
+      <c r="AW42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T19:01:00+08:00</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>目前無足夠證據顯示 Meta Platforms 相關信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr"/>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>0.079</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T43" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNd2FTR2VVcnNyQXoyWndTa205TWVDOTZhTTdudU0yWUlPMERDXy0zVnRlSHgtNkJRWGJyTEtqUXl0WHZjeUNKYzNWdk5ZeEtnYmZUWjJKbmVfaVVtOTJ0QlhYOWcxSVVabFBKQUtZVF9wM0M4WUU5RXBQT2JRZXZwd0NOWUd1aUoyUC1rVGxyS1g0V3Jvbm5sU1BxX3Fmdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W43" s="2" t="inlineStr">
+        <is>
+          <t>726f56e7556fab9bdf9deab7</t>
+        </is>
+      </c>
+      <c r="X43" s="2" t="inlineStr"/>
+      <c r="Y43" s="2" t="inlineStr"/>
+      <c r="Z43" s="2" t="inlineStr"/>
+      <c r="AA43" s="2" t="inlineStr"/>
+      <c r="AB43" s="2" t="inlineStr"/>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD43" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE43" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF43" s="2" t="inlineStr"/>
+      <c r="AG43" s="2" t="inlineStr"/>
+      <c r="AH43" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI43" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ43" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK43" s="2" t="n">
+        <v>1443</v>
+      </c>
+      <c r="AL43" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="AM43" s="2" t="inlineStr"/>
+      <c r="AN43" s="2" t="inlineStr"/>
+      <c r="AO43" s="2" t="inlineStr">
+        <is>
+          <t>693874aa285dd04e50bb1359</t>
+        </is>
+      </c>
+      <c r="AP43" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ43" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR43" s="2" t="inlineStr"/>
+      <c r="AS43" s="2" t="inlineStr">
+        <is>
+          <t>4ef9cf41dc72910c07585b78c215ad5d73cf5f5066d0f549bf40ee5ecd2443d9</t>
+        </is>
+      </c>
+      <c r="AT43" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU43" s="2" t="inlineStr"/>
+      <c r="AV43" s="2" t="inlineStr">
+        <is>
+          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
+        </is>
+      </c>
+      <c r="AW43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T20:22:37+08:00</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>$Meta Platforms (META.US)$ ...</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>目前無足夠資訊判斷 Meta Platforms 是否存在信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr"/>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>0.148</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>NON_CORE_SOURCE</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T44" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxOMzFhUEtyNm9YNHpPOGRETW0xU0EzXy1PckFJTk9jdFpSbXJIbkVvaVZRNDJMUi16UjRvLVVjMzFoVWZ4aDBFTjZPVmhqem9ndkJWT0hvQzd3alBSVXhTbFB3NVhIVDZTc1pGZzhKNVhGamd5enB1WGJza1dndkF4UUdWa0JfaUhmWjYzVGpBR2RqV2c5Nzk4QVh4bXUwQUJ5VlVNbmhnWTNpVmhiTU85NXlyQUVCYzZ6dF80WWU5RjBRNzBZUjJYcW1NTkUtaEtYSWVOOF91OXdOWmJkOTNGM3pxb1FhVDR0ODhKcWZuc3NqWFQzTXRqbXZWRkZRSmFQaFpJaTJJNEU0NTlHYzFtOG51djlKMzE0NEVyVThtN2Z1OU5tbjMtb3RKMW9rTHdpdmZlazgySXNZdFZra2JLS0lOMmdWbDZOWHVMSVNfcWNfdw?oc=5</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Moomoo</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>8463c439cab6cd0ceeed0259</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr"/>
+      <c r="Y44" s="2" t="inlineStr"/>
+      <c r="Z44" s="2" t="inlineStr"/>
+      <c r="AA44" s="2" t="inlineStr"/>
+      <c r="AB44" s="2" t="inlineStr"/>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD44" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE44" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF44" s="2" t="inlineStr"/>
+      <c r="AG44" s="2" t="inlineStr"/>
+      <c r="AH44" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI44" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ44" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK44" s="2" t="n">
+        <v>1437</v>
+      </c>
+      <c r="AL44" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="AM44" s="2" t="inlineStr"/>
+      <c r="AN44" s="2" t="inlineStr"/>
+      <c r="AO44" s="2" t="inlineStr">
+        <is>
+          <t>50895bc72b56d2d92b44606e</t>
+        </is>
+      </c>
+      <c r="AP44" s="2" t="inlineStr">
+        <is>
+          <t>排除、不納入風險事件</t>
+        </is>
+      </c>
+      <c r="AQ44" s="2" t="inlineStr">
+        <is>
+          <t>非主要公司網站</t>
+        </is>
+      </c>
+      <c r="AR44" s="2" t="inlineStr"/>
+      <c r="AS44" s="2" t="inlineStr">
+        <is>
+          <t>cd41978c9789b32ffc7b5d3c66226f253f4d8249a787a7cdb6610e88ba8266b7</t>
+        </is>
+      </c>
+      <c r="AT44" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU44" s="2" t="inlineStr"/>
+      <c r="AV44" s="2" t="inlineStr">
+        <is>
+          <t>$Meta Platforms (META.US)$ ...</t>
+        </is>
+      </c>
+      <c r="AW44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T16:01:04+08:00</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>小摩上調Meta目標價至940美元</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms 的目標價被小摩上調至 940 美元，並未涉及任何信用風險或違約訊息。</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr"/>
+      <c r="I45" s="2" t="inlineStr"/>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>0.619</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T45" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/news/5330363</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>c0a62dd94e77e5e7c175baf7</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr"/>
+      <c r="Y45" s="2" t="inlineStr"/>
+      <c r="Z45" s="2" t="inlineStr"/>
+      <c r="AA45" s="2" t="inlineStr"/>
+      <c r="AB45" s="2" t="inlineStr"/>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD45" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE45" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF45" s="2" t="inlineStr"/>
+      <c r="AG45" s="2" t="inlineStr"/>
+      <c r="AH45" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI45" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ45" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK45" s="2" t="n">
+        <v>1441</v>
+      </c>
+      <c r="AL45" s="2" t="n">
+        <v>166</v>
+      </c>
+      <c r="AM45" s="2" t="inlineStr"/>
+      <c r="AN45" s="2" t="inlineStr"/>
+      <c r="AO45" s="2" t="inlineStr">
+        <is>
+          <t>f241bb1e8daac06e5ebfd5dd</t>
+        </is>
+      </c>
+      <c r="AP45" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ45" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR45" s="2" t="inlineStr"/>
+      <c r="AS45" s="2" t="inlineStr">
+        <is>
+          <t>2902f0283f78587c48ffddceaf65e4f00ab9320a538b70310b7a65cb2e66c32c</t>
+        </is>
+      </c>
+      <c r="AT45" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU45" s="2" t="inlineStr">
+        <is>
+          <t>小摩上調Meta目標價至940美元</t>
+        </is>
+      </c>
+      <c r="AV45" s="2" t="inlineStr">
+        <is>
+          <t>JPMorgan raised its Meta target price to $940</t>
+        </is>
+      </c>
+      <c r="AW45" s="2" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T09:48:55+08:00</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>目前沒有足夠證據顯示 Meta Platforms 相關的信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr"/>
+      <c r="I46" s="2" t="inlineStr"/>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>方法一</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>0.724</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T46" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.gelonghui.com/live/2725612</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>TradingView</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>8276af8c1e2d6a8b1be57709</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr"/>
+      <c r="Y46" s="2" t="inlineStr"/>
+      <c r="Z46" s="2" t="inlineStr"/>
+      <c r="AA46" s="2" t="inlineStr"/>
+      <c r="AB46" s="2" t="inlineStr"/>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD46" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE46" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF46" s="2" t="inlineStr"/>
+      <c r="AG46" s="2" t="inlineStr"/>
+      <c r="AH46" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI46" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ46" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK46" s="2" t="n">
+        <v>1465</v>
+      </c>
+      <c r="AL46" s="2" t="n">
+        <v>86</v>
+      </c>
+      <c r="AM46" s="2" t="inlineStr"/>
+      <c r="AN46" s="2" t="inlineStr"/>
+      <c r="AO46" s="2" t="inlineStr">
+        <is>
+          <t>062e54352538d735417bc00a</t>
+        </is>
+      </c>
+      <c r="AP46" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ46" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR46" s="2" t="inlineStr"/>
+      <c r="AS46" s="2" t="inlineStr">
+        <is>
+          <t>7a654fc0a5274169b4f9fe947b8b8ec03dde033c6251e2de209d9ba7c3c6001a</t>
+        </is>
+      </c>
+      <c r="AT46" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU46" s="2" t="inlineStr">
+        <is>
+          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
+        </is>
+      </c>
+      <c r="AV46" s="2" t="inlineStr">
+        <is>
+          <t>"The Wolf of Wall Street" Ackman: If the war and inflation cool down, 2027 will be an amazing year</t>
+        </is>
+      </c>
+      <c r="AW46" s="2" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T21:13:19+08:00</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>無足夠證據表明 Meta Platforms 目前存在任何信用風險事件。</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="2" t="inlineStr"/>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>0.899</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T47" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS0s3YXJsQVNHNFBJSGVFUVMtOWwwVlE5UzN2c2V2OFVKOU1UZHJfT0c0Y1dXUHFWdFI0R2JBcGg3ZzJBUmZBSmF6ZHBvS3NyMWp0NklKQWxiTFFYZzRGSmNicFZzTFk0X0lrcFpWZ0VIcFd1Zi1UUVpMX2NlYzJmVEUxTVJrODRzblZvX25IRV9tajluWlBJ?oc=5</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>5774c207e5b4837ece36440d</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr"/>
+      <c r="Y47" s="2" t="inlineStr"/>
+      <c r="Z47" s="2" t="inlineStr"/>
+      <c r="AA47" s="2" t="inlineStr"/>
+      <c r="AB47" s="2" t="inlineStr"/>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD47" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE47" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF47" s="2" t="inlineStr"/>
+      <c r="AG47" s="2" t="inlineStr"/>
+      <c r="AH47" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI47" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ47" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK47" s="2" t="n">
+        <v>1447</v>
+      </c>
+      <c r="AL47" s="2" t="n">
+        <v>79</v>
+      </c>
+      <c r="AM47" s="2" t="inlineStr"/>
+      <c r="AN47" s="2" t="inlineStr"/>
+      <c r="AO47" s="2" t="inlineStr">
+        <is>
+          <t>2ed2364af3d9acea1114881a</t>
+        </is>
+      </c>
+      <c r="AP47" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ47" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR47" s="2" t="inlineStr"/>
+      <c r="AS47" s="2" t="inlineStr">
+        <is>
+          <t>16a4321cafcedd1de655faef6363e09c943abbfca2e21020dcd4978852904046</t>
+        </is>
+      </c>
+      <c r="AT47" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU47" s="2" t="inlineStr"/>
+      <c r="AV47" s="2" t="inlineStr">
+        <is>
+          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
+        </is>
+      </c>
+      <c r="AW47" s="2" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>META</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T23:07:13+08:00</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>此新聞未提及任何與信用風險相關的事件，無法判斷是否存在違約或其他信用風險指標。</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr">
+        <is>
+          <t>LLM</t>
+        </is>
+      </c>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>待人工覆核</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>方法二</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>0.933</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>NOT_RELEVANT</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr">
+        <is>
+          <t>Meta Platforms</t>
+        </is>
+      </c>
+      <c r="T48" s="2" t="inlineStr">
+        <is>
+          <t>公司清單／原始紀錄</t>
+        </is>
+      </c>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOU5uNjZ6MTZvd2dkQlFWUFJ2VW9RdGNmLS12R0x2UDlmMC1jRzBpWmFWNGwzcXFySjFBUzd1V1JSeU5FNGVYdDQzZ1hod1g5SmVOZUw2eTZKTEt0QnpFT0JONTc5eEhHUlNUTHlhMnd6TmF2eW9JX1FzZElGZzRsak1MdVFER2RYVDVJOHVVSnZLSXVzWUNBOFVoU0JfUF9z?oc=5</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Yahoo Finance</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>1662077625e20e4158c6d6d9</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr"/>
+      <c r="Y48" s="2" t="inlineStr"/>
+      <c r="Z48" s="2" t="inlineStr"/>
+      <c r="AA48" s="2" t="inlineStr"/>
+      <c r="AB48" s="2" t="inlineStr"/>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="AD48" s="2" t="inlineStr">
+        <is>
+          <t>UNCLEAR</t>
+        </is>
+      </c>
+      <c r="AE48" s="2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AF48" s="2" t="inlineStr"/>
+      <c r="AG48" s="2" t="inlineStr"/>
+      <c r="AH48" s="2" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+      <c r="AI48" s="2" t="inlineStr">
+        <is>
+          <t>openai/gpt-oss-20b</t>
+        </is>
+      </c>
+      <c r="AJ48" s="2" t="inlineStr">
+        <is>
+          <t>financial_events_v1.0</t>
+        </is>
+      </c>
+      <c r="AK48" s="2" t="n">
+        <v>1450</v>
+      </c>
+      <c r="AL48" s="2" t="n">
+        <v>98</v>
+      </c>
+      <c r="AM48" s="2" t="inlineStr"/>
+      <c r="AN48" s="2" t="inlineStr"/>
+      <c r="AO48" s="2" t="inlineStr">
+        <is>
+          <t>27ae0e4f67d27857be0e98ca</t>
+        </is>
+      </c>
+      <c r="AP48" s="2" t="inlineStr">
+        <is>
+          <t>人工確認</t>
+        </is>
+      </c>
+      <c r="AQ48" s="2" t="inlineStr">
+        <is>
+          <t>無關新聞事件</t>
+        </is>
+      </c>
+      <c r="AR48" s="2" t="inlineStr"/>
+      <c r="AS48" s="2" t="inlineStr">
+        <is>
+          <t>47c1b31266d05ddaa22517da130de1c8045ed17424f50ac7a377447ca0860fa0</t>
+        </is>
+      </c>
+      <c r="AT48" s="2" t="inlineStr">
+        <is>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
+        </is>
+      </c>
+      <c r="AU48" s="2" t="inlineStr"/>
+      <c r="AV48" s="2" t="inlineStr">
+        <is>
+          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
+        </is>
+      </c>
+      <c r="AW48" s="2" t="inlineStr"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AW32"/>
+  <autoFilter ref="A1:AW48"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -19812,7 +23000,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW17"/>
+  <dimension ref="A1:AW1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -20113,2480 +23301,8 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T19:15:00+08:00</t>
-        </is>
-      </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr"/>
-      <c r="H2" s="2" t="inlineStr"/>
-      <c r="I2" s="2" t="inlineStr"/>
-      <c r="J2" s="2" t="inlineStr"/>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>-0.9330000000000001</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr"/>
-      <c r="R2" s="2" t="inlineStr"/>
-      <c r="S2" s="2" t="inlineStr"/>
-      <c r="T2" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U2" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikgFBVV95cUxQeWhsa1VSYXhEM3JSbUNSMEZWTEFqd3A5NGd5SFJWdEZoZmpTRlNzUmM1RVFYT3cwb2JrNzRPMUFfUHlETHI5S1AyajJJdmF0YW5XbnU3MzBGREZOREo4YUszYUl3b3Y1TEdsMXpTWmxqX18zNUlSS2RwcjA0ZkJ6SXo1ek1IcWlhVl9IU1lJTVJqQQ?oc=5</t>
-        </is>
-      </c>
-      <c r="V2" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W2" s="2" t="inlineStr">
-        <is>
-          <t>ec4ba7c19aafcde2fbd710f7</t>
-        </is>
-      </c>
-      <c r="X2" s="2" t="inlineStr"/>
-      <c r="Y2" s="2" t="inlineStr"/>
-      <c r="Z2" s="2" t="inlineStr"/>
-      <c r="AA2" s="2" t="inlineStr"/>
-      <c r="AB2" s="2" t="inlineStr"/>
-      <c r="AC2" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD2" s="2" t="inlineStr"/>
-      <c r="AE2" s="2" t="inlineStr"/>
-      <c r="AF2" s="2" t="inlineStr"/>
-      <c r="AG2" s="2" t="inlineStr"/>
-      <c r="AH2" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI2" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ2" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK2" s="2" t="inlineStr"/>
-      <c r="AL2" s="2" t="inlineStr"/>
-      <c r="AM2" s="2" t="inlineStr"/>
-      <c r="AN2" s="2" t="inlineStr"/>
-      <c r="AO2" s="2" t="inlineStr">
-        <is>
-          <t>0c52c54c8a0e83fbafe6b0e1</t>
-        </is>
-      </c>
-      <c r="AP2" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ2" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="AR2" s="2" t="inlineStr"/>
-      <c r="AS2" s="2" t="inlineStr">
-        <is>
-          <t>703f213218315ca169df93ed957d57b06b6c1dd9d90f95dcae08448b5366a4d2</t>
-        </is>
-      </c>
-      <c r="AT2" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU2" s="2" t="inlineStr"/>
-      <c r="AV2" s="2" t="inlineStr">
-        <is>
-          <t>ETFs in Focus as META Drops 7% Despite Q3 Earnings Beat, Strong View</t>
-        </is>
-      </c>
-      <c r="AW2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T00:30:04+08:00</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr"/>
-      <c r="I3" s="2" t="inlineStr"/>
-      <c r="J3" s="2" t="inlineStr"/>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>方法一</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>-0.873</v>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>ANTITRUST_INVESTIGATION</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
-      <c r="S3" s="2" t="inlineStr"/>
-      <c r="T3" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U3" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2724913</t>
-        </is>
-      </c>
-      <c r="V3" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W3" s="2" t="inlineStr">
-        <is>
-          <t>d1348ad94c5e9aa7d9188003</t>
-        </is>
-      </c>
-      <c r="X3" s="2" t="inlineStr"/>
-      <c r="Y3" s="2" t="inlineStr"/>
-      <c r="Z3" s="2" t="inlineStr"/>
-      <c r="AA3" s="2" t="inlineStr"/>
-      <c r="AB3" s="2" t="inlineStr"/>
-      <c r="AC3" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD3" s="2" t="inlineStr"/>
-      <c r="AE3" s="2" t="inlineStr"/>
-      <c r="AF3" s="2" t="inlineStr"/>
-      <c r="AG3" s="2" t="inlineStr"/>
-      <c r="AH3" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI3" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ3" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK3" s="2" t="inlineStr"/>
-      <c r="AL3" s="2" t="inlineStr"/>
-      <c r="AM3" s="2" t="inlineStr"/>
-      <c r="AN3" s="2" t="inlineStr"/>
-      <c r="AO3" s="2" t="inlineStr">
-        <is>
-          <t>2ff90a8d58ba249a9252028a</t>
-        </is>
-      </c>
-      <c r="AP3" s="2" t="inlineStr">
-        <is>
-          <t>通知、檢視授信及自營部位、持續追蹤</t>
-        </is>
-      </c>
-      <c r="AQ3" s="2" t="inlineStr">
-        <is>
-          <t>反壟斷調查</t>
-        </is>
-      </c>
-      <c r="AR3" s="2" t="inlineStr"/>
-      <c r="AS3" s="2" t="inlineStr">
-        <is>
-          <t>3b9ae9feaec50aeeb331e95a5ee2a1e3c8322512f70ac97854f13f8a8a230dbf</t>
-        </is>
-      </c>
-      <c r="AT3" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU3" s="2" t="inlineStr">
-        <is>
-          <t>出版商和廣吿商呼籲歐盟和英國反壟斷監管機構暫停Meta的新商業條款</t>
-        </is>
-      </c>
-      <c r="AV3" s="2" t="inlineStr">
-        <is>
-          <t>Publishers and advertisers call on EU and UK antitrust regulators to suspend Meta's new business terms</t>
-        </is>
-      </c>
-      <c r="AW3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T20:24:10+08:00</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>巴西總統指控Meta操縱大選</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr"/>
-      <c r="I4" s="2" t="inlineStr"/>
-      <c r="J4" s="2" t="inlineStr"/>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>方法一</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>-0.824</v>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-      <c r="S4" s="2" t="inlineStr"/>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2726833</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W4" s="2" t="inlineStr">
-        <is>
-          <t>f25a40e5e491828684fad933</t>
-        </is>
-      </c>
-      <c r="X4" s="2" t="inlineStr"/>
-      <c r="Y4" s="2" t="inlineStr"/>
-      <c r="Z4" s="2" t="inlineStr"/>
-      <c r="AA4" s="2" t="inlineStr"/>
-      <c r="AB4" s="2" t="inlineStr"/>
-      <c r="AC4" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD4" s="2" t="inlineStr"/>
-      <c r="AE4" s="2" t="inlineStr"/>
-      <c r="AF4" s="2" t="inlineStr"/>
-      <c r="AG4" s="2" t="inlineStr"/>
-      <c r="AH4" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI4" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ4" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK4" s="2" t="inlineStr"/>
-      <c r="AL4" s="2" t="inlineStr"/>
-      <c r="AM4" s="2" t="inlineStr"/>
-      <c r="AN4" s="2" t="inlineStr"/>
-      <c r="AO4" s="2" t="inlineStr">
-        <is>
-          <t>0e55b465fd7b98d6d05db82c</t>
-        </is>
-      </c>
-      <c r="AP4" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ4" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="AR4" s="2" t="inlineStr"/>
-      <c r="AS4" s="2" t="inlineStr">
-        <is>
-          <t>1f1b7d07ae6f5f91e714914b3b662be882027be3a6ebc1733cfc29a4f725c9d0</t>
-        </is>
-      </c>
-      <c r="AT4" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU4" s="2" t="inlineStr">
-        <is>
-          <t>巴西總統指控Meta操縱大選</t>
-        </is>
-      </c>
-      <c r="AV4" s="2" t="inlineStr">
-        <is>
-          <t>Brazilian president accuses Meta of rigging election</t>
-        </is>
-      </c>
-      <c r="AW4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T14:15:46+08:00</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
-      <c r="J5" s="2" t="inlineStr"/>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>方法一</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>-0.745</v>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-      <c r="S5" s="2" t="inlineStr"/>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>https://tw.tradingview.com/symbols/NASDAQ-META/news/</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>a37f44666d6b93b23fa84c03</t>
-        </is>
-      </c>
-      <c r="X5" s="2" t="inlineStr"/>
-      <c r="Y5" s="2" t="inlineStr"/>
-      <c r="Z5" s="2" t="inlineStr"/>
-      <c r="AA5" s="2" t="inlineStr"/>
-      <c r="AB5" s="2" t="inlineStr"/>
-      <c r="AC5" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD5" s="2" t="inlineStr"/>
-      <c r="AE5" s="2" t="inlineStr"/>
-      <c r="AF5" s="2" t="inlineStr"/>
-      <c r="AG5" s="2" t="inlineStr"/>
-      <c r="AH5" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI5" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ5" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK5" s="2" t="inlineStr"/>
-      <c r="AL5" s="2" t="inlineStr"/>
-      <c r="AM5" s="2" t="inlineStr"/>
-      <c r="AN5" s="2" t="inlineStr"/>
-      <c r="AO5" s="2" t="inlineStr">
-        <is>
-          <t>c9eb84ac77729681440eb57a</t>
-        </is>
-      </c>
-      <c r="AP5" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ5" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="AR5" s="2" t="inlineStr"/>
-      <c r="AS5" s="2" t="inlineStr">
-        <is>
-          <t>1f591b90e9b440b67c36a5eb4472a728985b298e24dc706d0798748c6426b66a</t>
-        </is>
-      </c>
-      <c r="AT5" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU5" s="2" t="inlineStr">
-        <is>
-          <t>希臘通過針對15歲以下兒童的社交媒體禁令</t>
-        </is>
-      </c>
-      <c r="AV5" s="2" t="inlineStr">
-        <is>
-          <t>Greece passes social media ban for children under 15</t>
-        </is>
-      </c>
-      <c r="AW5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T18:13:48+08:00</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>-0.378</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>UNKNOWN</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-      <c r="S6" s="2" t="inlineStr"/>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMikwFBVV95cUxON0pWLThkWllqVTRvcVRMY1NVeUN0UVNxa08tNkRhbzQxTUFlaTZON1BOYkh4bDEtaHB4X2d6dHk3VS1sVDhYMEhhZ0IyMVpjTXJjWVJ3WE9ZTDdWWG9paC1zdHZpbFpFNVZNTk9aYXhQRnRtWVlXRE0tZ2hOaDFmc2RIQUV5aTRBbEJaaDNsWUNxUXc?oc=5</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>464a7cf6ed8a0d8eb8b7128c</t>
-        </is>
-      </c>
-      <c r="X6" s="2" t="inlineStr"/>
-      <c r="Y6" s="2" t="inlineStr"/>
-      <c r="Z6" s="2" t="inlineStr"/>
-      <c r="AA6" s="2" t="inlineStr"/>
-      <c r="AB6" s="2" t="inlineStr"/>
-      <c r="AC6" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD6" s="2" t="inlineStr"/>
-      <c r="AE6" s="2" t="inlineStr"/>
-      <c r="AF6" s="2" t="inlineStr"/>
-      <c r="AG6" s="2" t="inlineStr"/>
-      <c r="AH6" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI6" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ6" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK6" s="2" t="inlineStr"/>
-      <c r="AL6" s="2" t="inlineStr"/>
-      <c r="AM6" s="2" t="inlineStr"/>
-      <c r="AN6" s="2" t="inlineStr"/>
-      <c r="AO6" s="2" t="inlineStr">
-        <is>
-          <t>2030e51b7ee960a291545c4e</t>
-        </is>
-      </c>
-      <c r="AP6" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ6" s="2" t="inlineStr">
-        <is>
-          <t>待人工覆核</t>
-        </is>
-      </c>
-      <c r="AR6" s="2" t="inlineStr"/>
-      <c r="AS6" s="2" t="inlineStr">
-        <is>
-          <t>70d3c8f7cedf509a0d49a31d514c14f40cdbe72f4eeffa852820c7c46d87a158</t>
-        </is>
-      </c>
-      <c r="AT6" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU6" s="2" t="inlineStr"/>
-      <c r="AV6" s="2" t="inlineStr">
-        <is>
-          <t>Nasdaq, Dow, S&amp;P 500 Futures Drop Premarket: NVDA, AMD, META, CRWV, MRNA, WDC, BE In Focus</t>
-        </is>
-      </c>
-      <c r="AW6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T19:02:10+08:00</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
-      <c r="J7" s="2" t="inlineStr"/>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0.008999999999999999</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-      <c r="S7" s="2" t="inlineStr"/>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQTm1ESVJlZTFrQ2dzbzNrYXVrSWxNSmpkMkNVa2FKMG1WZ0Q5WDJpemo5dnR4Vzl3TXNORk9pa2hWQWZfUDJxS0ljT28xeW9yN2JyODJFRUZDX21QSVM3Yi1SSkZhNE5yOG4zUEJ1V2VGazJ1M3dQVEZVU2tBY0E5N1BmYlgweGJRUHlXRlRUXzh3b3F1dHdnUUJ6UWU?oc=5</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>36137dc64507e498c5a8b4a3</t>
-        </is>
-      </c>
-      <c r="X7" s="2" t="inlineStr"/>
-      <c r="Y7" s="2" t="inlineStr"/>
-      <c r="Z7" s="2" t="inlineStr"/>
-      <c r="AA7" s="2" t="inlineStr"/>
-      <c r="AB7" s="2" t="inlineStr"/>
-      <c r="AC7" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD7" s="2" t="inlineStr"/>
-      <c r="AE7" s="2" t="inlineStr"/>
-      <c r="AF7" s="2" t="inlineStr"/>
-      <c r="AG7" s="2" t="inlineStr"/>
-      <c r="AH7" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI7" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ7" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK7" s="2" t="inlineStr"/>
-      <c r="AL7" s="2" t="inlineStr"/>
-      <c r="AM7" s="2" t="inlineStr"/>
-      <c r="AN7" s="2" t="inlineStr"/>
-      <c r="AO7" s="2" t="inlineStr">
-        <is>
-          <t>db841bab92ab7c46294c18f6</t>
-        </is>
-      </c>
-      <c r="AP7" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ7" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR7" s="2" t="inlineStr"/>
-      <c r="AS7" s="2" t="inlineStr">
-        <is>
-          <t>e75e8c8129bbdb2191154bec165f56eaf1d00c270b682a696164f93458fff26e</t>
-        </is>
-      </c>
-      <c r="AT7" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU7" s="2" t="inlineStr"/>
-      <c r="AV7" s="2" t="inlineStr">
-        <is>
-          <t>ETFs Are Net Sellers of Meta Platforms (META) on Oct. 21</t>
-        </is>
-      </c>
-      <c r="AW7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T22:23:56+08:00</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="n">
-        <v>0.011</v>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr"/>
-      <c r="R8" s="2" t="inlineStr"/>
-      <c r="S8" s="2" t="inlineStr"/>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPVW91c2d5NHc5a2FWRXBqWktkSEVlTnQ4dzRiT1dYZzNoNUpjQ3dJMUduVzVScDVBbk9Ock5ERGVIRlJtUEQ4WS1GTnF5dFRjTTRKU3Q0RjVhVW13cGhWbmZVcEhuU0lzQ1VKTmJsbF9saWZQa1ZiSVJJRkVBV3BBejdHeUFPVlhhUDROb0N4YVhzdGdzUFNwV05ZLXk?oc=5</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>785b78480c14b20eb1f594f0</t>
-        </is>
-      </c>
-      <c r="X8" s="2" t="inlineStr"/>
-      <c r="Y8" s="2" t="inlineStr"/>
-      <c r="Z8" s="2" t="inlineStr"/>
-      <c r="AA8" s="2" t="inlineStr"/>
-      <c r="AB8" s="2" t="inlineStr"/>
-      <c r="AC8" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD8" s="2" t="inlineStr"/>
-      <c r="AE8" s="2" t="inlineStr"/>
-      <c r="AF8" s="2" t="inlineStr"/>
-      <c r="AG8" s="2" t="inlineStr"/>
-      <c r="AH8" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI8" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ8" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK8" s="2" t="inlineStr"/>
-      <c r="AL8" s="2" t="inlineStr"/>
-      <c r="AM8" s="2" t="inlineStr"/>
-      <c r="AN8" s="2" t="inlineStr"/>
-      <c r="AO8" s="2" t="inlineStr">
-        <is>
-          <t>5c22badffe5cdc021e3009ee</t>
-        </is>
-      </c>
-      <c r="AP8" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ8" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR8" s="2" t="inlineStr"/>
-      <c r="AS8" s="2" t="inlineStr">
-        <is>
-          <t>6d610b7eb950150470f57c0b234a95303c318c7975b534d2cd2e804370ec4b99</t>
-        </is>
-      </c>
-      <c r="AT8" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU8" s="2" t="inlineStr"/>
-      <c r="AV8" s="2" t="inlineStr">
-        <is>
-          <t>Meta: AI Spending Is Exploding, But So Is The Opportunity (NASDAQ:META)</t>
-        </is>
-      </c>
-      <c r="AW8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T19:40:12+08:00</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="2" t="inlineStr"/>
-      <c r="J9" s="2" t="inlineStr"/>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>NON_CORE_SOURCE</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-      <c r="S9" s="2" t="inlineStr"/>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxNb3BSbEJKZ3ZoRHcwbURvdW96Sm1iS3I5WXNSOWRTdHZJaC1GVWJYaVpuWHVUVVdwbGE3QlVrdlg3VGFrS0tpX05PM3FDVzFpX1FBcnJGT1dmZmxJQ2V6NTV6Uklsci02dFlvNFl1cUVjeDNmNTFjMFJqdEpBcFlPX3otemVOcVlQckNDT2pfZ2lCODZlQnQyWENyZThHQ3RMcmV3Wnh2ZTREeEJhS3R6a045b20xUXByZlpFTg?oc=5</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>Barchart.com</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>802f478a954c806c1d45e5e7</t>
-        </is>
-      </c>
-      <c r="X9" s="2" t="inlineStr"/>
-      <c r="Y9" s="2" t="inlineStr"/>
-      <c r="Z9" s="2" t="inlineStr"/>
-      <c r="AA9" s="2" t="inlineStr"/>
-      <c r="AB9" s="2" t="inlineStr"/>
-      <c r="AC9" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD9" s="2" t="inlineStr"/>
-      <c r="AE9" s="2" t="inlineStr"/>
-      <c r="AF9" s="2" t="inlineStr"/>
-      <c r="AG9" s="2" t="inlineStr"/>
-      <c r="AH9" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI9" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ9" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK9" s="2" t="inlineStr"/>
-      <c r="AL9" s="2" t="inlineStr"/>
-      <c r="AM9" s="2" t="inlineStr"/>
-      <c r="AN9" s="2" t="inlineStr"/>
-      <c r="AO9" s="2" t="inlineStr">
-        <is>
-          <t>7a52a62180c5bc31721f420f</t>
-        </is>
-      </c>
-      <c r="AP9" s="2" t="inlineStr">
-        <is>
-          <t>排除、不納入風險事件</t>
-        </is>
-      </c>
-      <c r="AQ9" s="2" t="inlineStr">
-        <is>
-          <t>非主要公司網站</t>
-        </is>
-      </c>
-      <c r="AR9" s="2" t="inlineStr"/>
-      <c r="AS9" s="2" t="inlineStr">
-        <is>
-          <t>61557616d68c76cf4c34a0623191d34058d3274ed70d8fc1e86334c98f7433ca</t>
-        </is>
-      </c>
-      <c r="AT9" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU9" s="2" t="inlineStr"/>
-      <c r="AV9" s="2" t="inlineStr">
-        <is>
-          <t>Buy, Sell, or Hold: How to Play Meta Platforms Stock After Its Q3 Earnings Beat</t>
-        </is>
-      </c>
-      <c r="AW9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T22:33:47+08:00</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="2" t="inlineStr"/>
-      <c r="J10" s="2" t="inlineStr"/>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.024</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-      <c r="S10" s="2" t="inlineStr"/>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiigFBVV95cUxQQXhDOGpZb054SmlrVEdRLUdPNmMxWEhWc3Z1Um9vLWVXZnBrdVJYRWpWSTRaSG1YNC1xcjBnemZlZGEzOGo5NGhvRllmcHRPZm5RMFpQSWdRX1NWRUEzNFpsUzNBclZDem1aT3lYMHpYMHU3NUlSZ3g0dVNBVDJHeDYzMVRHT2FZVEE?oc=5</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>Seeking Alpha</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>097dc8c2b12cafa6727c9bbb</t>
-        </is>
-      </c>
-      <c r="X10" s="2" t="inlineStr"/>
-      <c r="Y10" s="2" t="inlineStr"/>
-      <c r="Z10" s="2" t="inlineStr"/>
-      <c r="AA10" s="2" t="inlineStr"/>
-      <c r="AB10" s="2" t="inlineStr"/>
-      <c r="AC10" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD10" s="2" t="inlineStr"/>
-      <c r="AE10" s="2" t="inlineStr"/>
-      <c r="AF10" s="2" t="inlineStr"/>
-      <c r="AG10" s="2" t="inlineStr"/>
-      <c r="AH10" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI10" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ10" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK10" s="2" t="inlineStr"/>
-      <c r="AL10" s="2" t="inlineStr"/>
-      <c r="AM10" s="2" t="inlineStr"/>
-      <c r="AN10" s="2" t="inlineStr"/>
-      <c r="AO10" s="2" t="inlineStr">
-        <is>
-          <t>2c57a52603540bb61b3bf4fa</t>
-        </is>
-      </c>
-      <c r="AP10" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ10" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR10" s="2" t="inlineStr"/>
-      <c r="AS10" s="2" t="inlineStr">
-        <is>
-          <t>b36d9804e90e3ff91df4cf736f0b68d3b88ee6026366e5b8f3336a9db6b54010</t>
-        </is>
-      </c>
-      <c r="AT10" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU10" s="2" t="inlineStr"/>
-      <c r="AV10" s="2" t="inlineStr">
-        <is>
-          <t>Meta: Ignore The FCF Noise And Buy The Dip (NASDAQ:META)</t>
-        </is>
-      </c>
-      <c r="AW10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T22:15:24+08:00</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="2" t="inlineStr"/>
-      <c r="J11" s="2" t="inlineStr"/>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>NON_CORE_SOURCE</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-      <c r="S11" s="2" t="inlineStr"/>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxQYm8yUUVkOEpqVThyY3FUNkxnSEVKT2tzSEpVVnZrci1yYjlKMlZtZHpxeHFYQmlYbzdkRmZzOUl6aGxJeXZNU0x4Ny1QUUtZbnpNc0RfazVMMDA5R0dCdy1nak5DekZMWEVtUTFacWtuWXp2Z2dLTFhsamRjUGRhem94ckVfcHZyalV2ZVVrNnNORnBIdmFPdEYwaVNRcklDbV91RUNyZlo2dGpk?oc=5</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>marketscreener.com</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>9abb1549a2b10e0057938029</t>
-        </is>
-      </c>
-      <c r="X11" s="2" t="inlineStr"/>
-      <c r="Y11" s="2" t="inlineStr"/>
-      <c r="Z11" s="2" t="inlineStr"/>
-      <c r="AA11" s="2" t="inlineStr"/>
-      <c r="AB11" s="2" t="inlineStr"/>
-      <c r="AC11" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD11" s="2" t="inlineStr"/>
-      <c r="AE11" s="2" t="inlineStr"/>
-      <c r="AF11" s="2" t="inlineStr"/>
-      <c r="AG11" s="2" t="inlineStr"/>
-      <c r="AH11" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI11" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ11" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK11" s="2" t="inlineStr"/>
-      <c r="AL11" s="2" t="inlineStr"/>
-      <c r="AM11" s="2" t="inlineStr"/>
-      <c r="AN11" s="2" t="inlineStr"/>
-      <c r="AO11" s="2" t="inlineStr">
-        <is>
-          <t>b7806ae6c60efbb0fc8012c9</t>
-        </is>
-      </c>
-      <c r="AP11" s="2" t="inlineStr">
-        <is>
-          <t>排除、不納入風險事件</t>
-        </is>
-      </c>
-      <c r="AQ11" s="2" t="inlineStr">
-        <is>
-          <t>非主要公司網站</t>
-        </is>
-      </c>
-      <c r="AR11" s="2" t="inlineStr"/>
-      <c r="AS11" s="2" t="inlineStr">
-        <is>
-          <t>7460bf9f6be0b4f2f93f68a081035b7483fdc8361ea4c7c337c2c96d815d773e</t>
-        </is>
-      </c>
-      <c r="AT11" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU11" s="2" t="inlineStr"/>
-      <c r="AV11" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms to Implement New Commercial Terms Nov. 20</t>
-        </is>
-      </c>
-      <c r="AW11" s="2" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T19:01:00+08:00</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr"/>
-      <c r="I12" s="2" t="inlineStr"/>
-      <c r="J12" s="2" t="inlineStr"/>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O12" s="2" t="n">
-        <v>0.079</v>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr"/>
-      <c r="R12" s="2" t="inlineStr"/>
-      <c r="S12" s="2" t="inlineStr"/>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxNd2FTR2VVcnNyQXoyWndTa205TWVDOTZhTTdudU0yWUlPMERDXy0zVnRlSHgtNkJRWGJyTEtqUXl0WHZjeUNKYzNWdk5ZeEtnYmZUWjJKbmVfaVVtOTJ0QlhYOWcxSVVabFBKQUtZVF9wM0M4WUU5RXBQT2JRZXZwd0NOWUd1aUoyUC1rVGxyS1g0V3Jvbm5sU1BxX3Fmdw?oc=5</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>726f56e7556fab9bdf9deab7</t>
-        </is>
-      </c>
-      <c r="X12" s="2" t="inlineStr"/>
-      <c r="Y12" s="2" t="inlineStr"/>
-      <c r="Z12" s="2" t="inlineStr"/>
-      <c r="AA12" s="2" t="inlineStr"/>
-      <c r="AB12" s="2" t="inlineStr"/>
-      <c r="AC12" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD12" s="2" t="inlineStr"/>
-      <c r="AE12" s="2" t="inlineStr"/>
-      <c r="AF12" s="2" t="inlineStr"/>
-      <c r="AG12" s="2" t="inlineStr"/>
-      <c r="AH12" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI12" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ12" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK12" s="2" t="inlineStr"/>
-      <c r="AL12" s="2" t="inlineStr"/>
-      <c r="AM12" s="2" t="inlineStr"/>
-      <c r="AN12" s="2" t="inlineStr"/>
-      <c r="AO12" s="2" t="inlineStr">
-        <is>
-          <t>693874aa285dd04e50bb1359</t>
-        </is>
-      </c>
-      <c r="AP12" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ12" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR12" s="2" t="inlineStr"/>
-      <c r="AS12" s="2" t="inlineStr">
-        <is>
-          <t>0517b27ea681c43f5c5a7dc8767c5d0bfb6b5ca885d47a82bbe3196b354fc837</t>
-        </is>
-      </c>
-      <c r="AT12" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU12" s="2" t="inlineStr"/>
-      <c r="AV12" s="2" t="inlineStr">
-        <is>
-          <t>Is Meta Platforms Stock a Buy as Revenue Continues to Soar?</t>
-        </is>
-      </c>
-      <c r="AW12" s="2" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T20:22:37+08:00</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>$Meta Platforms (META.US)$ ...</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="2" t="inlineStr"/>
-      <c r="J13" s="2" t="inlineStr"/>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>NON_CORE_SOURCE</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr"/>
-      <c r="R13" s="2" t="inlineStr"/>
-      <c r="S13" s="2" t="inlineStr"/>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMi0gJBVV95cUxOMzFhUEtyNm9YNHpPOGRETW0xU0EzXy1PckFJTk9jdFpSbXJIbkVvaVZRNDJMUi16UjRvLVVjMzFoVWZ4aDBFTjZPVmhqem9ndkJWT0hvQzd3alBSVXhTbFB3NVhIVDZTc1pGZzhKNVhGamd5enB1WGJza1dndkF4UUdWa0JfaUhmWjYzVGpBR2RqV2c5Nzk4QVh4bXUwQUJ5VlVNbmhnWTNpVmhiTU85NXlyQUVCYzZ6dF80WWU5RjBRNzBZUjJYcW1NTkUtaEtYSWVOOF91OXdOWmJkOTNGM3pxb1FhVDR0ODhKcWZuc3NqWFQzTXRqbXZWRkZRSmFQaFpJaTJJNEU0NTlHYzFtOG51djlKMzE0NEVyVThtN2Z1OU5tbjMtb3RKMW9rTHdpdmZlazgySXNZdFZra2JLS0lOMmdWbDZOWHVMSVNfcWNfdw?oc=5</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>Moomoo</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>8463c439cab6cd0ceeed0259</t>
-        </is>
-      </c>
-      <c r="X13" s="2" t="inlineStr"/>
-      <c r="Y13" s="2" t="inlineStr"/>
-      <c r="Z13" s="2" t="inlineStr"/>
-      <c r="AA13" s="2" t="inlineStr"/>
-      <c r="AB13" s="2" t="inlineStr"/>
-      <c r="AC13" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD13" s="2" t="inlineStr"/>
-      <c r="AE13" s="2" t="inlineStr"/>
-      <c r="AF13" s="2" t="inlineStr"/>
-      <c r="AG13" s="2" t="inlineStr"/>
-      <c r="AH13" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI13" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ13" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK13" s="2" t="inlineStr"/>
-      <c r="AL13" s="2" t="inlineStr"/>
-      <c r="AM13" s="2" t="inlineStr"/>
-      <c r="AN13" s="2" t="inlineStr"/>
-      <c r="AO13" s="2" t="inlineStr">
-        <is>
-          <t>50895bc72b56d2d92b44606e</t>
-        </is>
-      </c>
-      <c r="AP13" s="2" t="inlineStr">
-        <is>
-          <t>排除、不納入風險事件</t>
-        </is>
-      </c>
-      <c r="AQ13" s="2" t="inlineStr">
-        <is>
-          <t>非主要公司網站</t>
-        </is>
-      </c>
-      <c r="AR13" s="2" t="inlineStr"/>
-      <c r="AS13" s="2" t="inlineStr">
-        <is>
-          <t>39a874f75cef45cadda21059624f246da76bcea88d3705c5c291469f18417643</t>
-        </is>
-      </c>
-      <c r="AT13" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU13" s="2" t="inlineStr"/>
-      <c r="AV13" s="2" t="inlineStr">
-        <is>
-          <t>$Meta Platforms (META.US)$ ...</t>
-        </is>
-      </c>
-      <c r="AW13" s="2" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T16:01:04+08:00</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>小摩上調Meta目標價至940美元</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="2" t="inlineStr"/>
-      <c r="J14" s="2" t="inlineStr"/>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>方法一</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0.619</v>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr"/>
-      <c r="R14" s="2" t="inlineStr"/>
-      <c r="S14" s="2" t="inlineStr"/>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/news/5330363</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>c0a62dd94e77e5e7c175baf7</t>
-        </is>
-      </c>
-      <c r="X14" s="2" t="inlineStr"/>
-      <c r="Y14" s="2" t="inlineStr"/>
-      <c r="Z14" s="2" t="inlineStr"/>
-      <c r="AA14" s="2" t="inlineStr"/>
-      <c r="AB14" s="2" t="inlineStr"/>
-      <c r="AC14" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD14" s="2" t="inlineStr"/>
-      <c r="AE14" s="2" t="inlineStr"/>
-      <c r="AF14" s="2" t="inlineStr"/>
-      <c r="AG14" s="2" t="inlineStr"/>
-      <c r="AH14" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI14" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ14" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK14" s="2" t="inlineStr"/>
-      <c r="AL14" s="2" t="inlineStr"/>
-      <c r="AM14" s="2" t="inlineStr"/>
-      <c r="AN14" s="2" t="inlineStr"/>
-      <c r="AO14" s="2" t="inlineStr">
-        <is>
-          <t>f241bb1e8daac06e5ebfd5dd</t>
-        </is>
-      </c>
-      <c r="AP14" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ14" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR14" s="2" t="inlineStr"/>
-      <c r="AS14" s="2" t="inlineStr">
-        <is>
-          <t>3fb9a23409e8708ea25ee8cb1bc2c57d982f0b2f9aece44cf25ef07e40b312e8</t>
-        </is>
-      </c>
-      <c r="AT14" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU14" s="2" t="inlineStr">
-        <is>
-          <t>小摩上調Meta目標價至940美元</t>
-        </is>
-      </c>
-      <c r="AV14" s="2" t="inlineStr">
-        <is>
-          <t>JPMorgan raised its Meta target price to $940</t>
-        </is>
-      </c>
-      <c r="AW14" s="2" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T09:48:55+08:00</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="2" t="inlineStr"/>
-      <c r="J15" s="2" t="inlineStr"/>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N15" s="2" t="inlineStr">
-        <is>
-          <t>方法一</t>
-        </is>
-      </c>
-      <c r="O15" s="2" t="n">
-        <v>0.724</v>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q15" s="2" t="inlineStr"/>
-      <c r="R15" s="2" t="inlineStr"/>
-      <c r="S15" s="2" t="inlineStr"/>
-      <c r="T15" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.gelonghui.com/live/2725612</t>
-        </is>
-      </c>
-      <c r="V15" s="2" t="inlineStr">
-        <is>
-          <t>TradingView</t>
-        </is>
-      </c>
-      <c r="W15" s="2" t="inlineStr">
-        <is>
-          <t>8276af8c1e2d6a8b1be57709</t>
-        </is>
-      </c>
-      <c r="X15" s="2" t="inlineStr"/>
-      <c r="Y15" s="2" t="inlineStr"/>
-      <c r="Z15" s="2" t="inlineStr"/>
-      <c r="AA15" s="2" t="inlineStr"/>
-      <c r="AB15" s="2" t="inlineStr"/>
-      <c r="AC15" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD15" s="2" t="inlineStr"/>
-      <c r="AE15" s="2" t="inlineStr"/>
-      <c r="AF15" s="2" t="inlineStr"/>
-      <c r="AG15" s="2" t="inlineStr"/>
-      <c r="AH15" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI15" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ15" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK15" s="2" t="inlineStr"/>
-      <c r="AL15" s="2" t="inlineStr"/>
-      <c r="AM15" s="2" t="inlineStr"/>
-      <c r="AN15" s="2" t="inlineStr"/>
-      <c r="AO15" s="2" t="inlineStr">
-        <is>
-          <t>062e54352538d735417bc00a</t>
-        </is>
-      </c>
-      <c r="AP15" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ15" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR15" s="2" t="inlineStr"/>
-      <c r="AS15" s="2" t="inlineStr">
-        <is>
-          <t>4b5ef37f6c305b434f4c1c87831cc70b581ac080fa1eb75cf03d769479d206b7</t>
-        </is>
-      </c>
-      <c r="AT15" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU15" s="2" t="inlineStr">
-        <is>
-          <t>“華爾街之狼”阿克曼：若戰爭與通脹降温，2027年將是令人驚豔的一年</t>
-        </is>
-      </c>
-      <c r="AV15" s="2" t="inlineStr">
-        <is>
-          <t>"The Wolf of Wall Street" Ackman: If the war and inflation cool down, 2027 will be an amazing year</t>
-        </is>
-      </c>
-      <c r="AW15" s="2" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T21:13:19+08:00</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="2" t="inlineStr"/>
-      <c r="J16" s="2" t="inlineStr"/>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="n">
-        <v>0.899</v>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr"/>
-      <c r="R16" s="2" t="inlineStr"/>
-      <c r="S16" s="2" t="inlineStr"/>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMilwFBVV95cUxNS0s3YXJsQVNHNFBJSGVFUVMtOWwwVlE5UzN2c2V2OFVKOU1UZHJfT0c0Y1dXUHFWdFI0R2JBcGg3ZzJBUmZBSmF6ZHBvS3NyMWp0NklKQWxiTFFYZzRGSmNicFZzTFk0X0lrcFpWZ0VIcFd1Zi1UUVpMX2NlYzJmVEUxTVJrODRzblZvX25IRV9tajluWlBJ?oc=5</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W16" s="2" t="inlineStr">
-        <is>
-          <t>5774c207e5b4837ece36440d</t>
-        </is>
-      </c>
-      <c r="X16" s="2" t="inlineStr"/>
-      <c r="Y16" s="2" t="inlineStr"/>
-      <c r="Z16" s="2" t="inlineStr"/>
-      <c r="AA16" s="2" t="inlineStr"/>
-      <c r="AB16" s="2" t="inlineStr"/>
-      <c r="AC16" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD16" s="2" t="inlineStr"/>
-      <c r="AE16" s="2" t="inlineStr"/>
-      <c r="AF16" s="2" t="inlineStr"/>
-      <c r="AG16" s="2" t="inlineStr"/>
-      <c r="AH16" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI16" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ16" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK16" s="2" t="inlineStr"/>
-      <c r="AL16" s="2" t="inlineStr"/>
-      <c r="AM16" s="2" t="inlineStr"/>
-      <c r="AN16" s="2" t="inlineStr"/>
-      <c r="AO16" s="2" t="inlineStr">
-        <is>
-          <t>2ed2364af3d9acea1114881a</t>
-        </is>
-      </c>
-      <c r="AP16" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ16" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR16" s="2" t="inlineStr"/>
-      <c r="AS16" s="2" t="inlineStr">
-        <is>
-          <t>29d466f90bfdbdf0f7a04f87c9e7bf26725f4409800afedde98bde36f1864b93</t>
-        </is>
-      </c>
-      <c r="AT16" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU16" s="2" t="inlineStr"/>
-      <c r="AV16" s="2" t="inlineStr">
-        <is>
-          <t>Meta (META) Stock Seems Fully Valued Despite Its 127% Three Year Run</t>
-        </is>
-      </c>
-      <c r="AW16" s="2" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>US</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>META</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Meta Platforms</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-23T23:07:13+08:00</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr"/>
-      <c r="I17" s="2" t="inlineStr"/>
-      <c r="J17" s="2" t="inlineStr"/>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>待補分析</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>方法二</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="n">
-        <v>0.9330000000000001</v>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>NOT_RELEVANT</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr"/>
-      <c r="R17" s="2" t="inlineStr"/>
-      <c r="S17" s="2" t="inlineStr"/>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>公司清單／原始紀錄</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxOOU5uNjZ6MTZvd2dkQlFWUFJ2VW9RdGNmLS12R0x2UDlmMC1jRzBpWmFWNGwzcXFySjFBUzd1V1JSeU5FNGVYdDQzZ1hod1g5SmVOZUw2eTZKTEt0QnpFT0JONTc5eEhHUlNUTHlhMnd6TmF2eW9JX1FzZElGZzRsak1MdVFER2RYVDVJOHVVSnZLSXVzWUNBOFVoU0JfUF9z?oc=5</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>Yahoo Finance</t>
-        </is>
-      </c>
-      <c r="W17" s="2" t="inlineStr">
-        <is>
-          <t>1662077625e20e4158c6d6d9</t>
-        </is>
-      </c>
-      <c r="X17" s="2" t="inlineStr"/>
-      <c r="Y17" s="2" t="inlineStr"/>
-      <c r="Z17" s="2" t="inlineStr"/>
-      <c r="AA17" s="2" t="inlineStr"/>
-      <c r="AB17" s="2" t="inlineStr"/>
-      <c r="AC17" s="2" t="inlineStr">
-        <is>
-          <t>QUOTA_PENDING</t>
-        </is>
-      </c>
-      <c r="AD17" s="2" t="inlineStr"/>
-      <c r="AE17" s="2" t="inlineStr"/>
-      <c r="AF17" s="2" t="inlineStr"/>
-      <c r="AG17" s="2" t="inlineStr"/>
-      <c r="AH17" s="2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AI17" s="2" t="inlineStr">
-        <is>
-          <t>openai/gpt-oss-20b</t>
-        </is>
-      </c>
-      <c r="AJ17" s="2" t="inlineStr">
-        <is>
-          <t>financial_events_v1.0</t>
-        </is>
-      </c>
-      <c r="AK17" s="2" t="inlineStr"/>
-      <c r="AL17" s="2" t="inlineStr"/>
-      <c r="AM17" s="2" t="inlineStr"/>
-      <c r="AN17" s="2" t="inlineStr"/>
-      <c r="AO17" s="2" t="inlineStr">
-        <is>
-          <t>27ae0e4f67d27857be0e98ca</t>
-        </is>
-      </c>
-      <c r="AP17" s="2" t="inlineStr">
-        <is>
-          <t>人工確認</t>
-        </is>
-      </c>
-      <c r="AQ17" s="2" t="inlineStr">
-        <is>
-          <t>無關新聞事件</t>
-        </is>
-      </c>
-      <c r="AR17" s="2" t="inlineStr"/>
-      <c r="AS17" s="2" t="inlineStr">
-        <is>
-          <t>8d2bf44846475f369f3134681a465fafc51dc63ac9d90ebf8bca03c554f5390f</t>
-        </is>
-      </c>
-      <c r="AT17" s="2" t="inlineStr">
-        <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
-        </is>
-      </c>
-      <c r="AU17" s="2" t="inlineStr"/>
-      <c r="AV17" s="2" t="inlineStr">
-        <is>
-          <t>Polen Focus Growth Strategy Boosts Meta Platforms, Inc. (META) on AI Monetization Potential</t>
-        </is>
-      </c>
-      <c r="AW17" s="2" t="inlineStr"/>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:AW17"/>
+  <autoFilter ref="A1:AW1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -22597,7 +23313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W3"/>
+  <dimension ref="A1:W4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -22745,7 +23461,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
+          <t>resume-8ace4fc710054c79af17e3416a397b99</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -22760,12 +23476,12 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-23T00:16:00+08:00</t>
+          <t>2026-10-22T00:26:32.508450+08:00</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:16:00+08:00</t>
+          <t>2026-10-24T00:26:32.508450+08:00</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -22773,47 +23489,43 @@
           <t>US</t>
         </is>
       </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>方法一|方法二</t>
-        </is>
-      </c>
+      <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="b">
         <v>1</v>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:20:47.845317+08:00</t>
+          <t>2026-10-24T00:26:34.299718+08:00</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:21:20.302846+08:00</t>
+          <t>2026-10-24T00:32:11.776786+08:00</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>1</v>
+        <v>17</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="M2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>48</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>17</v>
       </c>
-      <c r="N2" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>2</v>
-      </c>
       <c r="P2" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q2" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="R2" s="2" t="n">
-        <v>20</v>
+        <v>51</v>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
@@ -22822,14 +23534,14 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
+          <t>['沿用已擷取資料；不重新抓取']</t>
         </is>
       </c>
       <c r="U2" s="2" t="n">
-        <v>1</v>
+        <v>35</v>
       </c>
       <c r="V2" s="2" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="W2" s="2" t="n">
         <v>0</v>
@@ -22838,7 +23550,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+          <t>044ceacec26a4a2f8d3d0f4d45d89e7a</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -22876,37 +23588,37 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:19:11.949238+08:00</t>
+          <t>2026-10-24T00:20:47.845317+08:00</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-24T00:19:18.833437+08:00</t>
+          <t>2026-10-24T00:21:20.302846+08:00</t>
         </is>
       </c>
       <c r="K3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="N3" s="2" t="n">
-        <v>30</v>
+        <v>3</v>
       </c>
       <c r="O3" s="2" t="n">
-        <v>17</v>
+        <v>2</v>
       </c>
       <c r="P3" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q3" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="R3" s="2" t="n">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="S3" s="2" t="inlineStr">
         <is>
@@ -22915,21 +23627,114 @@
       </c>
       <c r="T3" s="2" t="inlineStr">
         <is>
-          <t>['沿用已擷取資料；不重新抓取']</t>
+          <t>['方法一 6 筆', '方法二 12 筆；公司 1 家（非輪替）', 'FinBERT 完成 18 筆']</t>
         </is>
       </c>
       <c r="U3" s="2" t="n">
         <v>1</v>
       </c>
       <c r="V3" s="2" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="W3" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>a62af6ad2a0044b7a685a4178159b27a</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>manual</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>success</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-23T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:16:00+08:00</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>US</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>方法一|方法二</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:11.949238+08:00</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-24T00:19:18.833437+08:00</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>30</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>17</v>
+      </c>
+      <c r="P4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" s="2" t="n">
+        <v>33</v>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>['沿用已擷取資料；不重新抓取']</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="V4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" s="2" t="n">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:W3"/>
+  <autoFilter ref="A1:W4"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>